--- a/src/test/resources/Excel/DBC模版.xlsx
+++ b/src/test/resources/Excel/DBC模版.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_USER\SLC\Code\IDEA_Project\smartGrid\src\test\resources\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_USER\SLC\Code\IDEA_Project\smart-dbc\src\test\resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C18D69-3FBB-4581-8950-59821F45A432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2786B26B-1C43-41EA-8262-9DAD89BF0865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="476" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CanProtocol_Info" sheetId="7" r:id="rId1"/>
@@ -2550,7 +2550,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="223">
   <si>
     <t>测试协议</t>
   </si>
@@ -3244,6 +3244,31 @@
   </si>
   <si>
     <t>testProtocol</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>SignalSendType
+信号发送类型（必填）9</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>DataType
+数据类型(必填)13</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>InitialValuePhys
+物理初始值（必填）18</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>SignalMinValueHex
+总线最小值（十六进制）(非必填)19</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>InvalidValueHex
+总线无效值（十六进制）（非必填）22</t>
     <phoneticPr fontId="44" type="noConversion"/>
   </si>
 </sst>
@@ -3252,9 +3277,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="[$¥-804]#,##0.0000000000000;[$¥-804]\-#,##0.0000000000000"/>
+    <numFmt numFmtId="176" formatCode="[$¥-804]#,##0.0000000000000;[$¥-804]\-#,##0.0000000000000"/>
   </numFmts>
-  <fonts count="46" x14ac:knownFonts="1">
+  <fonts count="47" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3552,6 +3577,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -3801,7 +3834,7 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="4" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
@@ -3828,7 +3861,7 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
@@ -3886,7 +3919,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4009,6 +4042,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="38">
     <cellStyle name="Standard_SL(Template)_PF2010_C71 CAN CMX V1.1_100817" xfId="3" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
@@ -4467,8 +4503,8 @@
       <c r="I1" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="30" t="s">
-        <v>17</v>
+      <c r="J1" s="52" t="s">
+        <v>218</v>
       </c>
       <c r="K1" s="30" t="s">
         <v>18</v>
@@ -4479,8 +4515,8 @@
       <c r="M1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="30" t="s">
-        <v>21</v>
+      <c r="N1" s="52" t="s">
+        <v>219</v>
       </c>
       <c r="O1" s="28" t="s">
         <v>22</v>
@@ -4494,11 +4530,11 @@
       <c r="R1" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="T1" s="30" t="s">
-        <v>27</v>
+      <c r="S1" s="52" t="s">
+        <v>220</v>
+      </c>
+      <c r="T1" s="52" t="s">
+        <v>221</v>
       </c>
       <c r="U1" s="30" t="s">
         <v>28</v>
@@ -4507,7 +4543,7 @@
         <v>29</v>
       </c>
       <c r="W1" s="30" t="s">
-        <v>30</v>
+        <v>222</v>
       </c>
       <c r="X1" s="30" t="s">
         <v>31</v>

--- a/src/test/resources/Excel/DBC模版.xlsx
+++ b/src/test/resources/Excel/DBC模版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_USER\SLC\Code\IDEA_Project\smart-dbc\src\test\resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2786B26B-1C43-41EA-8262-9DAD89BF0865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65300DA2-0418-40B7-9F8B-41182A0A8CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="476" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="476" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CanProtocol_Info" sheetId="7" r:id="rId1"/>
@@ -1719,6 +1719,41 @@
         </r>
       </text>
     </comment>
+    <comment ref="B11" authorId="1" shapeId="0" xr:uid="{94FABF88-1AA4-4777-BDB3-F411CAAF4BDA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="等线"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Normal 类型包括 Extended 和 Standard  。
+并且现程序根据id自动判断扩展帧 Extended 和标准帧 Standard ，故不必特地填写扩展帧</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="1" shapeId="0" xr:uid="{AC3CAF0B-70B3-4BC4-969A-CB047C53693F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="36"/>
+            <rFont val="Microsoft YaHei UI"/>
+            <charset val="134"/>
+          </rPr>
+          <t>注释不可以写到这里</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -2550,7 +2585,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="233">
   <si>
     <t>测试协议</t>
   </si>
@@ -3269,6 +3304,55 @@
   <si>
     <t>InvalidValueHex
 总线无效值（十六进制）（非必填）22</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>SignalName
+信号名称（必填）6
+绿色项的内容是必填项，其余项可以不填</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>SignalDescription
+信号描述(SignalComment 信号注释)（非必填）7</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>GroupType 
+分组类型</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>IfActive</t>
+  </si>
+  <si>
+    <t>StartBit
+起始位(必填)11</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitLength(Bit)
+信号长度(必填)12</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>Resolution 分辨率; 
+精度(必填)Factor14</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>Offset
+偏移量(必填)15</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>SignalMinValuePhys
+物理最小值(必填)16</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>SignalMaxValuePhys
+物理最大值(非必填)17</t>
     <phoneticPr fontId="44" type="noConversion"/>
   </si>
 </sst>
@@ -3279,7 +3363,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$¥-804]#,##0.0000000000000;[$¥-804]\-#,##0.0000000000000"/>
   </numFmts>
-  <fonts count="47" x14ac:knownFonts="1">
+  <fonts count="48" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3580,6 +3664,14 @@
     <font>
       <b/>
       <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <family val="2"/>
@@ -3919,7 +4011,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4043,6 +4135,15 @@
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4494,11 +4595,11 @@
       <c r="F1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="30" t="s">
-        <v>15</v>
+      <c r="G1" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="H1" s="52" t="s">
+        <v>224</v>
       </c>
       <c r="I1" s="30" t="s">
         <v>16</v>
@@ -4560,8 +4661,8 @@
       <c r="AB1" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="AC1" s="30" t="s">
-        <v>36</v>
+      <c r="AC1" s="52" t="s">
+        <v>225</v>
       </c>
       <c r="AD1" s="49" t="s">
         <v>37</v>
@@ -9153,12 +9254,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AH10"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.149999999999999" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="10.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.75" style="3" customWidth="1"/>
     <col min="4" max="4" width="9.875" style="3" customWidth="1"/>
     <col min="5" max="5" width="10.5" style="4" customWidth="1"/>
     <col min="6" max="6" width="8.875" style="3"/>
@@ -9171,12 +9272,12 @@
     <col min="14" max="14" width="11.875" style="3" customWidth="1"/>
     <col min="15" max="15" width="11.625" style="4" customWidth="1"/>
     <col min="16" max="16" width="8.875" style="4"/>
-    <col min="17" max="17" width="11.375" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="19" width="8.875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="11" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="11.125" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="24" width="8.875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="25" max="25" width="44.25" style="3" customWidth="1" collapsed="1"/>
+    <col min="17" max="17" width="11.375" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="19" width="8.875" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="11" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="11.125" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="24" width="8.875" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="25" width="44.25" style="3" customWidth="1"/>
     <col min="26" max="26" width="8.25" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="27" max="27" width="8.875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="28" max="28" width="11" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
@@ -9216,35 +9317,35 @@
       <c r="I1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="8" t="s">
-        <v>17</v>
+      <c r="J1" s="54" t="s">
+        <v>218</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>26</v>
+      <c r="L1" s="55" t="s">
+        <v>227</v>
+      </c>
+      <c r="M1" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="N1" s="54" t="s">
+        <v>219</v>
+      </c>
+      <c r="O1" s="55" t="s">
+        <v>229</v>
+      </c>
+      <c r="P1" s="55" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q1" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="R1" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="S1" s="54" t="s">
+        <v>220</v>
       </c>
       <c r="T1" s="8" t="s">
         <v>27</v>
@@ -9355,7 +9456,9 @@
         <v>200</v>
       </c>
       <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
+      <c r="I3" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="J3" s="12"/>
       <c r="K3" s="13"/>
       <c r="L3" s="13">
@@ -9401,7 +9504,9 @@
         <v>201</v>
       </c>
       <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
+      <c r="I4" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="J4" s="12"/>
       <c r="K4" s="13"/>
       <c r="L4" s="13">
@@ -9447,7 +9552,7 @@
         <v>203</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="E5" s="11">
         <v>100</v>
@@ -9587,7 +9692,7 @@
         <v>207</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="E8" s="16">
         <v>500</v>
@@ -9720,6 +9825,1868 @@
       <c r="AG10" s="12"/>
       <c r="AH10" s="12"/>
     </row>
+    <row r="11" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="31">
+        <v>100</v>
+      </c>
+      <c r="F11" s="31">
+        <v>8</v>
+      </c>
+      <c r="G11" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="31"/>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA11" s="31"/>
+      <c r="AB11" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC11" s="31"/>
+      <c r="AD11" s="34"/>
+      <c r="AE11" s="34"/>
+      <c r="AF11" s="34"/>
+      <c r="AG11" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH11" s="34" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="33"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="K12" s="45">
+        <v>0</v>
+      </c>
+      <c r="L12" s="45">
+        <v>0</v>
+      </c>
+      <c r="M12" s="45">
+        <v>8</v>
+      </c>
+      <c r="N12" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O12" s="45">
+        <v>1</v>
+      </c>
+      <c r="P12" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="45">
+        <v>0</v>
+      </c>
+      <c r="R12" s="45">
+        <v>255</v>
+      </c>
+      <c r="S12" s="45">
+        <v>0</v>
+      </c>
+      <c r="T12" s="45">
+        <v>0</v>
+      </c>
+      <c r="U12" s="45">
+        <v>255</v>
+      </c>
+      <c r="V12" s="45">
+        <v>0</v>
+      </c>
+      <c r="W12" s="34"/>
+      <c r="X12" s="34"/>
+      <c r="Y12" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z12" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA12" s="34"/>
+      <c r="AB12" s="33"/>
+      <c r="AC12" s="44"/>
+      <c r="AD12" s="33"/>
+      <c r="AE12" s="33"/>
+      <c r="AF12" s="33"/>
+      <c r="AG12" s="33"/>
+      <c r="AH12" s="33"/>
+    </row>
+    <row r="13" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="33"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="K13" s="34">
+        <v>1</v>
+      </c>
+      <c r="L13" s="34">
+        <v>8</v>
+      </c>
+      <c r="M13" s="34">
+        <v>2</v>
+      </c>
+      <c r="N13" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O13" s="45">
+        <v>1</v>
+      </c>
+      <c r="P13" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="34">
+        <v>0</v>
+      </c>
+      <c r="R13" s="34">
+        <v>3</v>
+      </c>
+      <c r="S13" s="34">
+        <v>0</v>
+      </c>
+      <c r="T13" s="34">
+        <v>0</v>
+      </c>
+      <c r="U13" s="34">
+        <v>3</v>
+      </c>
+      <c r="V13" s="34">
+        <v>0</v>
+      </c>
+      <c r="W13" s="34">
+        <v>3</v>
+      </c>
+      <c r="X13" s="34"/>
+      <c r="Y13" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z13" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA13" s="34"/>
+      <c r="AB13" s="33"/>
+      <c r="AC13" s="44"/>
+      <c r="AD13" s="33"/>
+      <c r="AE13" s="33"/>
+      <c r="AF13" s="33"/>
+      <c r="AG13" s="33"/>
+      <c r="AH13" s="33"/>
+    </row>
+    <row r="14" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="33"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="I14" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="J14" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="K14" s="34">
+        <v>2</v>
+      </c>
+      <c r="L14" s="34">
+        <v>10</v>
+      </c>
+      <c r="M14" s="34">
+        <v>4</v>
+      </c>
+      <c r="N14" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O14" s="45">
+        <v>1</v>
+      </c>
+      <c r="P14" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="34">
+        <v>0</v>
+      </c>
+      <c r="R14" s="34">
+        <v>15</v>
+      </c>
+      <c r="S14" s="34">
+        <v>0</v>
+      </c>
+      <c r="T14" s="34">
+        <v>0</v>
+      </c>
+      <c r="U14" s="34">
+        <v>15</v>
+      </c>
+      <c r="V14" s="34">
+        <v>0</v>
+      </c>
+      <c r="W14" s="34">
+        <v>15</v>
+      </c>
+      <c r="X14" s="34"/>
+      <c r="Y14" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z14" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA14" s="34"/>
+      <c r="AB14" s="33"/>
+      <c r="AC14" s="44"/>
+      <c r="AD14" s="33"/>
+      <c r="AE14" s="33"/>
+      <c r="AF14" s="33"/>
+      <c r="AG14" s="33"/>
+      <c r="AH14" s="33"/>
+    </row>
+    <row r="15" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="33"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="J15" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="K15" s="34">
+        <v>2</v>
+      </c>
+      <c r="L15" s="34">
+        <v>14</v>
+      </c>
+      <c r="M15" s="34">
+        <v>4</v>
+      </c>
+      <c r="N15" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O15" s="45">
+        <v>1</v>
+      </c>
+      <c r="P15" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="34">
+        <v>0</v>
+      </c>
+      <c r="R15" s="34">
+        <v>15</v>
+      </c>
+      <c r="S15" s="34">
+        <v>0</v>
+      </c>
+      <c r="T15" s="34">
+        <v>0</v>
+      </c>
+      <c r="U15" s="34">
+        <v>15</v>
+      </c>
+      <c r="V15" s="34">
+        <v>0</v>
+      </c>
+      <c r="W15" s="34">
+        <v>15</v>
+      </c>
+      <c r="X15" s="34"/>
+      <c r="Y15" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z15" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA15" s="34"/>
+      <c r="AB15" s="33"/>
+      <c r="AC15" s="44"/>
+      <c r="AD15" s="33"/>
+      <c r="AE15" s="33"/>
+      <c r="AF15" s="33"/>
+      <c r="AG15" s="33"/>
+      <c r="AH15" s="33"/>
+    </row>
+    <row r="16" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="33"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="J16" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34">
+        <v>56</v>
+      </c>
+      <c r="M16" s="34">
+        <v>8</v>
+      </c>
+      <c r="N16" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O16" s="45">
+        <v>1</v>
+      </c>
+      <c r="P16" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="34"/>
+      <c r="S16" s="34"/>
+      <c r="T16" s="34"/>
+      <c r="U16" s="34"/>
+      <c r="V16" s="34"/>
+      <c r="W16" s="34"/>
+      <c r="X16" s="34"/>
+      <c r="Y16" s="36"/>
+      <c r="Z16" s="33"/>
+      <c r="AA16" s="34"/>
+      <c r="AB16" s="33"/>
+      <c r="AC16" s="44"/>
+      <c r="AD16" s="33"/>
+      <c r="AE16" s="33"/>
+      <c r="AF16" s="33"/>
+      <c r="AG16" s="33"/>
+      <c r="AH16" s="33"/>
+    </row>
+    <row r="17" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="37">
+        <v>100</v>
+      </c>
+      <c r="F17" s="37">
+        <v>8</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="I17" s="37"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="37"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="37"/>
+      <c r="P17" s="37"/>
+      <c r="Q17" s="37"/>
+      <c r="R17" s="37"/>
+      <c r="S17" s="37"/>
+      <c r="T17" s="37"/>
+      <c r="U17" s="37"/>
+      <c r="V17" s="37"/>
+      <c r="W17" s="37"/>
+      <c r="X17" s="37"/>
+      <c r="Y17" s="37"/>
+      <c r="Z17" s="37"/>
+      <c r="AA17" s="37"/>
+      <c r="AB17" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC17" s="47"/>
+      <c r="AD17" s="34"/>
+      <c r="AE17" s="34"/>
+      <c r="AF17" s="50"/>
+      <c r="AG17" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH17" s="50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="33"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="I18" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="J18" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="K18" s="45">
+        <v>0</v>
+      </c>
+      <c r="L18" s="45">
+        <v>0</v>
+      </c>
+      <c r="M18" s="45">
+        <v>8</v>
+      </c>
+      <c r="N18" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O18" s="45">
+        <v>1</v>
+      </c>
+      <c r="P18" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="45">
+        <v>0</v>
+      </c>
+      <c r="R18" s="45">
+        <v>255</v>
+      </c>
+      <c r="S18" s="45">
+        <v>0</v>
+      </c>
+      <c r="T18" s="45">
+        <v>0</v>
+      </c>
+      <c r="U18" s="45">
+        <v>255</v>
+      </c>
+      <c r="V18" s="45">
+        <v>0</v>
+      </c>
+      <c r="W18" s="34"/>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z18" s="33"/>
+      <c r="AA18" s="34"/>
+      <c r="AB18" s="33"/>
+      <c r="AC18" s="44"/>
+      <c r="AD18" s="33"/>
+      <c r="AE18" s="33"/>
+      <c r="AF18" s="33"/>
+      <c r="AG18" s="33"/>
+      <c r="AH18" s="33"/>
+    </row>
+    <row r="19" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="33"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="J19" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="K19" s="34">
+        <v>1</v>
+      </c>
+      <c r="L19" s="34">
+        <f>M18+L18</f>
+        <v>8</v>
+      </c>
+      <c r="M19" s="34">
+        <v>8</v>
+      </c>
+      <c r="N19" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O19" s="45">
+        <v>1</v>
+      </c>
+      <c r="P19" s="45">
+        <v>-50</v>
+      </c>
+      <c r="Q19" s="34">
+        <v>-50</v>
+      </c>
+      <c r="R19" s="34">
+        <v>205</v>
+      </c>
+      <c r="S19" s="34">
+        <v>20</v>
+      </c>
+      <c r="T19" s="34">
+        <v>0</v>
+      </c>
+      <c r="U19" s="34">
+        <v>255</v>
+      </c>
+      <c r="V19" s="45">
+        <v>0</v>
+      </c>
+      <c r="W19" s="34"/>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="36"/>
+      <c r="Z19" s="36"/>
+      <c r="AA19" s="34"/>
+      <c r="AB19" s="33"/>
+      <c r="AC19" s="44"/>
+      <c r="AD19" s="33"/>
+      <c r="AE19" s="33"/>
+      <c r="AF19" s="33"/>
+      <c r="AG19" s="33"/>
+      <c r="AH19" s="33"/>
+    </row>
+    <row r="20" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="33"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="J20" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="K20" s="34">
+        <v>2</v>
+      </c>
+      <c r="L20" s="34">
+        <f>M19+L19</f>
+        <v>16</v>
+      </c>
+      <c r="M20" s="34">
+        <v>4</v>
+      </c>
+      <c r="N20" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O20" s="45">
+        <v>1</v>
+      </c>
+      <c r="P20" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="34">
+        <v>0</v>
+      </c>
+      <c r="R20" s="34">
+        <v>15</v>
+      </c>
+      <c r="S20" s="34">
+        <v>0</v>
+      </c>
+      <c r="T20" s="34">
+        <v>0</v>
+      </c>
+      <c r="U20" s="34">
+        <v>15</v>
+      </c>
+      <c r="V20" s="45">
+        <v>0</v>
+      </c>
+      <c r="W20" s="34"/>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z20" s="36"/>
+      <c r="AA20" s="34"/>
+      <c r="AB20" s="33"/>
+      <c r="AC20" s="44"/>
+      <c r="AD20" s="33"/>
+      <c r="AE20" s="33"/>
+      <c r="AF20" s="33"/>
+      <c r="AG20" s="33"/>
+      <c r="AH20" s="33"/>
+    </row>
+    <row r="21" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="33"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="I21" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="J21" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="K21" s="34">
+        <v>2</v>
+      </c>
+      <c r="L21" s="34">
+        <v>20</v>
+      </c>
+      <c r="M21" s="34">
+        <v>4</v>
+      </c>
+      <c r="N21" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O21" s="45">
+        <v>1</v>
+      </c>
+      <c r="P21" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="34">
+        <v>0</v>
+      </c>
+      <c r="R21" s="34">
+        <v>15</v>
+      </c>
+      <c r="S21" s="34">
+        <v>0</v>
+      </c>
+      <c r="T21" s="34">
+        <v>0</v>
+      </c>
+      <c r="U21" s="34">
+        <v>15</v>
+      </c>
+      <c r="V21" s="45">
+        <v>0</v>
+      </c>
+      <c r="W21" s="34"/>
+      <c r="X21" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y21" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z21" s="36"/>
+      <c r="AA21" s="34"/>
+      <c r="AB21" s="33"/>
+      <c r="AC21" s="44"/>
+      <c r="AD21" s="33"/>
+      <c r="AE21" s="33"/>
+      <c r="AF21" s="33"/>
+      <c r="AG21" s="33"/>
+      <c r="AH21" s="33"/>
+    </row>
+    <row r="22" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="33"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="I22" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="J22" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="K22" s="34">
+        <v>3</v>
+      </c>
+      <c r="L22" s="34">
+        <v>24</v>
+      </c>
+      <c r="M22" s="34">
+        <v>2</v>
+      </c>
+      <c r="N22" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O22" s="45">
+        <v>1</v>
+      </c>
+      <c r="P22" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="34">
+        <v>0</v>
+      </c>
+      <c r="R22" s="34">
+        <v>3</v>
+      </c>
+      <c r="S22" s="34">
+        <v>0</v>
+      </c>
+      <c r="T22" s="34">
+        <v>0</v>
+      </c>
+      <c r="U22" s="34">
+        <v>3</v>
+      </c>
+      <c r="V22" s="45">
+        <v>0</v>
+      </c>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z22" s="36"/>
+      <c r="AA22" s="34"/>
+      <c r="AB22" s="33"/>
+      <c r="AC22" s="44"/>
+      <c r="AD22" s="33"/>
+      <c r="AE22" s="33"/>
+      <c r="AF22" s="33"/>
+      <c r="AG22" s="33"/>
+      <c r="AH22" s="33"/>
+    </row>
+    <row r="23" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="33"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="I23" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="J23" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="K23" s="34">
+        <v>3</v>
+      </c>
+      <c r="L23" s="34">
+        <v>26</v>
+      </c>
+      <c r="M23" s="34">
+        <v>2</v>
+      </c>
+      <c r="N23" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O23" s="45">
+        <v>1</v>
+      </c>
+      <c r="P23" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="34">
+        <v>0</v>
+      </c>
+      <c r="R23" s="34">
+        <v>3</v>
+      </c>
+      <c r="S23" s="34">
+        <v>0</v>
+      </c>
+      <c r="T23" s="34">
+        <v>0</v>
+      </c>
+      <c r="U23" s="34">
+        <v>3</v>
+      </c>
+      <c r="V23" s="45">
+        <v>0</v>
+      </c>
+      <c r="W23" s="34"/>
+      <c r="X23" s="34"/>
+      <c r="Y23" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z23" s="36"/>
+      <c r="AA23" s="34"/>
+      <c r="AB23" s="33"/>
+      <c r="AC23" s="44"/>
+      <c r="AD23" s="33"/>
+      <c r="AE23" s="33"/>
+      <c r="AF23" s="33"/>
+      <c r="AG23" s="33"/>
+      <c r="AH23" s="33"/>
+    </row>
+    <row r="24" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="33"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="H24" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="I24" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="J24" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="K24" s="34">
+        <v>3</v>
+      </c>
+      <c r="L24" s="34">
+        <v>28</v>
+      </c>
+      <c r="M24" s="34">
+        <v>2</v>
+      </c>
+      <c r="N24" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O24" s="45">
+        <v>1</v>
+      </c>
+      <c r="P24" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="34">
+        <v>0</v>
+      </c>
+      <c r="R24" s="34">
+        <v>3</v>
+      </c>
+      <c r="S24" s="34">
+        <v>0</v>
+      </c>
+      <c r="T24" s="34"/>
+      <c r="U24" s="34"/>
+      <c r="V24" s="45"/>
+      <c r="W24" s="34"/>
+      <c r="X24" s="34"/>
+      <c r="Y24" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z24" s="36"/>
+      <c r="AA24" s="34"/>
+      <c r="AB24" s="33"/>
+      <c r="AC24" s="44"/>
+      <c r="AD24" s="33"/>
+      <c r="AE24" s="33"/>
+      <c r="AF24" s="33"/>
+      <c r="AG24" s="33"/>
+      <c r="AH24" s="33"/>
+    </row>
+    <row r="25" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="33"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="H25" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="I25" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="J25" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="K25" s="34">
+        <v>7</v>
+      </c>
+      <c r="L25" s="34">
+        <v>56</v>
+      </c>
+      <c r="M25" s="34">
+        <v>8</v>
+      </c>
+      <c r="N25" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O25" s="45">
+        <v>1</v>
+      </c>
+      <c r="P25" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="34">
+        <v>0</v>
+      </c>
+      <c r="R25" s="34">
+        <v>255</v>
+      </c>
+      <c r="S25" s="34">
+        <v>0</v>
+      </c>
+      <c r="T25" s="34">
+        <v>0</v>
+      </c>
+      <c r="U25" s="34">
+        <v>255</v>
+      </c>
+      <c r="V25" s="45">
+        <v>0</v>
+      </c>
+      <c r="W25" s="34"/>
+      <c r="X25" s="34"/>
+      <c r="Y25" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z25" s="36"/>
+      <c r="AA25" s="34"/>
+      <c r="AB25" s="33"/>
+      <c r="AC25" s="44"/>
+      <c r="AD25" s="33"/>
+      <c r="AE25" s="33"/>
+      <c r="AF25" s="33"/>
+      <c r="AG25" s="33"/>
+      <c r="AH25" s="33"/>
+    </row>
+    <row r="26" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" s="39">
+        <v>50</v>
+      </c>
+      <c r="F26" s="39">
+        <v>8</v>
+      </c>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
+      <c r="S26" s="39"/>
+      <c r="T26" s="39"/>
+      <c r="U26" s="39"/>
+      <c r="V26" s="39"/>
+      <c r="W26" s="39"/>
+      <c r="X26" s="39"/>
+      <c r="Y26" s="39"/>
+      <c r="Z26" s="39"/>
+      <c r="AA26" s="39"/>
+      <c r="AB26" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC26" s="39"/>
+      <c r="AD26" s="34"/>
+      <c r="AE26" s="34"/>
+      <c r="AF26" s="34"/>
+      <c r="AG26" s="34"/>
+      <c r="AH26" s="34"/>
+    </row>
+    <row r="27" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="H27" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="I27" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="J27" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="K27" s="33"/>
+      <c r="L27" s="34">
+        <v>7</v>
+      </c>
+      <c r="M27" s="34">
+        <v>8</v>
+      </c>
+      <c r="N27" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O27" s="34">
+        <v>1</v>
+      </c>
+      <c r="P27" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="33"/>
+      <c r="S27" s="33"/>
+      <c r="T27" s="33"/>
+      <c r="U27" s="33"/>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="33"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+      <c r="AA27" s="33"/>
+      <c r="AB27" s="33"/>
+      <c r="AC27" s="44"/>
+      <c r="AD27" s="33"/>
+      <c r="AE27" s="33"/>
+      <c r="AF27" s="33"/>
+      <c r="AG27" s="33"/>
+      <c r="AH27" s="33"/>
+    </row>
+    <row r="28" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="H28" s="33"/>
+      <c r="I28" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="J28" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="K28" s="33"/>
+      <c r="L28" s="34">
+        <v>8</v>
+      </c>
+      <c r="M28" s="34">
+        <v>8</v>
+      </c>
+      <c r="N28" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O28" s="34">
+        <v>1</v>
+      </c>
+      <c r="P28" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="33"/>
+      <c r="S28" s="33"/>
+      <c r="T28" s="33"/>
+      <c r="U28" s="33"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="33"/>
+      <c r="Y28" s="33"/>
+      <c r="Z28" s="33"/>
+      <c r="AA28" s="33"/>
+      <c r="AB28" s="33"/>
+      <c r="AC28" s="44"/>
+      <c r="AD28" s="33"/>
+      <c r="AE28" s="33"/>
+      <c r="AF28" s="33"/>
+      <c r="AG28" s="33"/>
+      <c r="AH28" s="33"/>
+    </row>
+    <row r="29" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="H29" s="33"/>
+      <c r="I29" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="J29" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="K29" s="33"/>
+      <c r="L29" s="34">
+        <v>20</v>
+      </c>
+      <c r="M29" s="34">
+        <v>8</v>
+      </c>
+      <c r="N29" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O29" s="34">
+        <v>1</v>
+      </c>
+      <c r="P29" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="33"/>
+      <c r="R29" s="33"/>
+      <c r="S29" s="33"/>
+      <c r="T29" s="33"/>
+      <c r="U29" s="33"/>
+      <c r="V29" s="33"/>
+      <c r="W29" s="33"/>
+      <c r="X29" s="33"/>
+      <c r="Y29" s="33"/>
+      <c r="Z29" s="33"/>
+      <c r="AA29" s="33"/>
+      <c r="AB29" s="33"/>
+      <c r="AC29" s="44"/>
+      <c r="AD29" s="33"/>
+      <c r="AE29" s="33"/>
+      <c r="AF29" s="33"/>
+      <c r="AG29" s="33"/>
+      <c r="AH29" s="33"/>
+    </row>
+    <row r="30" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="33"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="33"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" s="33"/>
+      <c r="I30" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="J30" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="K30" s="33"/>
+      <c r="L30" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="M30" s="34">
+        <v>4</v>
+      </c>
+      <c r="N30" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O30" s="34">
+        <v>1</v>
+      </c>
+      <c r="P30" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="33"/>
+      <c r="R30" s="33"/>
+      <c r="S30" s="33"/>
+      <c r="T30" s="33"/>
+      <c r="U30" s="33"/>
+      <c r="V30" s="33"/>
+      <c r="W30" s="33"/>
+      <c r="X30" s="33"/>
+      <c r="Y30" s="33"/>
+      <c r="Z30" s="33"/>
+      <c r="AA30" s="33"/>
+      <c r="AB30" s="33"/>
+      <c r="AC30" s="44"/>
+      <c r="AD30" s="33"/>
+      <c r="AE30" s="33"/>
+      <c r="AF30" s="33"/>
+      <c r="AG30" s="33"/>
+      <c r="AH30" s="33"/>
+    </row>
+    <row r="31" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="33"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="H31" s="33"/>
+      <c r="I31" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="J31" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="K31" s="33"/>
+      <c r="L31" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="M31" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="N31" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O31" s="34">
+        <v>1</v>
+      </c>
+      <c r="P31" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="33"/>
+      <c r="S31" s="33"/>
+      <c r="T31" s="33"/>
+      <c r="U31" s="33"/>
+      <c r="V31" s="33"/>
+      <c r="W31" s="33"/>
+      <c r="X31" s="33"/>
+      <c r="Y31" s="33"/>
+      <c r="Z31" s="33"/>
+      <c r="AA31" s="33"/>
+      <c r="AB31" s="33"/>
+      <c r="AC31" s="44"/>
+      <c r="AD31" s="33"/>
+      <c r="AE31" s="33"/>
+      <c r="AF31" s="33"/>
+      <c r="AG31" s="33"/>
+      <c r="AH31" s="33"/>
+    </row>
+    <row r="32" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="33"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="H32" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="I32" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="J32" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="K32" s="34"/>
+      <c r="L32" s="48">
+        <v>41</v>
+      </c>
+      <c r="M32" s="48">
+        <v>16</v>
+      </c>
+      <c r="N32" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O32" s="34">
+        <v>1</v>
+      </c>
+      <c r="P32" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="34"/>
+      <c r="R32" s="34"/>
+      <c r="S32" s="34"/>
+      <c r="T32" s="34"/>
+      <c r="U32" s="34"/>
+      <c r="V32" s="34"/>
+      <c r="W32" s="34"/>
+      <c r="X32" s="34"/>
+      <c r="Y32" s="33"/>
+      <c r="Z32" s="33"/>
+      <c r="AA32" s="34"/>
+      <c r="AB32" s="33"/>
+      <c r="AC32" s="44"/>
+      <c r="AD32" s="33"/>
+      <c r="AE32" s="33"/>
+      <c r="AF32" s="33"/>
+      <c r="AG32" s="33"/>
+      <c r="AH32" s="33"/>
+    </row>
+    <row r="33" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="41">
+        <v>200</v>
+      </c>
+      <c r="F33" s="40">
+        <v>8</v>
+      </c>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="41"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="40"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="41"/>
+      <c r="S33" s="41"/>
+      <c r="T33" s="41"/>
+      <c r="U33" s="41"/>
+      <c r="V33" s="41"/>
+      <c r="W33" s="41"/>
+      <c r="X33" s="41"/>
+      <c r="Y33" s="40"/>
+      <c r="Z33" s="40"/>
+      <c r="AA33" s="23"/>
+      <c r="AB33" s="27"/>
+      <c r="AC33" s="27"/>
+      <c r="AD33" s="26"/>
+      <c r="AE33" s="26"/>
+      <c r="AF33" s="27"/>
+      <c r="AG33" s="27"/>
+      <c r="AH33" s="27"/>
+    </row>
+    <row r="34" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="42"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="J34" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="K34" s="43"/>
+      <c r="L34" s="43">
+        <v>0</v>
+      </c>
+      <c r="M34" s="43">
+        <v>8</v>
+      </c>
+      <c r="N34" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="O34" s="43">
+        <v>1</v>
+      </c>
+      <c r="P34" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="43"/>
+      <c r="R34" s="43"/>
+      <c r="S34" s="43"/>
+      <c r="T34" s="43"/>
+      <c r="U34" s="43"/>
+      <c r="V34" s="43"/>
+      <c r="W34" s="43"/>
+      <c r="X34" s="43"/>
+      <c r="Y34" s="42"/>
+      <c r="Z34" s="42"/>
+      <c r="AA34" s="23"/>
+      <c r="AB34" s="27"/>
+      <c r="AC34" s="27"/>
+      <c r="AD34" s="26"/>
+      <c r="AE34" s="26"/>
+      <c r="AF34" s="27"/>
+      <c r="AG34" s="27"/>
+      <c r="AH34" s="27"/>
+    </row>
+    <row r="35" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="42"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="J35" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="K35" s="43"/>
+      <c r="L35" s="43">
+        <v>8</v>
+      </c>
+      <c r="M35" s="43">
+        <v>8</v>
+      </c>
+      <c r="N35" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="O35" s="43">
+        <v>1</v>
+      </c>
+      <c r="P35" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="43"/>
+      <c r="R35" s="43"/>
+      <c r="S35" s="43"/>
+      <c r="T35" s="43"/>
+      <c r="U35" s="43"/>
+      <c r="V35" s="43"/>
+      <c r="W35" s="43"/>
+      <c r="X35" s="43"/>
+      <c r="Y35" s="42"/>
+      <c r="Z35" s="42"/>
+      <c r="AA35" s="23"/>
+      <c r="AB35" s="27"/>
+      <c r="AC35" s="27"/>
+      <c r="AD35" s="26"/>
+      <c r="AE35" s="26"/>
+      <c r="AF35" s="27"/>
+      <c r="AG35" s="27"/>
+      <c r="AH35" s="27"/>
+    </row>
+    <row r="36" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="42"/>
+      <c r="B36" s="42"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="J36" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="K36" s="43"/>
+      <c r="L36" s="43">
+        <v>16</v>
+      </c>
+      <c r="M36" s="43">
+        <v>8</v>
+      </c>
+      <c r="N36" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="O36" s="43">
+        <v>1</v>
+      </c>
+      <c r="P36" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="43"/>
+      <c r="S36" s="43"/>
+      <c r="T36" s="43"/>
+      <c r="U36" s="43"/>
+      <c r="V36" s="43"/>
+      <c r="W36" s="43"/>
+      <c r="X36" s="43"/>
+      <c r="Y36" s="42"/>
+      <c r="Z36" s="42"/>
+      <c r="AA36" s="23"/>
+      <c r="AB36" s="27"/>
+      <c r="AC36" s="27"/>
+      <c r="AD36" s="26"/>
+      <c r="AE36" s="26"/>
+      <c r="AF36" s="27"/>
+      <c r="AG36" s="27"/>
+      <c r="AH36" s="27"/>
+    </row>
+    <row r="37" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="42"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="J37" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="K37" s="43"/>
+      <c r="L37" s="43">
+        <v>24</v>
+      </c>
+      <c r="M37" s="43">
+        <v>8</v>
+      </c>
+      <c r="N37" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="O37" s="43">
+        <v>1</v>
+      </c>
+      <c r="P37" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="43"/>
+      <c r="R37" s="43"/>
+      <c r="S37" s="43"/>
+      <c r="T37" s="43"/>
+      <c r="U37" s="43"/>
+      <c r="V37" s="43"/>
+      <c r="W37" s="43"/>
+      <c r="X37" s="43"/>
+      <c r="Y37" s="42"/>
+      <c r="Z37" s="42"/>
+      <c r="AA37" s="23"/>
+      <c r="AB37" s="27"/>
+      <c r="AC37" s="27"/>
+      <c r="AD37" s="26"/>
+      <c r="AE37" s="26"/>
+      <c r="AF37" s="27"/>
+      <c r="AG37" s="27"/>
+      <c r="AH37" s="27"/>
+    </row>
+    <row r="38" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="42"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="42"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="J38" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="K38" s="43"/>
+      <c r="L38" s="43">
+        <v>32</v>
+      </c>
+      <c r="M38" s="43">
+        <v>8</v>
+      </c>
+      <c r="N38" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="O38" s="43">
+        <v>0.2</v>
+      </c>
+      <c r="P38" s="43">
+        <v>-20</v>
+      </c>
+      <c r="Q38" s="43"/>
+      <c r="R38" s="43"/>
+      <c r="S38" s="43"/>
+      <c r="T38" s="43"/>
+      <c r="U38" s="43"/>
+      <c r="V38" s="43"/>
+      <c r="W38" s="43"/>
+      <c r="X38" s="43"/>
+      <c r="Y38" s="42"/>
+      <c r="Z38" s="42"/>
+      <c r="AA38" s="23"/>
+      <c r="AB38" s="27"/>
+      <c r="AC38" s="27"/>
+      <c r="AD38" s="26"/>
+      <c r="AE38" s="26"/>
+      <c r="AF38" s="27"/>
+      <c r="AG38" s="27"/>
+      <c r="AH38" s="27"/>
+    </row>
+    <row r="39" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="42"/>
+      <c r="B39" s="42"/>
+      <c r="C39" s="42"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="J39" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="K39" s="43"/>
+      <c r="L39" s="43">
+        <v>40</v>
+      </c>
+      <c r="M39" s="43">
+        <v>8</v>
+      </c>
+      <c r="N39" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="O39" s="43">
+        <v>0.5</v>
+      </c>
+      <c r="P39" s="43">
+        <v>-50</v>
+      </c>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="43"/>
+      <c r="T39" s="43"/>
+      <c r="U39" s="43"/>
+      <c r="V39" s="43"/>
+      <c r="W39" s="43"/>
+      <c r="X39" s="43"/>
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="23"/>
+      <c r="AB39" s="27"/>
+      <c r="AC39" s="27"/>
+      <c r="AD39" s="26"/>
+      <c r="AE39" s="26"/>
+      <c r="AF39" s="27"/>
+      <c r="AG39" s="27"/>
+      <c r="AH39" s="27"/>
+    </row>
+    <row r="40" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="42"/>
+      <c r="B40" s="42"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="J40" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="K40" s="43"/>
+      <c r="L40" s="43">
+        <v>48</v>
+      </c>
+      <c r="M40" s="43">
+        <v>8</v>
+      </c>
+      <c r="N40" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="O40" s="43">
+        <v>0.1</v>
+      </c>
+      <c r="P40" s="43">
+        <v>-100.5</v>
+      </c>
+      <c r="Q40" s="43"/>
+      <c r="R40" s="43"/>
+      <c r="S40" s="43"/>
+      <c r="T40" s="43"/>
+      <c r="U40" s="43"/>
+      <c r="V40" s="43"/>
+      <c r="W40" s="43"/>
+      <c r="X40" s="43"/>
+      <c r="Y40" s="42"/>
+      <c r="Z40" s="42"/>
+      <c r="AA40" s="23"/>
+      <c r="AB40" s="27"/>
+      <c r="AC40" s="27"/>
+      <c r="AD40" s="26"/>
+      <c r="AE40" s="26"/>
+      <c r="AF40" s="27"/>
+      <c r="AG40" s="27"/>
+      <c r="AH40" s="27"/>
+    </row>
+    <row r="41" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="42"/>
+      <c r="B41" s="42"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="J41" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="K41" s="43"/>
+      <c r="L41" s="43">
+        <v>56</v>
+      </c>
+      <c r="M41" s="43">
+        <v>8</v>
+      </c>
+      <c r="N41" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="O41" s="43">
+        <v>0.1</v>
+      </c>
+      <c r="P41" s="43">
+        <v>100</v>
+      </c>
+      <c r="Q41" s="43"/>
+      <c r="R41" s="43"/>
+      <c r="S41" s="43"/>
+      <c r="T41" s="43"/>
+      <c r="U41" s="43"/>
+      <c r="V41" s="43"/>
+      <c r="W41" s="43"/>
+      <c r="X41" s="43"/>
+      <c r="Y41" s="42"/>
+      <c r="Z41" s="42"/>
+      <c r="AA41" s="23"/>
+      <c r="AB41" s="27"/>
+      <c r="AC41" s="27"/>
+      <c r="AD41" s="26"/>
+      <c r="AE41" s="26"/>
+      <c r="AF41" s="27"/>
+      <c r="AG41" s="27"/>
+      <c r="AH41" s="27"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="44" type="noConversion"/>
   <dataValidations count="10">
@@ -9730,7 +11697,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{00000000-0002-0000-0300-000003000000}">
       <formula1>"Cycle,Event, IfActive,CE,CA"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576 K2:M1048576" xr:uid="{00000000-0002-0000-0300-000004000000}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:M1048576 E2:E1048576" xr:uid="{00000000-0002-0000-0300-000004000000}">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{00000000-0002-0000-0300-000005000000}">
@@ -10054,7 +12021,7 @@
         <v>212</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E5" s="11">
         <v>100</v>
@@ -10198,7 +12165,7 @@
         <v>199</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E8" s="16">
         <v>500</v>

--- a/src/test/resources/Excel/DBC模版.xlsx
+++ b/src/test/resources/Excel/DBC模版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_USER\SLC\Code\IDEA_Project\smart-dbc\src\test\resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65300DA2-0418-40B7-9F8B-41182A0A8CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF74DEF-D1BA-4A85-BB53-62D269395DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="476" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20085" yWindow="2865" windowWidth="18300" windowHeight="17385" tabRatio="476" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CanProtocol_Info" sheetId="7" r:id="rId1"/>
@@ -2585,15 +2585,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="240">
   <si>
     <t>测试协议</t>
   </si>
   <si>
     <t>DBC英文名</t>
-  </si>
-  <si>
-    <t>DBC描述</t>
   </si>
   <si>
     <t>DBC页面名称</t>
@@ -3353,6 +3350,38 @@
   <si>
     <t>SignalMaxValuePhys
 物理最大值(非必填)17</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>DBC描述</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点列表</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCS</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCS, GW</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>波特率（单位：Kbps）</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>DBC版本</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.0.0</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.0.1</t>
     <phoneticPr fontId="44" type="noConversion"/>
   </si>
 </sst>
@@ -3363,7 +3392,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$¥-804]#,##0.0000000000000;[$¥-804]\-#,##0.0000000000000"/>
   </numFmts>
-  <fonts count="48" x14ac:knownFonts="1">
+  <fonts count="49" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3677,6 +3706,14 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -3794,7 +3831,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -3910,6 +3947,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -4011,7 +4063,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4145,6 +4197,20 @@
     </xf>
     <xf numFmtId="0" fontId="47" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="38">
@@ -4472,15 +4538,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1" s="51" t="s">
         <v>215</v>
-      </c>
-      <c r="B1" s="51" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
@@ -4494,45 +4560,74 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.25" customWidth="1"/>
-    <col min="2" max="2" width="14.875" customWidth="1"/>
-    <col min="3" max="3" width="12.625" customWidth="1"/>
+    <col min="1" max="2" width="13.25" customWidth="1"/>
+    <col min="3" max="3" width="14.875" customWidth="1"/>
+    <col min="4" max="4" width="12.625" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="25.625" style="57" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="59" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1" s="59" t="s">
+        <v>232</v>
+      </c>
+      <c r="D1" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" s="59" t="s">
+        <v>233</v>
+      </c>
+      <c r="F1" s="60" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="58" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="B2" s="59" t="s">
+        <v>238</v>
+      </c>
+      <c r="C2" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>235</v>
+      </c>
+      <c r="F2" s="61">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="B3" s="59" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
+      <c r="D3" s="58" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="59" t="s">
+        <v>235</v>
+      </c>
+      <c r="F3" s="61">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -4578,120 +4673,120 @@
   <sheetData>
     <row r="1" spans="1:34" s="23" customFormat="1" ht="143.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="D1" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="E1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="F1" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="28" t="s">
-        <v>13</v>
-      </c>
       <c r="G1" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="H1" s="52" t="s">
         <v>223</v>
       </c>
-      <c r="H1" s="52" t="s">
+      <c r="I1" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="52" t="s">
+        <v>218</v>
+      </c>
+      <c r="O1" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q1" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="R1" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" s="52" t="s">
+        <v>219</v>
+      </c>
+      <c r="T1" s="52" t="s">
+        <v>220</v>
+      </c>
+      <c r="U1" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="W1" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="X1" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y1" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z1" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA1" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC1" s="52" t="s">
         <v>224</v>
       </c>
-      <c r="I1" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="52" t="s">
-        <v>218</v>
-      </c>
-      <c r="K1" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="52" t="s">
-        <v>219</v>
-      </c>
-      <c r="O1" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="P1" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q1" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="R1" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="S1" s="52" t="s">
-        <v>220</v>
-      </c>
-      <c r="T1" s="52" t="s">
-        <v>221</v>
-      </c>
-      <c r="U1" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="V1" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="W1" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="X1" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y1" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z1" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA1" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB1" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC1" s="52" t="s">
-        <v>225</v>
-      </c>
       <c r="AD1" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="AE1" s="49" t="s">
+      <c r="AF1" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="AF1" s="49" t="s">
+      <c r="AG1" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="AG1" s="34" t="s">
+      <c r="AH1" s="34" t="s">
         <v>40</v>
-      </c>
-      <c r="AH1" s="34" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="23" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="C2" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="D2" s="31" t="s">
         <v>44</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>45</v>
       </c>
       <c r="E2" s="31">
         <v>100</v>
@@ -4700,10 +4795,10 @@
         <v>8</v>
       </c>
       <c r="G2" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="31" t="s">
         <v>46</v>
-      </c>
-      <c r="H2" s="31" t="s">
-        <v>47</v>
       </c>
       <c r="I2" s="31"/>
       <c r="J2" s="31"/>
@@ -4723,21 +4818,21 @@
       <c r="X2" s="31"/>
       <c r="Y2" s="31"/>
       <c r="Z2" s="31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA2" s="31"/>
       <c r="AB2" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AC2" s="31"/>
       <c r="AD2" s="34"/>
       <c r="AE2" s="34"/>
       <c r="AF2" s="34"/>
       <c r="AG2" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH2" s="34" t="s">
         <v>50</v>
-      </c>
-      <c r="AH2" s="34" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:34" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -4748,28 +4843,28 @@
       <c r="E3" s="34"/>
       <c r="F3" s="33"/>
       <c r="G3" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="I3" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="I3" s="44" t="s">
+      <c r="J3" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="J3" s="44" t="s">
+      <c r="K3" s="45">
+        <v>0</v>
+      </c>
+      <c r="L3" s="45">
+        <v>0</v>
+      </c>
+      <c r="M3" s="45">
+        <v>8</v>
+      </c>
+      <c r="N3" s="46" t="s">
         <v>55</v>
-      </c>
-      <c r="K3" s="45">
-        <v>0</v>
-      </c>
-      <c r="L3" s="45">
-        <v>0</v>
-      </c>
-      <c r="M3" s="45">
-        <v>8</v>
-      </c>
-      <c r="N3" s="46" t="s">
-        <v>56</v>
       </c>
       <c r="O3" s="45">
         <v>1</v>
@@ -4798,10 +4893,10 @@
       <c r="W3" s="34"/>
       <c r="X3" s="34"/>
       <c r="Y3" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z3" s="33" t="s">
         <v>57</v>
-      </c>
-      <c r="Z3" s="33" t="s">
-        <v>58</v>
       </c>
       <c r="AA3" s="34"/>
       <c r="AB3" s="33"/>
@@ -4820,16 +4915,16 @@
       <c r="E4" s="34"/>
       <c r="F4" s="33"/>
       <c r="G4" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="36" t="s">
-        <v>60</v>
-      </c>
       <c r="I4" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="44" t="s">
         <v>54</v>
-      </c>
-      <c r="J4" s="44" t="s">
-        <v>55</v>
       </c>
       <c r="K4" s="34">
         <v>1</v>
@@ -4841,7 +4936,7 @@
         <v>2</v>
       </c>
       <c r="N4" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O4" s="45">
         <v>1</v>
@@ -4872,10 +4967,10 @@
       </c>
       <c r="X4" s="34"/>
       <c r="Y4" s="36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Z4" s="33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AA4" s="34"/>
       <c r="AB4" s="33"/>
@@ -4894,16 +4989,16 @@
       <c r="E5" s="34"/>
       <c r="F5" s="33"/>
       <c r="G5" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="H5" s="33" t="s">
-        <v>63</v>
-      </c>
       <c r="I5" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="44" t="s">
         <v>54</v>
-      </c>
-      <c r="J5" s="44" t="s">
-        <v>55</v>
       </c>
       <c r="K5" s="34">
         <v>2</v>
@@ -4915,7 +5010,7 @@
         <v>4</v>
       </c>
       <c r="N5" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O5" s="45">
         <v>1</v>
@@ -4946,10 +5041,10 @@
       </c>
       <c r="X5" s="34"/>
       <c r="Y5" s="36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Z5" s="33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AA5" s="34"/>
       <c r="AB5" s="33"/>
@@ -4968,16 +5063,16 @@
       <c r="E6" s="34"/>
       <c r="F6" s="33"/>
       <c r="G6" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="36" t="s">
-        <v>66</v>
-      </c>
       <c r="I6" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="44" t="s">
         <v>54</v>
-      </c>
-      <c r="J6" s="44" t="s">
-        <v>55</v>
       </c>
       <c r="K6" s="34">
         <v>2</v>
@@ -4989,7 +5084,7 @@
         <v>4</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O6" s="45">
         <v>1</v>
@@ -5020,10 +5115,10 @@
       </c>
       <c r="X6" s="34"/>
       <c r="Y6" s="36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AA6" s="34"/>
       <c r="AB6" s="33"/>
@@ -5042,16 +5137,16 @@
       <c r="E7" s="34"/>
       <c r="F7" s="33"/>
       <c r="G7" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="H7" s="36" t="s">
-        <v>69</v>
-      </c>
       <c r="I7" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="44" t="s">
         <v>54</v>
-      </c>
-      <c r="J7" s="44" t="s">
-        <v>55</v>
       </c>
       <c r="K7" s="34"/>
       <c r="L7" s="34">
@@ -5061,7 +5156,7 @@
         <v>8</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O7" s="45">
         <v>1</v>
@@ -5090,16 +5185,16 @@
     </row>
     <row r="8" spans="1:34" s="24" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="C8" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="D8" s="37" t="s">
         <v>72</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>73</v>
       </c>
       <c r="E8" s="37">
         <v>100</v>
@@ -5108,10 +5203,10 @@
         <v>8</v>
       </c>
       <c r="G8" s="37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I8" s="37"/>
       <c r="J8" s="47"/>
@@ -5133,17 +5228,17 @@
       <c r="Z8" s="37"/>
       <c r="AA8" s="37"/>
       <c r="AB8" s="37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AC8" s="47"/>
       <c r="AD8" s="34"/>
       <c r="AE8" s="34"/>
       <c r="AF8" s="50"/>
       <c r="AG8" s="50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AH8" s="50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -5154,16 +5249,16 @@
       <c r="E9" s="34"/>
       <c r="F9" s="33"/>
       <c r="G9" s="33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H9" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="I9" s="44" t="s">
-        <v>54</v>
-      </c>
       <c r="J9" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K9" s="45">
         <v>0</v>
@@ -5175,7 +5270,7 @@
         <v>8</v>
       </c>
       <c r="N9" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O9" s="45">
         <v>1</v>
@@ -5204,7 +5299,7 @@
       <c r="W9" s="34"/>
       <c r="X9" s="34"/>
       <c r="Y9" s="33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z9" s="33"/>
       <c r="AA9" s="34"/>
@@ -5224,16 +5319,16 @@
       <c r="E10" s="34"/>
       <c r="F10" s="33"/>
       <c r="G10" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="H10" s="36" t="s">
-        <v>77</v>
-      </c>
       <c r="I10" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J10" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K10" s="34">
         <v>1</v>
@@ -5246,7 +5341,7 @@
         <v>8</v>
       </c>
       <c r="N10" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O10" s="45">
         <v>1</v>
@@ -5293,16 +5388,16 @@
       <c r="E11" s="34"/>
       <c r="F11" s="33"/>
       <c r="G11" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="H11" s="36" t="s">
-        <v>79</v>
-      </c>
       <c r="I11" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K11" s="34">
         <v>2</v>
@@ -5315,7 +5410,7 @@
         <v>4</v>
       </c>
       <c r="N11" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O11" s="45">
         <v>1</v>
@@ -5344,7 +5439,7 @@
       <c r="W11" s="34"/>
       <c r="X11" s="34"/>
       <c r="Y11" s="36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z11" s="36"/>
       <c r="AA11" s="34"/>
@@ -5364,16 +5459,16 @@
       <c r="E12" s="34"/>
       <c r="F12" s="33"/>
       <c r="G12" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="H12" s="36" t="s">
-        <v>82</v>
-      </c>
       <c r="I12" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K12" s="34">
         <v>2</v>
@@ -5385,7 +5480,7 @@
         <v>4</v>
       </c>
       <c r="N12" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O12" s="45">
         <v>1</v>
@@ -5413,10 +5508,10 @@
       </c>
       <c r="W12" s="34"/>
       <c r="X12" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y12" s="36" t="s">
         <v>83</v>
-      </c>
-      <c r="Y12" s="36" t="s">
-        <v>84</v>
       </c>
       <c r="Z12" s="36"/>
       <c r="AA12" s="34"/>
@@ -5436,16 +5531,16 @@
       <c r="E13" s="34"/>
       <c r="F13" s="33"/>
       <c r="G13" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="H13" s="36" t="s">
-        <v>86</v>
-      </c>
       <c r="I13" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K13" s="34">
         <v>3</v>
@@ -5457,7 +5552,7 @@
         <v>2</v>
       </c>
       <c r="N13" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O13" s="45">
         <v>1</v>
@@ -5486,7 +5581,7 @@
       <c r="W13" s="34"/>
       <c r="X13" s="34"/>
       <c r="Y13" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z13" s="36"/>
       <c r="AA13" s="34"/>
@@ -5506,16 +5601,16 @@
       <c r="E14" s="34"/>
       <c r="F14" s="33"/>
       <c r="G14" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="H14" s="36" t="s">
-        <v>89</v>
-      </c>
       <c r="I14" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K14" s="34">
         <v>3</v>
@@ -5527,7 +5622,7 @@
         <v>2</v>
       </c>
       <c r="N14" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O14" s="45">
         <v>1</v>
@@ -5556,7 +5651,7 @@
       <c r="W14" s="34"/>
       <c r="X14" s="34"/>
       <c r="Y14" s="36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Z14" s="36"/>
       <c r="AA14" s="34"/>
@@ -5576,16 +5671,16 @@
       <c r="E15" s="34"/>
       <c r="F15" s="33"/>
       <c r="G15" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="H15" s="36" t="s">
-        <v>92</v>
-      </c>
       <c r="I15" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K15" s="34">
         <v>3</v>
@@ -5597,7 +5692,7 @@
         <v>2</v>
       </c>
       <c r="N15" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O15" s="45">
         <v>1</v>
@@ -5620,7 +5715,7 @@
       <c r="W15" s="34"/>
       <c r="X15" s="34"/>
       <c r="Y15" s="36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Z15" s="36"/>
       <c r="AA15" s="34"/>
@@ -5640,16 +5735,16 @@
       <c r="E16" s="34"/>
       <c r="F16" s="33"/>
       <c r="G16" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="H16" s="38" t="s">
-        <v>95</v>
-      </c>
       <c r="I16" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K16" s="34">
         <v>7</v>
@@ -5661,7 +5756,7 @@
         <v>8</v>
       </c>
       <c r="N16" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O16" s="45">
         <v>1</v>
@@ -5690,7 +5785,7 @@
       <c r="W16" s="34"/>
       <c r="X16" s="34"/>
       <c r="Y16" s="36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Z16" s="36"/>
       <c r="AA16" s="34"/>
@@ -5704,16 +5799,16 @@
     </row>
     <row r="17" spans="1:34" s="25" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="B17" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>98</v>
-      </c>
       <c r="D17" s="39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E17" s="39">
         <v>50</v>
@@ -5723,7 +5818,7 @@
       </c>
       <c r="G17" s="39"/>
       <c r="H17" s="39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I17" s="39"/>
       <c r="J17" s="39"/>
@@ -5745,7 +5840,7 @@
       <c r="Z17" s="39"/>
       <c r="AA17" s="39"/>
       <c r="AB17" s="39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AC17" s="39"/>
       <c r="AD17" s="34"/>
@@ -5756,7 +5851,7 @@
     </row>
     <row r="18" spans="1:34" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A18" s="33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
@@ -5764,16 +5859,16 @@
       <c r="E18" s="34"/>
       <c r="F18" s="33"/>
       <c r="G18" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="H18" s="38" t="s">
+      <c r="I18" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I18" s="44" t="s">
-        <v>103</v>
-      </c>
       <c r="J18" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K18" s="33"/>
       <c r="L18" s="34">
@@ -5783,7 +5878,7 @@
         <v>8</v>
       </c>
       <c r="N18" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O18" s="34">
         <v>1</v>
@@ -5812,7 +5907,7 @@
     </row>
     <row r="19" spans="1:34" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A19" s="33" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B19" s="33"/>
       <c r="C19" s="33"/>
@@ -5820,14 +5915,14 @@
       <c r="E19" s="34"/>
       <c r="F19" s="33"/>
       <c r="G19" s="33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H19" s="33"/>
       <c r="I19" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J19" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K19" s="33"/>
       <c r="L19" s="34">
@@ -5837,7 +5932,7 @@
         <v>8</v>
       </c>
       <c r="N19" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O19" s="34">
         <v>1</v>
@@ -5866,7 +5961,7 @@
     </row>
     <row r="20" spans="1:34" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A20" s="33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B20" s="33"/>
       <c r="C20" s="33"/>
@@ -5874,14 +5969,14 @@
       <c r="E20" s="34"/>
       <c r="F20" s="33"/>
       <c r="G20" s="33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H20" s="33"/>
       <c r="I20" s="44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J20" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K20" s="33"/>
       <c r="L20" s="34">
@@ -5891,7 +5986,7 @@
         <v>8</v>
       </c>
       <c r="N20" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O20" s="34">
         <v>1</v>
@@ -5922,30 +6017,30 @@
       <c r="A21" s="33"/>
       <c r="B21" s="33"/>
       <c r="C21" s="33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D21" s="33"/>
       <c r="E21" s="34"/>
       <c r="F21" s="33"/>
       <c r="G21" s="33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H21" s="33"/>
       <c r="I21" s="44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J21" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K21" s="33"/>
       <c r="L21" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M21" s="34">
         <v>4</v>
       </c>
       <c r="N21" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O21" s="34">
         <v>1</v>
@@ -5980,24 +6075,24 @@
       <c r="E22" s="34"/>
       <c r="F22" s="33"/>
       <c r="G22" s="33" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H22" s="33"/>
       <c r="I22" s="44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K22" s="33"/>
       <c r="L22" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="M22" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="M22" s="48" t="s">
-        <v>113</v>
-      </c>
       <c r="N22" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O22" s="34">
         <v>1</v>
@@ -6032,16 +6127,16 @@
       <c r="E23" s="34"/>
       <c r="F23" s="33"/>
       <c r="G23" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="H23" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="H23" s="38" t="s">
-        <v>115</v>
-      </c>
       <c r="I23" s="44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J23" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K23" s="34"/>
       <c r="L23" s="48">
@@ -6051,7 +6146,7 @@
         <v>16</v>
       </c>
       <c r="N23" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O23" s="34">
         <v>1</v>
@@ -6080,16 +6175,16 @@
     </row>
     <row r="24" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="B24" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="40" t="s">
-        <v>117</v>
-      </c>
       <c r="D24" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E24" s="41">
         <v>200</v>
@@ -6126,14 +6221,14 @@
       <c r="E25" s="43"/>
       <c r="F25" s="42"/>
       <c r="G25" s="42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H25" s="42"/>
       <c r="I25" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J25" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K25" s="43"/>
       <c r="L25" s="43">
@@ -6143,7 +6238,7 @@
         <v>8</v>
       </c>
       <c r="N25" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O25" s="43">
         <v>1</v>
@@ -6170,14 +6265,14 @@
       <c r="E26" s="43"/>
       <c r="F26" s="42"/>
       <c r="G26" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H26" s="42"/>
       <c r="I26" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J26" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K26" s="43"/>
       <c r="L26" s="43">
@@ -6187,7 +6282,7 @@
         <v>8</v>
       </c>
       <c r="N26" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O26" s="43">
         <v>1</v>
@@ -6214,14 +6309,14 @@
       <c r="E27" s="43"/>
       <c r="F27" s="42"/>
       <c r="G27" s="42" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H27" s="42"/>
       <c r="I27" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J27" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K27" s="43"/>
       <c r="L27" s="43">
@@ -6231,7 +6326,7 @@
         <v>8</v>
       </c>
       <c r="N27" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O27" s="43">
         <v>1</v>
@@ -6258,14 +6353,14 @@
       <c r="E28" s="43"/>
       <c r="F28" s="42"/>
       <c r="G28" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H28" s="42"/>
       <c r="I28" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J28" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K28" s="43"/>
       <c r="L28" s="43">
@@ -6275,7 +6370,7 @@
         <v>8</v>
       </c>
       <c r="N28" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O28" s="43">
         <v>1</v>
@@ -6302,14 +6397,14 @@
       <c r="E29" s="43"/>
       <c r="F29" s="42"/>
       <c r="G29" s="42" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H29" s="42"/>
       <c r="I29" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J29" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K29" s="43"/>
       <c r="L29" s="43">
@@ -6319,7 +6414,7 @@
         <v>8</v>
       </c>
       <c r="N29" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O29" s="43">
         <v>0.2</v>
@@ -6346,14 +6441,14 @@
       <c r="E30" s="43"/>
       <c r="F30" s="42"/>
       <c r="G30" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H30" s="42"/>
       <c r="I30" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J30" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K30" s="43"/>
       <c r="L30" s="43">
@@ -6363,7 +6458,7 @@
         <v>8</v>
       </c>
       <c r="N30" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O30" s="43">
         <v>0.5</v>
@@ -6390,14 +6485,14 @@
       <c r="E31" s="43"/>
       <c r="F31" s="42"/>
       <c r="G31" s="42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H31" s="42"/>
       <c r="I31" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J31" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K31" s="43"/>
       <c r="L31" s="43">
@@ -6407,7 +6502,7 @@
         <v>8</v>
       </c>
       <c r="N31" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O31" s="43">
         <v>0.1</v>
@@ -6434,14 +6529,14 @@
       <c r="E32" s="43"/>
       <c r="F32" s="42"/>
       <c r="G32" s="42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H32" s="42"/>
       <c r="I32" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J32" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K32" s="43"/>
       <c r="L32" s="43">
@@ -6451,7 +6546,7 @@
         <v>8</v>
       </c>
       <c r="N32" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O32" s="43">
         <v>0.1</v>
@@ -6472,16 +6567,16 @@
     </row>
     <row r="33" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>127</v>
-      </c>
       <c r="D33" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E33" s="41">
         <v>200</v>
@@ -6518,14 +6613,14 @@
       <c r="E34" s="43"/>
       <c r="F34" s="42"/>
       <c r="G34" s="42" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H34" s="42"/>
       <c r="I34" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J34" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K34" s="43"/>
       <c r="L34" s="43">
@@ -6535,7 +6630,7 @@
         <v>8</v>
       </c>
       <c r="N34" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O34" s="43">
         <v>1</v>
@@ -6562,14 +6657,14 @@
       <c r="E35" s="43"/>
       <c r="F35" s="42"/>
       <c r="G35" s="42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H35" s="42"/>
       <c r="I35" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J35" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K35" s="43"/>
       <c r="L35" s="43">
@@ -6579,7 +6674,7 @@
         <v>8</v>
       </c>
       <c r="N35" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O35" s="43">
         <v>1</v>
@@ -6606,14 +6701,14 @@
       <c r="E36" s="43"/>
       <c r="F36" s="42"/>
       <c r="G36" s="42" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H36" s="42"/>
       <c r="I36" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J36" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K36" s="43"/>
       <c r="L36" s="43">
@@ -6623,7 +6718,7 @@
         <v>8</v>
       </c>
       <c r="N36" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O36" s="43">
         <v>1</v>
@@ -6650,14 +6745,14 @@
       <c r="E37" s="43"/>
       <c r="F37" s="42"/>
       <c r="G37" s="42" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H37" s="42"/>
       <c r="I37" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J37" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K37" s="43"/>
       <c r="L37" s="43">
@@ -6667,7 +6762,7 @@
         <v>8</v>
       </c>
       <c r="N37" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O37" s="43">
         <v>1</v>
@@ -6694,14 +6789,14 @@
       <c r="E38" s="43"/>
       <c r="F38" s="42"/>
       <c r="G38" s="42" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H38" s="42"/>
       <c r="I38" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J38" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K38" s="43"/>
       <c r="L38" s="43">
@@ -6711,7 +6806,7 @@
         <v>8</v>
       </c>
       <c r="N38" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O38" s="43">
         <v>1</v>
@@ -6738,14 +6833,14 @@
       <c r="E39" s="43"/>
       <c r="F39" s="42"/>
       <c r="G39" s="42" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H39" s="42"/>
       <c r="I39" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J39" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K39" s="43"/>
       <c r="L39" s="43">
@@ -6755,7 +6850,7 @@
         <v>8</v>
       </c>
       <c r="N39" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O39" s="43">
         <v>1</v>
@@ -6782,14 +6877,14 @@
       <c r="E40" s="43"/>
       <c r="F40" s="42"/>
       <c r="G40" s="42" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H40" s="42"/>
       <c r="I40" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J40" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K40" s="43"/>
       <c r="L40" s="43">
@@ -6799,7 +6894,7 @@
         <v>8</v>
       </c>
       <c r="N40" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O40" s="43">
         <v>1</v>
@@ -6826,14 +6921,14 @@
       <c r="E41" s="43"/>
       <c r="F41" s="42"/>
       <c r="G41" s="42" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H41" s="42"/>
       <c r="I41" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J41" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K41" s="43"/>
       <c r="L41" s="43">
@@ -6843,7 +6938,7 @@
         <v>8</v>
       </c>
       <c r="N41" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O41" s="43">
         <v>1</v>
@@ -6864,16 +6959,16 @@
     </row>
     <row r="42" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="B42" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="B42" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="40" t="s">
-        <v>137</v>
-      </c>
       <c r="D42" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E42" s="41">
         <v>200</v>
@@ -6910,14 +7005,14 @@
       <c r="E43" s="43"/>
       <c r="F43" s="42"/>
       <c r="G43" s="42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H43" s="42"/>
       <c r="I43" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J43" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K43" s="43"/>
       <c r="L43" s="43">
@@ -6927,7 +7022,7 @@
         <v>8</v>
       </c>
       <c r="N43" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O43" s="43">
         <v>1</v>
@@ -6954,14 +7049,14 @@
       <c r="E44" s="43"/>
       <c r="F44" s="42"/>
       <c r="G44" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H44" s="42"/>
       <c r="I44" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J44" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K44" s="43"/>
       <c r="L44" s="43">
@@ -6971,7 +7066,7 @@
         <v>8</v>
       </c>
       <c r="N44" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O44" s="43">
         <v>1</v>
@@ -6998,14 +7093,14 @@
       <c r="E45" s="43"/>
       <c r="F45" s="42"/>
       <c r="G45" s="42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H45" s="42"/>
       <c r="I45" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J45" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K45" s="43"/>
       <c r="L45" s="43">
@@ -7015,7 +7110,7 @@
         <v>8</v>
       </c>
       <c r="N45" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O45" s="43">
         <v>1</v>
@@ -7042,14 +7137,14 @@
       <c r="E46" s="43"/>
       <c r="F46" s="42"/>
       <c r="G46" s="42" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H46" s="42"/>
       <c r="I46" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J46" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K46" s="43"/>
       <c r="L46" s="43">
@@ -7059,7 +7154,7 @@
         <v>8</v>
       </c>
       <c r="N46" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O46" s="43">
         <v>1</v>
@@ -7086,14 +7181,14 @@
       <c r="E47" s="43"/>
       <c r="F47" s="42"/>
       <c r="G47" s="42" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H47" s="42"/>
       <c r="I47" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J47" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K47" s="43"/>
       <c r="L47" s="43">
@@ -7103,7 +7198,7 @@
         <v>8</v>
       </c>
       <c r="N47" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O47" s="43">
         <v>0.2</v>
@@ -7130,14 +7225,14 @@
       <c r="E48" s="43"/>
       <c r="F48" s="42"/>
       <c r="G48" s="42" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H48" s="42"/>
       <c r="I48" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J48" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K48" s="43"/>
       <c r="L48" s="43">
@@ -7147,7 +7242,7 @@
         <v>8</v>
       </c>
       <c r="N48" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O48" s="43">
         <v>0.5</v>
@@ -7174,14 +7269,14 @@
       <c r="E49" s="43"/>
       <c r="F49" s="42"/>
       <c r="G49" s="42" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H49" s="42"/>
       <c r="I49" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J49" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K49" s="43"/>
       <c r="L49" s="43">
@@ -7191,7 +7286,7 @@
         <v>8</v>
       </c>
       <c r="N49" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O49" s="43">
         <v>0.1</v>
@@ -7218,14 +7313,14 @@
       <c r="E50" s="43"/>
       <c r="F50" s="42"/>
       <c r="G50" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H50" s="42"/>
       <c r="I50" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J50" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K50" s="43"/>
       <c r="L50" s="43">
@@ -7235,7 +7330,7 @@
         <v>8</v>
       </c>
       <c r="N50" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O50" s="43">
         <v>0.1</v>
@@ -7256,16 +7351,16 @@
     </row>
     <row r="51" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="B51" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="B51" s="39" t="s">
+      <c r="C51" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="C51" s="40" t="s">
-        <v>148</v>
-      </c>
       <c r="D51" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E51" s="41">
         <v>200</v>
@@ -7302,14 +7397,14 @@
       <c r="E52" s="43"/>
       <c r="F52" s="42"/>
       <c r="G52" s="42" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H52" s="42"/>
       <c r="I52" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J52" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K52" s="43"/>
       <c r="L52" s="43">
@@ -7319,7 +7414,7 @@
         <v>8</v>
       </c>
       <c r="N52" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O52" s="43">
         <v>1</v>
@@ -7346,14 +7441,14 @@
       <c r="E53" s="43"/>
       <c r="F53" s="42"/>
       <c r="G53" s="42" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H53" s="42"/>
       <c r="I53" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J53" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K53" s="43"/>
       <c r="L53" s="43">
@@ -7363,7 +7458,7 @@
         <v>8</v>
       </c>
       <c r="N53" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O53" s="43">
         <v>1</v>
@@ -7390,14 +7485,14 @@
       <c r="E54" s="43"/>
       <c r="F54" s="42"/>
       <c r="G54" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H54" s="42"/>
       <c r="I54" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J54" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K54" s="43"/>
       <c r="L54" s="43">
@@ -7407,7 +7502,7 @@
         <v>8</v>
       </c>
       <c r="N54" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O54" s="43">
         <v>1</v>
@@ -7434,14 +7529,14 @@
       <c r="E55" s="43"/>
       <c r="F55" s="42"/>
       <c r="G55" s="42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H55" s="42"/>
       <c r="I55" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J55" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K55" s="43"/>
       <c r="L55" s="43">
@@ -7451,7 +7546,7 @@
         <v>8</v>
       </c>
       <c r="N55" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O55" s="43">
         <v>1</v>
@@ -7478,14 +7573,14 @@
       <c r="E56" s="43"/>
       <c r="F56" s="42"/>
       <c r="G56" s="42" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H56" s="42"/>
       <c r="I56" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J56" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K56" s="43"/>
       <c r="L56" s="43">
@@ -7495,7 +7590,7 @@
         <v>8</v>
       </c>
       <c r="N56" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O56" s="43">
         <v>1</v>
@@ -7522,14 +7617,14 @@
       <c r="E57" s="43"/>
       <c r="F57" s="42"/>
       <c r="G57" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H57" s="42"/>
       <c r="I57" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J57" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K57" s="43"/>
       <c r="L57" s="43">
@@ -7539,7 +7634,7 @@
         <v>8</v>
       </c>
       <c r="N57" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O57" s="43">
         <v>1</v>
@@ -7566,14 +7661,14 @@
       <c r="E58" s="43"/>
       <c r="F58" s="42"/>
       <c r="G58" s="42" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H58" s="42"/>
       <c r="I58" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J58" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K58" s="43"/>
       <c r="L58" s="43">
@@ -7583,7 +7678,7 @@
         <v>8</v>
       </c>
       <c r="N58" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O58" s="43">
         <v>1</v>
@@ -7610,14 +7705,14 @@
       <c r="E59" s="43"/>
       <c r="F59" s="42"/>
       <c r="G59" s="42" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H59" s="42"/>
       <c r="I59" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J59" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K59" s="43"/>
       <c r="L59" s="43">
@@ -7627,7 +7722,7 @@
         <v>8</v>
       </c>
       <c r="N59" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O59" s="43">
         <v>1</v>
@@ -7648,16 +7743,16 @@
     </row>
     <row r="60" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="B60" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="C60" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="B60" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="C60" s="40" t="s">
-        <v>158</v>
-      </c>
       <c r="D60" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E60" s="41">
         <v>200</v>
@@ -7694,14 +7789,14 @@
       <c r="E61" s="43"/>
       <c r="F61" s="42"/>
       <c r="G61" s="42" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H61" s="42"/>
       <c r="I61" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J61" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K61" s="43"/>
       <c r="L61" s="43">
@@ -7711,7 +7806,7 @@
         <v>8</v>
       </c>
       <c r="N61" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O61" s="43">
         <v>1</v>
@@ -7738,14 +7833,14 @@
       <c r="E62" s="43"/>
       <c r="F62" s="42"/>
       <c r="G62" s="42" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H62" s="42"/>
       <c r="I62" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J62" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K62" s="43"/>
       <c r="L62" s="43">
@@ -7755,7 +7850,7 @@
         <v>8</v>
       </c>
       <c r="N62" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O62" s="43">
         <v>1</v>
@@ -7782,14 +7877,14 @@
       <c r="E63" s="43"/>
       <c r="F63" s="42"/>
       <c r="G63" s="42" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H63" s="42"/>
       <c r="I63" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J63" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K63" s="43"/>
       <c r="L63" s="43">
@@ -7799,7 +7894,7 @@
         <v>8</v>
       </c>
       <c r="N63" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O63" s="43">
         <v>1</v>
@@ -7826,14 +7921,14 @@
       <c r="E64" s="43"/>
       <c r="F64" s="42"/>
       <c r="G64" s="42" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H64" s="42"/>
       <c r="I64" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J64" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K64" s="43"/>
       <c r="L64" s="43">
@@ -7843,7 +7938,7 @@
         <v>8</v>
       </c>
       <c r="N64" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O64" s="43">
         <v>1</v>
@@ -7870,14 +7965,14 @@
       <c r="E65" s="43"/>
       <c r="F65" s="42"/>
       <c r="G65" s="42" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H65" s="42"/>
       <c r="I65" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J65" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K65" s="43"/>
       <c r="L65" s="43">
@@ -7887,7 +7982,7 @@
         <v>8</v>
       </c>
       <c r="N65" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O65" s="43">
         <v>0.1</v>
@@ -7914,14 +8009,14 @@
       <c r="E66" s="43"/>
       <c r="F66" s="42"/>
       <c r="G66" s="42" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H66" s="42"/>
       <c r="I66" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J66" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K66" s="43"/>
       <c r="L66" s="43">
@@ -7931,7 +8026,7 @@
         <v>8</v>
       </c>
       <c r="N66" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O66" s="43">
         <v>0.5</v>
@@ -7958,14 +8053,14 @@
       <c r="E67" s="43"/>
       <c r="F67" s="42"/>
       <c r="G67" s="42" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H67" s="42"/>
       <c r="I67" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J67" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K67" s="43"/>
       <c r="L67" s="43">
@@ -7975,7 +8070,7 @@
         <v>8</v>
       </c>
       <c r="N67" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O67" s="43">
         <v>0.1</v>
@@ -8002,14 +8097,14 @@
       <c r="E68" s="43"/>
       <c r="F68" s="42"/>
       <c r="G68" s="42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H68" s="42"/>
       <c r="I68" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J68" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K68" s="43"/>
       <c r="L68" s="43">
@@ -8019,7 +8114,7 @@
         <v>8</v>
       </c>
       <c r="N68" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O68" s="43">
         <v>0.1</v>
@@ -8040,16 +8135,16 @@
     </row>
     <row r="69" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="B69" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="B69" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="C69" s="40" t="s">
-        <v>168</v>
-      </c>
       <c r="D69" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E69" s="41">
         <v>200</v>
@@ -8086,14 +8181,14 @@
       <c r="E70" s="43"/>
       <c r="F70" s="42"/>
       <c r="G70" s="42" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H70" s="42"/>
       <c r="I70" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J70" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K70" s="43"/>
       <c r="L70" s="43">
@@ -8103,7 +8198,7 @@
         <v>8</v>
       </c>
       <c r="N70" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O70" s="43">
         <v>1</v>
@@ -8130,14 +8225,14 @@
       <c r="E71" s="43"/>
       <c r="F71" s="42"/>
       <c r="G71" s="42" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H71" s="42"/>
       <c r="I71" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J71" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K71" s="43"/>
       <c r="L71" s="43">
@@ -8147,7 +8242,7 @@
         <v>8</v>
       </c>
       <c r="N71" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O71" s="43">
         <v>1</v>
@@ -8174,14 +8269,14 @@
       <c r="E72" s="43"/>
       <c r="F72" s="42"/>
       <c r="G72" s="42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H72" s="42"/>
       <c r="I72" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J72" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K72" s="43"/>
       <c r="L72" s="43">
@@ -8191,7 +8286,7 @@
         <v>8</v>
       </c>
       <c r="N72" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O72" s="43">
         <v>1</v>
@@ -8218,14 +8313,14 @@
       <c r="E73" s="43"/>
       <c r="F73" s="42"/>
       <c r="G73" s="42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H73" s="42"/>
       <c r="I73" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J73" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K73" s="43"/>
       <c r="L73" s="43">
@@ -8235,7 +8330,7 @@
         <v>8</v>
       </c>
       <c r="N73" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O73" s="43">
         <v>1</v>
@@ -8262,14 +8357,14 @@
       <c r="E74" s="43"/>
       <c r="F74" s="42"/>
       <c r="G74" s="42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H74" s="42"/>
       <c r="I74" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J74" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K74" s="43"/>
       <c r="L74" s="43">
@@ -8279,7 +8374,7 @@
         <v>8</v>
       </c>
       <c r="N74" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O74" s="43">
         <v>1</v>
@@ -8306,14 +8401,14 @@
       <c r="E75" s="43"/>
       <c r="F75" s="42"/>
       <c r="G75" s="42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H75" s="42"/>
       <c r="I75" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J75" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K75" s="43"/>
       <c r="L75" s="43">
@@ -8323,7 +8418,7 @@
         <v>8</v>
       </c>
       <c r="N75" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O75" s="43">
         <v>1</v>
@@ -8350,14 +8445,14 @@
       <c r="E76" s="43"/>
       <c r="F76" s="42"/>
       <c r="G76" s="42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H76" s="42"/>
       <c r="I76" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J76" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K76" s="43"/>
       <c r="L76" s="43">
@@ -8367,7 +8462,7 @@
         <v>8</v>
       </c>
       <c r="N76" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O76" s="43">
         <v>1</v>
@@ -8394,14 +8489,14 @@
       <c r="E77" s="43"/>
       <c r="F77" s="42"/>
       <c r="G77" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H77" s="42"/>
       <c r="I77" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J77" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K77" s="43"/>
       <c r="L77" s="43">
@@ -8411,7 +8506,7 @@
         <v>8</v>
       </c>
       <c r="N77" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O77" s="43">
         <v>1</v>
@@ -8432,16 +8527,16 @@
     </row>
     <row r="78" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="B78" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="C78" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="B78" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="C78" s="40" t="s">
-        <v>178</v>
-      </c>
       <c r="D78" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E78" s="41">
         <v>200</v>
@@ -8478,14 +8573,14 @@
       <c r="E79" s="43"/>
       <c r="F79" s="42"/>
       <c r="G79" s="42" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H79" s="42"/>
       <c r="I79" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J79" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K79" s="43"/>
       <c r="L79" s="43">
@@ -8495,7 +8590,7 @@
         <v>8</v>
       </c>
       <c r="N79" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O79" s="43">
         <v>1</v>
@@ -8522,14 +8617,14 @@
       <c r="E80" s="43"/>
       <c r="F80" s="42"/>
       <c r="G80" s="42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H80" s="42"/>
       <c r="I80" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J80" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K80" s="43"/>
       <c r="L80" s="43">
@@ -8539,7 +8634,7 @@
         <v>8</v>
       </c>
       <c r="N80" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O80" s="43">
         <v>1</v>
@@ -8566,14 +8661,14 @@
       <c r="E81" s="43"/>
       <c r="F81" s="42"/>
       <c r="G81" s="42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H81" s="42"/>
       <c r="I81" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J81" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K81" s="43"/>
       <c r="L81" s="43">
@@ -8583,7 +8678,7 @@
         <v>8</v>
       </c>
       <c r="N81" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O81" s="43">
         <v>1</v>
@@ -8610,14 +8705,14 @@
       <c r="E82" s="43"/>
       <c r="F82" s="42"/>
       <c r="G82" s="42" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H82" s="42"/>
       <c r="I82" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J82" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K82" s="43"/>
       <c r="L82" s="43">
@@ -8627,7 +8722,7 @@
         <v>8</v>
       </c>
       <c r="N82" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O82" s="43">
         <v>1</v>
@@ -8654,14 +8749,14 @@
       <c r="E83" s="43"/>
       <c r="F83" s="42"/>
       <c r="G83" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H83" s="42"/>
       <c r="I83" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J83" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K83" s="43"/>
       <c r="L83" s="43">
@@ -8671,7 +8766,7 @@
         <v>8</v>
       </c>
       <c r="N83" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O83" s="43">
         <v>0.2</v>
@@ -8698,14 +8793,14 @@
       <c r="E84" s="43"/>
       <c r="F84" s="42"/>
       <c r="G84" s="42" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H84" s="42"/>
       <c r="I84" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J84" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K84" s="43"/>
       <c r="L84" s="43">
@@ -8715,7 +8810,7 @@
         <v>8</v>
       </c>
       <c r="N84" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O84" s="43">
         <v>0.5</v>
@@ -8742,14 +8837,14 @@
       <c r="E85" s="43"/>
       <c r="F85" s="42"/>
       <c r="G85" s="42" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H85" s="42"/>
       <c r="I85" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J85" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K85" s="43"/>
       <c r="L85" s="43">
@@ -8759,7 +8854,7 @@
         <v>8</v>
       </c>
       <c r="N85" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O85" s="43">
         <v>0.1</v>
@@ -8786,14 +8881,14 @@
       <c r="E86" s="43"/>
       <c r="F86" s="42"/>
       <c r="G86" s="42" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H86" s="42"/>
       <c r="I86" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J86" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K86" s="43"/>
       <c r="L86" s="43">
@@ -8803,7 +8898,7 @@
         <v>8</v>
       </c>
       <c r="N86" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O86" s="43">
         <v>0.1</v>
@@ -8824,16 +8919,16 @@
     </row>
     <row r="87" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="B87" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="C87" s="40" t="s">
         <v>187</v>
       </c>
-      <c r="B87" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="C87" s="40" t="s">
-        <v>188</v>
-      </c>
       <c r="D87" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E87" s="41">
         <v>200</v>
@@ -8870,14 +8965,14 @@
       <c r="E88" s="43"/>
       <c r="F88" s="42"/>
       <c r="G88" s="42" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H88" s="42"/>
       <c r="I88" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J88" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K88" s="43"/>
       <c r="L88" s="43">
@@ -8887,7 +8982,7 @@
         <v>8</v>
       </c>
       <c r="N88" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O88" s="43">
         <v>1</v>
@@ -8914,14 +9009,14 @@
       <c r="E89" s="43"/>
       <c r="F89" s="42"/>
       <c r="G89" s="42" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H89" s="42"/>
       <c r="I89" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J89" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K89" s="43"/>
       <c r="L89" s="43">
@@ -8931,7 +9026,7 @@
         <v>8</v>
       </c>
       <c r="N89" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O89" s="43">
         <v>1</v>
@@ -8958,14 +9053,14 @@
       <c r="E90" s="43"/>
       <c r="F90" s="42"/>
       <c r="G90" s="42" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H90" s="42"/>
       <c r="I90" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J90" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K90" s="43"/>
       <c r="L90" s="43">
@@ -8975,7 +9070,7 @@
         <v>8</v>
       </c>
       <c r="N90" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O90" s="43">
         <v>1</v>
@@ -9002,14 +9097,14 @@
       <c r="E91" s="43"/>
       <c r="F91" s="42"/>
       <c r="G91" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H91" s="42"/>
       <c r="I91" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J91" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K91" s="43"/>
       <c r="L91" s="43">
@@ -9019,7 +9114,7 @@
         <v>8</v>
       </c>
       <c r="N91" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O91" s="43">
         <v>1</v>
@@ -9046,14 +9141,14 @@
       <c r="E92" s="43"/>
       <c r="F92" s="42"/>
       <c r="G92" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H92" s="42"/>
       <c r="I92" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J92" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K92" s="43"/>
       <c r="L92" s="43">
@@ -9063,7 +9158,7 @@
         <v>8</v>
       </c>
       <c r="N92" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O92" s="43">
         <v>1</v>
@@ -9090,14 +9185,14 @@
       <c r="E93" s="43"/>
       <c r="F93" s="42"/>
       <c r="G93" s="42" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H93" s="42"/>
       <c r="I93" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J93" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K93" s="43"/>
       <c r="L93" s="43">
@@ -9107,7 +9202,7 @@
         <v>8</v>
       </c>
       <c r="N93" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O93" s="43">
         <v>1</v>
@@ -9134,14 +9229,14 @@
       <c r="E94" s="43"/>
       <c r="F94" s="42"/>
       <c r="G94" s="42" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H94" s="42"/>
       <c r="I94" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J94" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K94" s="43"/>
       <c r="L94" s="43">
@@ -9151,7 +9246,7 @@
         <v>8</v>
       </c>
       <c r="N94" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O94" s="43">
         <v>1</v>
@@ -9178,14 +9273,14 @@
       <c r="E95" s="43"/>
       <c r="F95" s="42"/>
       <c r="G95" s="42" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H95" s="42"/>
       <c r="I95" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J95" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K95" s="43"/>
       <c r="L95" s="43">
@@ -9195,7 +9290,7 @@
         <v>8</v>
       </c>
       <c r="N95" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O95" s="43">
         <v>1</v>
@@ -9291,120 +9386,120 @@
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1" ht="88.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>16</v>
-      </c>
       <c r="J1" s="54" t="s">
+        <v>217</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="55" t="s">
+        <v>226</v>
+      </c>
+      <c r="M1" s="55" t="s">
+        <v>227</v>
+      </c>
+      <c r="N1" s="54" t="s">
         <v>218</v>
       </c>
-      <c r="K1" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="55" t="s">
-        <v>227</v>
-      </c>
-      <c r="M1" s="55" t="s">
+      <c r="O1" s="55" t="s">
         <v>228</v>
       </c>
-      <c r="N1" s="54" t="s">
+      <c r="P1" s="55" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q1" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="R1" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="S1" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="O1" s="55" t="s">
-        <v>229</v>
-      </c>
-      <c r="P1" s="55" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q1" s="54" t="s">
-        <v>231</v>
-      </c>
-      <c r="R1" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="S1" s="54" t="s">
-        <v>220</v>
-      </c>
       <c r="T1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Z1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="AA1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AB1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AB1" s="8" t="s">
+      <c r="AC1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AC1" s="8" t="s">
+      <c r="AD1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="AD1" s="17" t="s">
+      <c r="AE1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="AE1" s="17" t="s">
+      <c r="AF1" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="AF1" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG1" s="21" t="s">
-        <v>40</v>
+      <c r="AG1" s="56" t="s">
+        <v>234</v>
       </c>
       <c r="AH1" s="21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="2" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>199</v>
-      </c>
       <c r="D2" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E2" s="11">
         <v>100</v>
@@ -9439,10 +9534,10 @@
       <c r="AE2" s="10"/>
       <c r="AF2" s="10"/>
       <c r="AG2" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH2" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="AH2" s="10" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -9453,11 +9548,11 @@
       <c r="E3" s="13"/>
       <c r="F3" s="12"/>
       <c r="G3" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J3" s="12"/>
       <c r="K3" s="13"/>
@@ -9501,11 +9596,11 @@
       <c r="E4" s="13"/>
       <c r="F4" s="12"/>
       <c r="G4" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J4" s="12"/>
       <c r="K4" s="13"/>
@@ -9543,16 +9638,16 @@
     </row>
     <row r="5" spans="1:34" s="2" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>203</v>
-      </c>
       <c r="D5" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E5" s="11">
         <v>100</v>
@@ -9597,7 +9692,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
@@ -9643,7 +9738,7 @@
       <c r="E7" s="13"/>
       <c r="F7" s="12"/>
       <c r="G7" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
@@ -9683,16 +9778,16 @@
     </row>
     <row r="8" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>207</v>
-      </c>
       <c r="D8" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E8" s="16">
         <v>500</v>
@@ -9727,10 +9822,10 @@
       <c r="AE8" s="15"/>
       <c r="AF8" s="15"/>
       <c r="AG8" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AH8" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -9741,7 +9836,7 @@
       <c r="E9" s="13"/>
       <c r="F9" s="12"/>
       <c r="G9" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -9787,7 +9882,7 @@
       <c r="E10" s="13"/>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
@@ -9827,16 +9922,16 @@
     </row>
     <row r="11" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="C11" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="D11" s="31" t="s">
         <v>44</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>45</v>
       </c>
       <c r="E11" s="31">
         <v>100</v>
@@ -9845,10 +9940,10 @@
         <v>8</v>
       </c>
       <c r="G11" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="31" t="s">
         <v>46</v>
-      </c>
-      <c r="H11" s="31" t="s">
-        <v>47</v>
       </c>
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
@@ -9868,21 +9963,21 @@
       <c r="X11" s="31"/>
       <c r="Y11" s="31"/>
       <c r="Z11" s="31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA11" s="31"/>
       <c r="AB11" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AC11" s="31"/>
       <c r="AD11" s="34"/>
       <c r="AE11" s="34"/>
       <c r="AF11" s="34"/>
       <c r="AG11" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH11" s="34" t="s">
         <v>50</v>
-      </c>
-      <c r="AH11" s="34" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
@@ -9893,28 +9988,28 @@
       <c r="E12" s="34"/>
       <c r="F12" s="33"/>
       <c r="G12" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="H12" s="33" t="s">
+      <c r="I12" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="I12" s="44" t="s">
+      <c r="J12" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="44" t="s">
+      <c r="K12" s="45">
+        <v>0</v>
+      </c>
+      <c r="L12" s="45">
+        <v>0</v>
+      </c>
+      <c r="M12" s="45">
+        <v>8</v>
+      </c>
+      <c r="N12" s="46" t="s">
         <v>55</v>
-      </c>
-      <c r="K12" s="45">
-        <v>0</v>
-      </c>
-      <c r="L12" s="45">
-        <v>0</v>
-      </c>
-      <c r="M12" s="45">
-        <v>8</v>
-      </c>
-      <c r="N12" s="46" t="s">
-        <v>56</v>
       </c>
       <c r="O12" s="45">
         <v>1</v>
@@ -9943,10 +10038,10 @@
       <c r="W12" s="34"/>
       <c r="X12" s="34"/>
       <c r="Y12" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z12" s="33" t="s">
         <v>57</v>
-      </c>
-      <c r="Z12" s="33" t="s">
-        <v>58</v>
       </c>
       <c r="AA12" s="34"/>
       <c r="AB12" s="33"/>
@@ -9965,16 +10060,16 @@
       <c r="E13" s="34"/>
       <c r="F13" s="33"/>
       <c r="G13" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="36" t="s">
-        <v>60</v>
-      </c>
       <c r="I13" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" s="44" t="s">
         <v>54</v>
-      </c>
-      <c r="J13" s="44" t="s">
-        <v>55</v>
       </c>
       <c r="K13" s="34">
         <v>1</v>
@@ -9986,7 +10081,7 @@
         <v>2</v>
       </c>
       <c r="N13" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O13" s="45">
         <v>1</v>
@@ -10017,10 +10112,10 @@
       </c>
       <c r="X13" s="34"/>
       <c r="Y13" s="36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Z13" s="33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AA13" s="34"/>
       <c r="AB13" s="33"/>
@@ -10039,16 +10134,16 @@
       <c r="E14" s="34"/>
       <c r="F14" s="33"/>
       <c r="G14" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="H14" s="33" t="s">
-        <v>63</v>
-      </c>
       <c r="I14" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="J14" s="44" t="s">
         <v>54</v>
-      </c>
-      <c r="J14" s="44" t="s">
-        <v>55</v>
       </c>
       <c r="K14" s="34">
         <v>2</v>
@@ -10060,7 +10155,7 @@
         <v>4</v>
       </c>
       <c r="N14" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O14" s="45">
         <v>1</v>
@@ -10091,10 +10186,10 @@
       </c>
       <c r="X14" s="34"/>
       <c r="Y14" s="36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Z14" s="33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AA14" s="34"/>
       <c r="AB14" s="33"/>
@@ -10113,16 +10208,16 @@
       <c r="E15" s="34"/>
       <c r="F15" s="33"/>
       <c r="G15" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="H15" s="36" t="s">
-        <v>66</v>
-      </c>
       <c r="I15" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" s="44" t="s">
         <v>54</v>
-      </c>
-      <c r="J15" s="44" t="s">
-        <v>55</v>
       </c>
       <c r="K15" s="34">
         <v>2</v>
@@ -10134,7 +10229,7 @@
         <v>4</v>
       </c>
       <c r="N15" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O15" s="45">
         <v>1</v>
@@ -10165,10 +10260,10 @@
       </c>
       <c r="X15" s="34"/>
       <c r="Y15" s="36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Z15" s="33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AA15" s="34"/>
       <c r="AB15" s="33"/>
@@ -10187,16 +10282,16 @@
       <c r="E16" s="34"/>
       <c r="F16" s="33"/>
       <c r="G16" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="H16" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="H16" s="36" t="s">
-        <v>69</v>
-      </c>
       <c r="I16" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="J16" s="44" t="s">
         <v>54</v>
-      </c>
-      <c r="J16" s="44" t="s">
-        <v>55</v>
       </c>
       <c r="K16" s="34"/>
       <c r="L16" s="34">
@@ -10206,7 +10301,7 @@
         <v>8</v>
       </c>
       <c r="N16" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O16" s="45">
         <v>1</v>
@@ -10235,16 +10330,16 @@
     </row>
     <row r="17" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="C17" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="D17" s="37" t="s">
         <v>72</v>
-      </c>
-      <c r="D17" s="37" t="s">
-        <v>73</v>
       </c>
       <c r="E17" s="37">
         <v>100</v>
@@ -10253,10 +10348,10 @@
         <v>8</v>
       </c>
       <c r="G17" s="37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I17" s="37"/>
       <c r="J17" s="47"/>
@@ -10278,17 +10373,17 @@
       <c r="Z17" s="37"/>
       <c r="AA17" s="37"/>
       <c r="AB17" s="37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AC17" s="47"/>
       <c r="AD17" s="34"/>
       <c r="AE17" s="34"/>
       <c r="AF17" s="50"/>
       <c r="AG17" s="50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AH17" s="50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
@@ -10299,16 +10394,16 @@
       <c r="E18" s="34"/>
       <c r="F18" s="33"/>
       <c r="G18" s="33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H18" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="I18" s="44" t="s">
-        <v>54</v>
-      </c>
       <c r="J18" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K18" s="45">
         <v>0</v>
@@ -10320,7 +10415,7 @@
         <v>8</v>
       </c>
       <c r="N18" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O18" s="45">
         <v>1</v>
@@ -10349,7 +10444,7 @@
       <c r="W18" s="34"/>
       <c r="X18" s="34"/>
       <c r="Y18" s="33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z18" s="33"/>
       <c r="AA18" s="34"/>
@@ -10369,16 +10464,16 @@
       <c r="E19" s="34"/>
       <c r="F19" s="33"/>
       <c r="G19" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="H19" s="36" t="s">
-        <v>77</v>
-      </c>
       <c r="I19" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J19" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K19" s="34">
         <v>1</v>
@@ -10391,7 +10486,7 @@
         <v>8</v>
       </c>
       <c r="N19" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O19" s="45">
         <v>1</v>
@@ -10438,16 +10533,16 @@
       <c r="E20" s="34"/>
       <c r="F20" s="33"/>
       <c r="G20" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="H20" s="36" t="s">
-        <v>79</v>
-      </c>
       <c r="I20" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J20" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K20" s="34">
         <v>2</v>
@@ -10460,7 +10555,7 @@
         <v>4</v>
       </c>
       <c r="N20" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O20" s="45">
         <v>1</v>
@@ -10489,7 +10584,7 @@
       <c r="W20" s="34"/>
       <c r="X20" s="34"/>
       <c r="Y20" s="36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z20" s="36"/>
       <c r="AA20" s="34"/>
@@ -10509,16 +10604,16 @@
       <c r="E21" s="34"/>
       <c r="F21" s="33"/>
       <c r="G21" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="H21" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="36" t="s">
-        <v>82</v>
-      </c>
       <c r="I21" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J21" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K21" s="34">
         <v>2</v>
@@ -10530,7 +10625,7 @@
         <v>4</v>
       </c>
       <c r="N21" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O21" s="45">
         <v>1</v>
@@ -10558,10 +10653,10 @@
       </c>
       <c r="W21" s="34"/>
       <c r="X21" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y21" s="36" t="s">
         <v>83</v>
-      </c>
-      <c r="Y21" s="36" t="s">
-        <v>84</v>
       </c>
       <c r="Z21" s="36"/>
       <c r="AA21" s="34"/>
@@ -10581,16 +10676,16 @@
       <c r="E22" s="34"/>
       <c r="F22" s="33"/>
       <c r="G22" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="H22" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="H22" s="36" t="s">
-        <v>86</v>
-      </c>
       <c r="I22" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K22" s="34">
         <v>3</v>
@@ -10602,7 +10697,7 @@
         <v>2</v>
       </c>
       <c r="N22" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O22" s="45">
         <v>1</v>
@@ -10631,7 +10726,7 @@
       <c r="W22" s="34"/>
       <c r="X22" s="34"/>
       <c r="Y22" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z22" s="36"/>
       <c r="AA22" s="34"/>
@@ -10651,16 +10746,16 @@
       <c r="E23" s="34"/>
       <c r="F23" s="33"/>
       <c r="G23" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="H23" s="36" t="s">
-        <v>89</v>
-      </c>
       <c r="I23" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J23" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K23" s="34">
         <v>3</v>
@@ -10672,7 +10767,7 @@
         <v>2</v>
       </c>
       <c r="N23" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O23" s="45">
         <v>1</v>
@@ -10701,7 +10796,7 @@
       <c r="W23" s="34"/>
       <c r="X23" s="34"/>
       <c r="Y23" s="36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Z23" s="36"/>
       <c r="AA23" s="34"/>
@@ -10721,16 +10816,16 @@
       <c r="E24" s="34"/>
       <c r="F24" s="33"/>
       <c r="G24" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="H24" s="36" t="s">
-        <v>92</v>
-      </c>
       <c r="I24" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J24" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K24" s="34">
         <v>3</v>
@@ -10742,7 +10837,7 @@
         <v>2</v>
       </c>
       <c r="N24" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O24" s="45">
         <v>1</v>
@@ -10765,7 +10860,7 @@
       <c r="W24" s="34"/>
       <c r="X24" s="34"/>
       <c r="Y24" s="36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Z24" s="36"/>
       <c r="AA24" s="34"/>
@@ -10785,16 +10880,16 @@
       <c r="E25" s="34"/>
       <c r="F25" s="33"/>
       <c r="G25" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="H25" s="38" t="s">
-        <v>95</v>
-      </c>
       <c r="I25" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J25" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K25" s="34">
         <v>7</v>
@@ -10806,7 +10901,7 @@
         <v>8</v>
       </c>
       <c r="N25" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O25" s="45">
         <v>1</v>
@@ -10835,7 +10930,7 @@
       <c r="W25" s="34"/>
       <c r="X25" s="34"/>
       <c r="Y25" s="36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Z25" s="36"/>
       <c r="AA25" s="34"/>
@@ -10849,16 +10944,16 @@
     </row>
     <row r="26" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="B26" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>98</v>
-      </c>
       <c r="D26" s="39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E26" s="39">
         <v>50</v>
@@ -10868,7 +10963,7 @@
       </c>
       <c r="G26" s="39"/>
       <c r="H26" s="39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I26" s="39"/>
       <c r="J26" s="39"/>
@@ -10890,7 +10985,7 @@
       <c r="Z26" s="39"/>
       <c r="AA26" s="39"/>
       <c r="AB26" s="39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AC26" s="39"/>
       <c r="AD26" s="34"/>
@@ -10901,7 +10996,7 @@
     </row>
     <row r="27" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B27" s="33"/>
       <c r="C27" s="33"/>
@@ -10909,16 +11004,16 @@
       <c r="E27" s="34"/>
       <c r="F27" s="33"/>
       <c r="G27" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="H27" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="H27" s="38" t="s">
+      <c r="I27" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="I27" s="44" t="s">
-        <v>103</v>
-      </c>
       <c r="J27" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K27" s="33"/>
       <c r="L27" s="34">
@@ -10928,7 +11023,7 @@
         <v>8</v>
       </c>
       <c r="N27" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O27" s="34">
         <v>1</v>
@@ -10957,7 +11052,7 @@
     </row>
     <row r="28" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="33" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" s="33"/>
       <c r="C28" s="33"/>
@@ -10965,14 +11060,14 @@
       <c r="E28" s="34"/>
       <c r="F28" s="33"/>
       <c r="G28" s="33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H28" s="33"/>
       <c r="I28" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J28" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K28" s="33"/>
       <c r="L28" s="34">
@@ -10982,7 +11077,7 @@
         <v>8</v>
       </c>
       <c r="N28" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O28" s="34">
         <v>1</v>
@@ -11011,7 +11106,7 @@
     </row>
     <row r="29" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B29" s="33"/>
       <c r="C29" s="33"/>
@@ -11019,14 +11114,14 @@
       <c r="E29" s="34"/>
       <c r="F29" s="33"/>
       <c r="G29" s="33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H29" s="33"/>
       <c r="I29" s="44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J29" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K29" s="33"/>
       <c r="L29" s="34">
@@ -11036,7 +11131,7 @@
         <v>8</v>
       </c>
       <c r="N29" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O29" s="34">
         <v>1</v>
@@ -11067,30 +11162,30 @@
       <c r="A30" s="33"/>
       <c r="B30" s="33"/>
       <c r="C30" s="33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D30" s="33"/>
       <c r="E30" s="34"/>
       <c r="F30" s="33"/>
       <c r="G30" s="33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H30" s="33"/>
       <c r="I30" s="44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J30" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K30" s="33"/>
       <c r="L30" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M30" s="34">
         <v>4</v>
       </c>
       <c r="N30" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O30" s="34">
         <v>1</v>
@@ -11125,24 +11220,24 @@
       <c r="E31" s="34"/>
       <c r="F31" s="33"/>
       <c r="G31" s="33" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H31" s="33"/>
       <c r="I31" s="44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J31" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K31" s="33"/>
       <c r="L31" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="M31" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="M31" s="48" t="s">
-        <v>113</v>
-      </c>
       <c r="N31" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O31" s="34">
         <v>1</v>
@@ -11177,16 +11272,16 @@
       <c r="E32" s="34"/>
       <c r="F32" s="33"/>
       <c r="G32" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="H32" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="H32" s="38" t="s">
-        <v>115</v>
-      </c>
       <c r="I32" s="44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J32" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K32" s="34"/>
       <c r="L32" s="48">
@@ -11196,7 +11291,7 @@
         <v>16</v>
       </c>
       <c r="N32" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O32" s="34">
         <v>1</v>
@@ -11225,16 +11320,16 @@
     </row>
     <row r="33" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="B33" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>117</v>
-      </c>
       <c r="D33" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E33" s="41">
         <v>200</v>
@@ -11279,14 +11374,14 @@
       <c r="E34" s="43"/>
       <c r="F34" s="42"/>
       <c r="G34" s="42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H34" s="42"/>
       <c r="I34" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J34" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K34" s="43"/>
       <c r="L34" s="43">
@@ -11296,7 +11391,7 @@
         <v>8</v>
       </c>
       <c r="N34" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O34" s="43">
         <v>1</v>
@@ -11331,14 +11426,14 @@
       <c r="E35" s="43"/>
       <c r="F35" s="42"/>
       <c r="G35" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H35" s="42"/>
       <c r="I35" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J35" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K35" s="43"/>
       <c r="L35" s="43">
@@ -11348,7 +11443,7 @@
         <v>8</v>
       </c>
       <c r="N35" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O35" s="43">
         <v>1</v>
@@ -11383,14 +11478,14 @@
       <c r="E36" s="43"/>
       <c r="F36" s="42"/>
       <c r="G36" s="42" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H36" s="42"/>
       <c r="I36" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J36" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K36" s="43"/>
       <c r="L36" s="43">
@@ -11400,7 +11495,7 @@
         <v>8</v>
       </c>
       <c r="N36" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O36" s="43">
         <v>1</v>
@@ -11435,14 +11530,14 @@
       <c r="E37" s="43"/>
       <c r="F37" s="42"/>
       <c r="G37" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H37" s="42"/>
       <c r="I37" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J37" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K37" s="43"/>
       <c r="L37" s="43">
@@ -11452,7 +11547,7 @@
         <v>8</v>
       </c>
       <c r="N37" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O37" s="43">
         <v>1</v>
@@ -11487,14 +11582,14 @@
       <c r="E38" s="43"/>
       <c r="F38" s="42"/>
       <c r="G38" s="42" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H38" s="42"/>
       <c r="I38" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J38" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K38" s="43"/>
       <c r="L38" s="43">
@@ -11504,7 +11599,7 @@
         <v>8</v>
       </c>
       <c r="N38" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O38" s="43">
         <v>0.2</v>
@@ -11539,14 +11634,14 @@
       <c r="E39" s="43"/>
       <c r="F39" s="42"/>
       <c r="G39" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H39" s="42"/>
       <c r="I39" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J39" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K39" s="43"/>
       <c r="L39" s="43">
@@ -11556,7 +11651,7 @@
         <v>8</v>
       </c>
       <c r="N39" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O39" s="43">
         <v>0.5</v>
@@ -11591,14 +11686,14 @@
       <c r="E40" s="43"/>
       <c r="F40" s="42"/>
       <c r="G40" s="42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H40" s="42"/>
       <c r="I40" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J40" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K40" s="43"/>
       <c r="L40" s="43">
@@ -11608,7 +11703,7 @@
         <v>8</v>
       </c>
       <c r="N40" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O40" s="43">
         <v>0.1</v>
@@ -11643,14 +11738,14 @@
       <c r="E41" s="43"/>
       <c r="F41" s="42"/>
       <c r="G41" s="42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H41" s="42"/>
       <c r="I41" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J41" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K41" s="43"/>
       <c r="L41" s="43">
@@ -11660,7 +11755,7 @@
         <v>8</v>
       </c>
       <c r="N41" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O41" s="43">
         <v>0.1</v>
@@ -11764,120 +11859,120 @@
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1" ht="88.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Z1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="AA1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AB1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AB1" s="8" t="s">
+      <c r="AC1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AC1" s="8" t="s">
+      <c r="AD1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="AD1" s="17" t="s">
+      <c r="AE1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="AE1" s="17" t="s">
+      <c r="AF1" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="AF1" s="17" t="s">
-        <v>39</v>
-      </c>
       <c r="AG1" s="21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AH1" s="21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="2" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>207</v>
-      </c>
       <c r="D2" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E2" s="11">
         <v>100</v>
@@ -11912,10 +12007,10 @@
       <c r="AE2" s="10"/>
       <c r="AF2" s="10"/>
       <c r="AG2" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH2" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="AH2" s="10" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -11926,7 +12021,7 @@
       <c r="E3" s="13"/>
       <c r="F3" s="12"/>
       <c r="G3" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
@@ -11972,7 +12067,7 @@
       <c r="E4" s="13"/>
       <c r="F4" s="12"/>
       <c r="G4" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
@@ -12012,16 +12107,16 @@
     </row>
     <row r="5" spans="1:34" s="2" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>212</v>
-      </c>
       <c r="D5" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E5" s="11">
         <v>100</v>
@@ -12056,10 +12151,10 @@
       <c r="AE5" s="10"/>
       <c r="AF5" s="10"/>
       <c r="AG5" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH5" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="AH5" s="10" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -12070,7 +12165,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
@@ -12116,7 +12211,7 @@
       <c r="E7" s="13"/>
       <c r="F7" s="12"/>
       <c r="G7" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
@@ -12156,16 +12251,16 @@
     </row>
     <row r="8" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>199</v>
-      </c>
       <c r="D8" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" s="16">
         <v>500</v>
@@ -12200,10 +12295,10 @@
       <c r="AE8" s="15"/>
       <c r="AF8" s="19"/>
       <c r="AG8" s="22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AH8" s="22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -12214,7 +12309,7 @@
       <c r="E9" s="13"/>
       <c r="F9" s="12"/>
       <c r="G9" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -12260,7 +12355,7 @@
       <c r="E10" s="13"/>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>

--- a/src/test/resources/Excel/DBC模版.xlsx
+++ b/src/test/resources/Excel/DBC模版.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_USER\SLC\Code\IDEA_Project\smart-dbc\src\test\resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF74DEF-D1BA-4A85-BB53-62D269395DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D7A55C-A02A-4934-AD4D-C4C639DCCB9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20085" yWindow="2865" windowWidth="18300" windowHeight="17385" tabRatio="476" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="476" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CanProtocol_Info" sheetId="7" r:id="rId1"/>
-    <sheet name="DbcList" sheetId="6" r:id="rId2"/>
-    <sheet name="Example" sheetId="1" r:id="rId3"/>
-    <sheet name="CAN1" sheetId="2" r:id="rId4"/>
-    <sheet name="CAN2" sheetId="5" r:id="rId5"/>
+    <sheet name="AttributeDefinition" sheetId="8" r:id="rId2"/>
+    <sheet name="DbcList" sheetId="6" r:id="rId3"/>
+    <sheet name="Example" sheetId="1" r:id="rId4"/>
+    <sheet name="CAN1" sheetId="2" r:id="rId5"/>
+    <sheet name="CAN2" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,857 +40,138 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>作者</author>
-    <author>石李城</author>
+    <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{BD51F242-2B3E-40A2-A2F9-5104A8D5D822}">
       <text>
         <r>
           <rPr>
             <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入报文名称。
-1、以字母或下划线开头，并且只可能进一步由26个字母、数字和下划线组成。
-2、长度最多为128个字符。为了与较旧的工具兼容，长度不得超过32个字符。
-3、报文名称中请不要使用换行符、空格等无效格式。
-4、请一定填写报文名称，报文名称不能为空。
-5、请不要填写重复的报文名称。
-6、信号逐行填写，报文信息只填写在属于该报文的信号的第一行。</t>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+你在这里定义好了你的自定义属性的名称后，你可以在你的表头中使用你的这个自定义属性。
+然后你就可以在对应的列里边填入你的值即可。</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{35ADE984-0FD7-4F44-B354-B6143E7DBEF2}">
       <text>
         <r>
           <rPr>
             <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入报文类型。
-报文类型只能为：Normal,NM,Diag,Extended,Standard   中的一个。
-Normal 类型包括 Extended 和 Standard  。
-并且现程序根据id自动判断扩展帧 Extended 和标准帧 Standard ，故不必特地填写扩展帧
-请一定填写报文类型，报文类型不能为空。</t>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+值类型固定是整形、浮点型、字符串、枚举类型和16进制数值，共5个类型。</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{32141E84-366B-411C-A66D-81AF5211331D}">
       <text>
         <r>
           <rPr>
             <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">请输入11位的报文ID。
-1、请确定报文ID为16进制正整数。
-2、报文ID可以带有"0x"标识，也可以不带“0x”。
-3、请一定填写报文ID，报文ID不能为空。报文ID不能重复。
-4、标准帧范围0x0~0x7FF; 扩展帧范围0x0~0x1FFF_FFFF，现改为范围0x7FF~0x1FFF_FFFF。
-5、注意: 标准帧0x211那么在DBC编码里它就是0x211的十进制表示。如果是扩展帧，0x211就会变成0x211+0x8000_0000然后再变成十进制存储。DBC编码由此来识别是扩展帧还是标准帧。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <strike/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>6、 如果协议中只填写了报文ID且小于0x7FF，那么DBC编码的时候可以识别成标准帧也可以识别成扩展帧，程序将无法正确识别。</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-7、现程序自动将范围0x0~0x7FF识别成标准帧。范围0x7FF~0x1FFF_FFFF，识别成扩展帧。</t>
+最大值和最小值只有当值类型是数值类型的时候有效，例如说整形、浮点型和16进制数值。
+字符串和枚举类型则不适用最大值最小值。</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{DC1A8136-C1B6-43DA-8EF0-0DE3CA605544}">
       <text>
         <r>
           <rPr>
             <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入报文发送类型。
-报文发送类型只能为：Cycle,Event, IfActive,CE,CA    中的一个。
-请确定大小写与建议值保持一致。
-请一定填写报文发送类型，报文发送类型不能为空，事件型 Event 报文可以可以不写周期。
-Cycle:周期型，按照一定周期循环发送
-Event:事件型，触发事件后，仅发送一次
-IfActive:事件周期型，触发事件后，按照周期循环发送一定次数
-当信号所在报文的发送类型为"Cycle"时，信号发送类型只能为"Cycle"。
-报文发送类型为"Event"时，报文中至少有一个信号的发送类型为"Event"。
-报文发送类型为"IfActive"时，报文中至少有一个信号的发送类型为"IfActive"。
-报文发送类型为"CE"时，报文中至少有一个信号的发送类型为"Event"。
-报文发送类型为"CA"时，报文中至少有一个信号的发送类型为"IfActive"。</t>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+默认值在任何的值类型时都有效。</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{99D438C2-2010-452B-8414-6DE3120E73F7}">
       <text>
         <r>
           <rPr>
             <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入报文周期时间。
-请确定报文周期时间为10进制正整数。
-当是事件型报文时，报文周期时间可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入报文长度。
-请确定报文长度为10进制正整数。
-报文长度最好不要超过8。
-请一定填写报文长度，报文长度不能为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号名称。
-信号名称只能为数字、下划线、字母，长度不能超过32个字符。
-信号名称中请不要使用换行符、空格等无效格式。
-请一定填写信号名称，信号名称不能为空。
-信号信息逐行填写。
-请不要填写重复的信号名称。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号描述。
-信号描述请不要使用","（英文逗号）和";"（英文分号）等无效格式。
-信号描述可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号排列格式。
-1、信号排列格式只能为： Intel,Motorola LSB,Motorola MSB     中的一种。
-2、请一定填写信号排列格式，信号排列格式不能为空，为空则默认为英特尔格式。
-3、英特尔格式,数据的最低位存放在矩阵的最低位。
-4、摩托罗拉格式,数据最低位存放在矩阵的高位。
-5、Motorola_MSB  ;该格式与 DBC 文件(即用txt打开)的格式保持一致 ，即信号的起始位是 数据最低位 ，在矩阵中的位置是 MSB
-6、Motorola_LSB   ;该格式与 CANdb++ 软件中的格式一致 ，即信号的起始位是 数据最高位 ，在矩阵中的位置是 LSB 
-7、例如：同样占据矩阵中01234567这8个bit的信号。
-Intel 格式的数据最低位是0，起始位是0；
-Motorola_MSB 格式，数据最低位是7，起始位则是7;
-Motorola LSB 格式，数据最低位还是7，但是起始位和 Intel 格式一样是 0 ;</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">请输入信号发送类型。
-信号发送类型只能为  Cycle,OnWrite,OnWriteWithRepetition,OnChange,OnChangeWithRepetition,IfActive,IfActiveWithRepetition    中的一种。
-请一定填写信号发送类型，信号发送类型不能为空。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1、当信号所在报文的发送类型为"Cycle"时</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">，信号发送类型只能为"Cycle"。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2、当信号所在报文的发送类型为"Event"时</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">，信号发送类型只能为"OnWrite"，"OnWriteWithRepetition"，"OnChange"，"OnChangeWithRepetition"中的一种。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3、当信号所在报文的发送类型为"IfActive"时</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">，信号发送类型只能为"IfActive"，"IfActiveWithRepetition"中的一种。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>4、当信号所在报文的发送类型为"CE"时</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">，信号发送类型只能为"OnWrite"，"OnWriteWithRepetition"，"OnChange"，"OnChangeWithRepetition"中的一种。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>5、当信号所在报文的发送类型为"CA"时</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>，信号发送类型只能为"IfActive"，"IfActiveWithRepetition"中的一种。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000B000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>起始字节不是必填项，起始位才是必填项，请填写信号在8*8矩阵的哪一个bit起始。
-请输入信号起始字节。
-请一定填写信号起始字节。
-请确定信号起始字节为10进制正整数。
-请确定信号的起始字节与起始位保持一致。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000C000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="等线"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号起始位。
-请一定填写信号起始位，起始位不能为空。
-请确定信号起始位为10进制正整数。
-请确定报文中的信号不重复排列。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000D000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号长度。
-请一定填写信号长度，信号长度不能为空。
-请确认信号长度为10进制正整数。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>有符号 、无符号、双精度和单精度类型。
-请输入信号数据类型。
-信号数据类型只能为  Unsigned,Signed,IEEE float,IEEE Double,Boolean    中的一种。
-请一定填写信号数据类型，信号数据类型不能为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号精度。
-信号精度只能为数字、小数点、或者分数。
-信号精度中请不要使用换行符、空格等无效格式。
-请一定填写信号精度，信号精度不能为空。
-精度不可以为0，因为是除数，为0后将无意义。
-物理值(实际值)= 原始值(总线值/未处理值)*精度 +偏移量</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000010000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号偏移量。
-信号偏移量只能为数字、小数点、负号。
-信号偏移量中请不要使用换行符、空格等无效格式。
-请一定填写信号偏移量，信号偏移量不能为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000011000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="等线"/>
-            <charset val="134"/>
-          </rPr>
-          <t>程序会校验你填入的最小值、最大值和初始值。根据信号的长度，以及精度和偏移量计算。
-如果不填，程序会自动帮你计算并填入默认值</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000012000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <rFont val="等线"/>
-            <charset val="134"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">之后的总线值都不是必填项目，填了我也不会管(除非有错)，但是之前的物理最小值和物理最大值和初始值是必填。如果物理最小值、物理最大值和物理初始值你也不想填；可以，程序会默认给默认值赋值成最小值，同时根据长度、精度和偏移量自动计算最小最大值。
-总线值即原始值，未经过处理的值。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="等线"/>
-            <charset val="134"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>物理值(实际值)= 原始值(总线值/未处理值)*精度 +偏移量</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000013000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入总线初始值。
-请确定信号初始值为16进制正整数。
-请确定信号初始值在信号总线最小值和信号总线最大值之间。
-信号初始值可以带有"0x"标识。
-信号初始值可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000014000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号无效值。
-请确定信号无效值为16进制正整数。
-请确定信号无效值在信号总线最小值和信号总线最大值之间。
-信号无效值可以带有"0x"标识。
-信号无效值可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="X1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000015000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号单位。
-信号单位请不要使用","（英文逗号）和";"（英文分号）等无效格式。
-信号单位可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000016000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">信号值描述
-采用键值对的方式描述数据，一个键值对应一个数据，例如 key:value
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1、如何填写键：</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">请确定信号值描述的值没有超过信号长度能表达的值范围。
-带有0x的数会被识别成16进制数，不带的会被识别成10进制数。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2、如何分割键和值：</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">使用等号、中文冒号、英文冒号分隔键和值。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3、如何分割多个键值对：</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">使用句号、中英文分号、或者回车换行符分割一组键值对。
-又或者使用引号把单个注释项引起来。（不推荐引号这种写法）
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>4、如何填写值：</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>值描述的内容中可以出现逗号和小数点，但是不可以使用中英文分号、中英文冒号、等号、中英文引号、句号或者回车换行符，否则可能无法识别。简单来讲就是用于分割的符号不可以出现在内容中。
-启用值描述，本程序在检查值描述规则的时候，不符合规则的值描述会被当成注释直接添加到注释中。
-例如：
-0=预留；1=关闭；  2  :   开启 
-1=关闭；就是一组键值对，"1"表示键 ，"关闭"表示值</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="11"/>
-            <rFont val="等线"/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Z1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000017000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>这一栏可以填入报文或者信号的备注。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AA1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000018000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号非使能值。
-请确定信号非使能值为16进制正整数。
-请确定信号非使能值在信号总线最小值和信号总线最大值之间。
-信号非使能值可以带有"0x"标识。
-信号非使能值可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AB1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000019000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="等线"/>
-            <charset val="134"/>
-          </rPr>
-          <t>网关需求报文。
-理论上，网关不会读取路由表中任何数据，如果网关需要读取其中某一些数据，就填写Yes，否则填写No，或者不填</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AC1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">分组类型，或者说分组模式、即多路复用。当你需要在一个报文矩阵中的同一个位置，塞入两个或以上的报文时，就需要采用多路复用，也就是分组功能。否则会出现报文id重复错误，或者出现报文重叠错误。
-请填入以下三种类型的数据：默认分组，分组标志位和组号。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1、默认分组。</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-请填入 ：默认、默认分组、不分组、Default、DefaultGroup、single 或者你干脆直接空着不填(</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>推荐默认分组直接不填</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>)（注意：是叫你不填，并不不是让你填写0）。默认分组就表示最基本的状态，如果该帧报文全是默认分组，则只可以表示64bit的数据。如果该帧报文同时还存在其他分组报文，那么默认分组的报文会出现在所有的分组中，并且位置一致</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">。就是说，当不同分组的报文发过来的时候，默认分组的报文都存在。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">2、分组标志位。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">请填入：分组标志位、标志位、GroupFlag、Flag。即可被识别成标志位。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>一个报文只可以有一个分组标志位。</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-标志位用于储存并表示当前报文的组号。虽然有了分组，信号就可以在该帧同一个位置表示多个数据，但是一次只能发送一个分组的数据，只能同时激活一组数据(当然，默认分组会一直处于激活状态)。故标志位就是用于表示该组数据的组号。不同分组的报文发过来的时候，分组标志位也不同。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">3、组号。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请填入：“组号：67(替换成你的组号)”，“Num：50(替换成你的组号)”,“32(或者你直接填写一个数字也是可以的)”。</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>推荐直接填写数字组号即可，只能填写大于等于0的整型数。</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-组号用于标注分组，实现在8*8矩阵的同一个位置放上好几个数据。当当前报文的分组标志位是67时，只激活组号67的报文，程序按照组号67的规则来解析，以此类推。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AD1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001B000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入报文发送的快速周期。
-请确定报文发送的快速周期为10进制正整数。
-报文发送的快速周期可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AE1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001C000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入报文快速发送的次数。
-请确定报文快速发送的次数为10进制正整数。
-报文快速发送的次数可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AF1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001D000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入报文延时时间。
-请确定报文延时时间为10进制正整数。
-报文延时时间可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AG1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001E000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>如果是发送节点，在报文所在行、节点所在列对应的单元格输入"s"。
-如果是接收节点，在报文所在行、节点所在列对应的单元格输入"r"。
-请确定报文一定有发送节点。
-信号可以没有接受节点。
-节点名称，以字母或下划线开头，并且只可能进一步由26个字母、数字和下划线组成，长度不得超过32个字符。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001F000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="等线"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Normal 类型包括 Extended 和 Standard  。
-并且现程序根据id自动判断扩展帧 Extended 和标准帧 Standard ，故不必特地填写扩展帧</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000020000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="36"/>
-            <rFont val="Microsoft YaHei UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t>注释不可以写到这里</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
+ </t>
         </r>
       </text>
     </comment>
@@ -904,7 +186,7 @@
     <author>石李城</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -923,7 +205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -940,7 +222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -979,7 +261,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
@@ -1003,7 +285,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
+    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
       <text>
         <r>
           <rPr>
@@ -1018,7 +300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
       <text>
         <r>
           <rPr>
@@ -1034,7 +316,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
         <r>
           <rPr>
@@ -1052,7 +334,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
         <r>
           <rPr>
@@ -1067,7 +349,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
         <r>
           <rPr>
@@ -1090,7 +372,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000A000000}">
+    <comment ref="J1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -1194,7 +476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000B000000}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -1211,7 +493,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000C000000}">
+    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -1227,7 +509,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000D000000}">
+    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -1242,7 +524,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000E000000}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -1258,7 +540,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000F000000}">
+    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -1276,7 +558,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000010000000}">
+    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000010000000}">
       <text>
         <r>
           <rPr>
@@ -1292,7 +574,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000011000000}">
+    <comment ref="Q1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000011000000}">
       <text>
         <r>
           <rPr>
@@ -1306,7 +588,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000012000000}">
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000012000000}">
       <text>
         <r>
           <rPr>
@@ -1331,7 +613,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000013000000}">
+    <comment ref="V1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000013000000}">
       <text>
         <r>
           <rPr>
@@ -1348,7 +630,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000014000000}">
+    <comment ref="W1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000014000000}">
       <text>
         <r>
           <rPr>
@@ -1365,7 +647,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000015000000}">
+    <comment ref="X1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000015000000}">
       <text>
         <r>
           <rPr>
@@ -1380,7 +662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000016000000}">
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000016000000}">
       <text>
         <r>
           <rPr>
@@ -1481,7 +763,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000017000000}">
+    <comment ref="Z1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000017000000}">
       <text>
         <r>
           <rPr>
@@ -1494,7 +776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000018000000}">
+    <comment ref="AA1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000018000000}">
       <text>
         <r>
           <rPr>
@@ -1511,7 +793,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000019000000}">
+    <comment ref="AB1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000019000000}">
       <text>
         <r>
           <rPr>
@@ -1525,7 +807,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001A000000}">
+    <comment ref="AC1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001A000000}">
       <text>
         <r>
           <rPr>
@@ -1657,7 +939,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001B000000}">
+    <comment ref="AD1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001B000000}">
       <text>
         <r>
           <rPr>
@@ -1672,7 +954,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001C000000}">
+    <comment ref="AE1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001C000000}">
       <text>
         <r>
           <rPr>
@@ -1687,7 +969,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001D000000}">
+    <comment ref="AF1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001D000000}">
       <text>
         <r>
           <rPr>
@@ -1702,7 +984,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001E000000}">
+    <comment ref="AG1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001E000000}">
       <text>
         <r>
           <rPr>
@@ -1719,7 +1001,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="1" shapeId="0" xr:uid="{94FABF88-1AA4-4777-BDB3-F411CAAF4BDA}">
+    <comment ref="B2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001F000000}">
       <text>
         <r>
           <rPr>
@@ -1733,7 +1015,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A12" authorId="1" shapeId="0" xr:uid="{AC3CAF0B-70B3-4BC4-969A-CB047C53693F}">
+    <comment ref="A3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000020000000}">
       <text>
         <r>
           <rPr>
@@ -1765,7 +1047,7 @@
     <author>石李城</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1784,7 +1066,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1801,7 +1083,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -1840,7 +1122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -1864,7 +1146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
+    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -1879,7 +1161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000006000000}">
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
@@ -1895,7 +1177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000007000000}">
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
@@ -1913,7 +1195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
@@ -1928,7 +1210,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000009000000}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
       <text>
         <r>
           <rPr>
@@ -1951,6 +1233,867 @@
         </r>
       </text>
     </comment>
+    <comment ref="J1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">请输入信号发送类型。
+信号发送类型只能为  Cycle,OnWrite,OnWriteWithRepetition,OnChange,OnChangeWithRepetition,IfActive,IfActiveWithRepetition    中的一种。
+请一定填写信号发送类型，信号发送类型不能为空。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>1、当信号所在报文的发送类型为"Cycle"时</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">，信号发送类型只能为"Cycle"。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>2、当信号所在报文的发送类型为"Event"时</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">，信号发送类型只能为"OnWrite"，"OnWriteWithRepetition"，"OnChange"，"OnChangeWithRepetition"中的一种。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>3、当信号所在报文的发送类型为"IfActive"时</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">，信号发送类型只能为"IfActive"，"IfActiveWithRepetition"中的一种。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>4、当信号所在报文的发送类型为"CE"时</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">，信号发送类型只能为"OnWrite"，"OnWriteWithRepetition"，"OnChange"，"OnChangeWithRepetition"中的一种。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>5、当信号所在报文的发送类型为"CA"时</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>，信号发送类型只能为"IfActive"，"IfActiveWithRepetition"中的一种。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000B000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>起始字节不是必填项，起始位才是必填项，请填写信号在8*8矩阵的哪一个bit起始。
+请输入信号起始字节。
+请一定填写信号起始字节。
+请确定信号起始字节为10进制正整数。
+请确定信号的起始字节与起始位保持一致。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000C000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="等线"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号起始位。
+请一定填写信号起始位，起始位不能为空。
+请确定信号起始位为10进制正整数。
+请确定报文中的信号不重复排列。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000D000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号长度。
+请一定填写信号长度，信号长度不能为空。
+请确认信号长度为10进制正整数。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000E000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>有符号 、无符号、双精度和单精度类型。
+请输入信号数据类型。
+信号数据类型只能为  Unsigned,Signed,IEEE float,IEEE Double,Boolean    中的一种。
+请一定填写信号数据类型，信号数据类型不能为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000F000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号精度。
+信号精度只能为数字、小数点、或者分数。
+信号精度中请不要使用换行符、空格等无效格式。
+请一定填写信号精度，信号精度不能为空。
+精度不可以为0，因为是除数，为0后将无意义。
+物理值(实际值)= 原始值(总线值/未处理值)*精度 +偏移量</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000010000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号偏移量。
+信号偏移量只能为数字、小数点、负号。
+信号偏移量中请不要使用换行符、空格等无效格式。
+请一定填写信号偏移量，信号偏移量不能为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000011000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="等线"/>
+            <charset val="134"/>
+          </rPr>
+          <t>程序会校验你填入的最小值、最大值和初始值。根据信号的长度，以及精度和偏移量计算。
+如果不填，程序会自动帮你计算并填入默认值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000012000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <rFont val="等线"/>
+            <charset val="134"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">之后的总线值都不是必填项目，填了我也不会管(除非有错)，但是之前的物理最小值和物理最大值和初始值是必填。如果物理最小值、物理最大值和物理初始值你也不想填；可以，程序会默认给默认值赋值成最小值，同时根据长度、精度和偏移量自动计算最小最大值。
+总线值即原始值，未经过处理的值。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="等线"/>
+            <charset val="134"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>物理值(实际值)= 原始值(总线值/未处理值)*精度 +偏移量</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000013000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入总线初始值。
+请确定信号初始值为16进制正整数。
+请确定信号初始值在信号总线最小值和信号总线最大值之间。
+信号初始值可以带有"0x"标识。
+信号初始值可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000014000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号无效值。
+请确定信号无效值为16进制正整数。
+请确定信号无效值在信号总线最小值和信号总线最大值之间。
+信号无效值可以带有"0x"标识。
+信号无效值可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000015000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号单位。
+信号单位请不要使用","（英文逗号）和";"（英文分号）等无效格式。
+信号单位可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000016000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">信号值描述
+采用键值对的方式描述数据，一个键值对应一个数据，例如 key:value
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>1、如何填写键：</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">请确定信号值描述的值没有超过信号长度能表达的值范围。
+带有0x的数会被识别成16进制数，不带的会被识别成10进制数。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>2、如何分割键和值：</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">使用等号、中文冒号、英文冒号分隔键和值。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>3、如何分割多个键值对：</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">使用句号、中英文分号、或者回车换行符分割一组键值对。
+又或者使用引号把单个注释项引起来。（不推荐引号这种写法）
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>4、如何填写值：</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>值描述的内容中可以出现逗号和小数点，但是不可以使用中英文分号、中英文冒号、等号、中英文引号、句号或者回车换行符，否则可能无法识别。简单来讲就是用于分割的符号不可以出现在内容中。
+启用值描述，本程序在检查值描述规则的时候，不符合规则的值描述会被当成注释直接添加到注释中。
+例如：
+0=预留；1=关闭；  2  :   开启 
+1=关闭；就是一组键值对，"1"表示键 ，"关闭"表示值</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <rFont val="等线"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000017000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>这一栏可以填入报文或者信号的备注。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000018000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号非使能值。
+请确定信号非使能值为16进制正整数。
+请确定信号非使能值在信号总线最小值和信号总线最大值之间。
+信号非使能值可以带有"0x"标识。
+信号非使能值可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000019000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="等线"/>
+            <charset val="134"/>
+          </rPr>
+          <t>网关需求报文。
+理论上，网关不会读取路由表中任何数据，如果网关需要读取其中某一些数据，就填写Yes，否则填写No，或者不填</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AC1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">分组类型，或者说分组模式、即多路复用。当你需要在一个报文矩阵中的同一个位置，塞入两个或以上的报文时，就需要采用多路复用，也就是分组功能。否则会出现报文id重复错误，或者出现报文重叠错误。
+请填入以下三种类型的数据：默认分组，分组标志位和组号。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>1、默认分组。</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+请填入 ：默认、默认分组、不分组、Default、DefaultGroup、single 或者你干脆直接空着不填(</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>推荐默认分组直接不填</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>)（注意：是叫你不填，并不不是让你填写0）。默认分组就表示最基本的状态，如果该帧报文全是默认分组，则只可以表示64bit的数据。如果该帧报文同时还存在其他分组报文，那么默认分组的报文会出现在所有的分组中，并且位置一致</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">。就是说，当不同分组的报文发过来的时候，默认分组的报文都存在。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">2、分组标志位。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">请填入：分组标志位、标志位、GroupFlag、Flag。即可被识别成标志位。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>一个报文只可以有一个分组标志位。</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+标志位用于储存并表示当前报文的组号。虽然有了分组，信号就可以在该帧同一个位置表示多个数据，但是一次只能发送一个分组的数据，只能同时激活一组数据(当然，默认分组会一直处于激活状态)。故标志位就是用于表示该组数据的组号。不同分组的报文发过来的时候，分组标志位也不同。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">3、组号。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请填入：“组号：67(替换成你的组号)”，“Num：50(替换成你的组号)”,“32(或者你直接填写一个数字也是可以的)”。</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>推荐直接填写数字组号即可，只能填写大于等于0的整型数。</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+组号用于标注分组，实现在8*8矩阵的同一个位置放上好几个数据。当当前报文的分组标志位是67时，只激活组号67的报文，程序按照组号67的规则来解析，以此类推。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AD1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001B000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入报文发送的快速周期。
+请确定报文发送的快速周期为10进制正整数。
+报文发送的快速周期可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AE1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001C000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入报文快速发送的次数。
+请确定报文快速发送的次数为10进制正整数。
+报文快速发送的次数可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AF1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001D000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入报文延时时间。
+请确定报文延时时间为10进制正整数。
+报文延时时间可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AG1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001E000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>如果是发送节点，在报文所在行、节点所在列对应的单元格输入"s"。
+如果是接收节点，在报文所在行、节点所在列对应的单元格输入"r"。
+请确定报文一定有发送节点。
+信号可以没有接受节点。
+节点名称，以字母或下划线开头，并且只可能进一步由26个字母、数字和下划线组成，长度不得超过32个字符。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="1" shapeId="0" xr:uid="{24EEFAFB-6A0F-4942-BA1F-8B2C15165DF7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="等线"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Normal 类型包括 Extended 和 Standard  。
+并且现程序根据id自动判断扩展帧 Extended 和标准帧 Standard ，故不必特地填写扩展帧</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="1" shapeId="0" xr:uid="{222AE9C2-F0E7-470E-81F0-83082A08FAD3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="36"/>
+            <rFont val="Microsoft YaHei UI"/>
+            <charset val="134"/>
+          </rPr>
+          <t>注释不可以写到这里</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>作者</author>
+    <author>石李城</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入报文名称。
+1、以字母或下划线开头，并且只可能进一步由26个字母、数字和下划线组成。
+2、长度最多为128个字符。为了与较旧的工具兼容，长度不得超过32个字符。
+3、报文名称中请不要使用换行符、空格等无效格式。
+4、请一定填写报文名称，报文名称不能为空。
+5、请不要填写重复的报文名称。
+6、信号逐行填写，报文信息只填写在属于该报文的信号的第一行。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入报文类型。
+报文类型只能为：Normal,NM,Diag,Extended,Standard   中的一个。
+Normal 类型包括 Extended 和 Standard  。
+并且现程序根据id自动判断扩展帧 Extended 和标准帧 Standard ，故不必特地填写扩展帧
+请一定填写报文类型，报文类型不能为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">请输入11位的报文ID。
+1、请确定报文ID为16进制正整数。
+2、报文ID可以带有"0x"标识，也可以不带“0x”。
+3、请一定填写报文ID，报文ID不能为空。报文ID不能重复。
+4、标准帧范围0x0~0x7FF; 扩展帧范围0x0~0x1FFF_FFFF，现改为范围0x7FF~0x1FFF_FFFF。
+5、注意: 标准帧0x211那么在DBC编码里它就是0x211的十进制表示。如果是扩展帧，0x211就会变成0x211+0x8000_0000然后再变成十进制存储。DBC编码由此来识别是扩展帧还是标准帧。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <strike/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>6、 如果协议中只填写了报文ID且小于0x7FF，那么DBC编码的时候可以识别成标准帧也可以识别成扩展帧，程序将无法正确识别。</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+7、现程序自动将范围0x0~0x7FF识别成标准帧。范围0x7FF~0x1FFF_FFFF，识别成扩展帧。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入报文发送类型。
+报文发送类型只能为：Cycle,Event, IfActive,CE,CA    中的一个。
+请确定大小写与建议值保持一致。
+请一定填写报文发送类型，报文发送类型不能为空，事件型 Event 报文可以可以不写周期。
+Cycle:周期型，按照一定周期循环发送
+Event:事件型，触发事件后，仅发送一次
+IfActive:事件周期型，触发事件后，按照周期循环发送一定次数
+当信号所在报文的发送类型为"Cycle"时，信号发送类型只能为"Cycle"。
+报文发送类型为"Event"时，报文中至少有一个信号的发送类型为"Event"。
+报文发送类型为"IfActive"时，报文中至少有一个信号的发送类型为"IfActive"。
+报文发送类型为"CE"时，报文中至少有一个信号的发送类型为"Event"。
+报文发送类型为"CA"时，报文中至少有一个信号的发送类型为"IfActive"。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入报文周期时间。
+请确定报文周期时间为10进制正整数。
+当是事件型报文时，报文周期时间可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入报文长度。
+请确定报文长度为10进制正整数。
+报文长度最好不要超过8。
+请一定填写报文长度，报文长度不能为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000007000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号名称。
+信号名称只能为数字、下划线、字母，长度不能超过32个字符。
+信号名称中请不要使用换行符、空格等无效格式。
+请一定填写信号名称，信号名称不能为空。
+信号信息逐行填写。
+请不要填写重复的信号名称。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号描述。
+信号描述请不要使用","（英文逗号）和";"（英文分号）等无效格式。
+信号描述可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000009000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号排列格式。
+1、信号排列格式只能为： Intel,Motorola LSB,Motorola MSB     中的一种。
+2、请一定填写信号排列格式，信号排列格式不能为空，为空则默认为英特尔格式。
+3、英特尔格式,数据的最低位存放在矩阵的最低位。
+4、摩托罗拉格式,数据最低位存放在矩阵的高位。
+5、Motorola_MSB  ;该格式与 DBC 文件(即用txt打开)的格式保持一致 ，即信号的起始位是 数据最低位 ，在矩阵中的位置是 MSB
+6、Motorola_LSB   ;该格式与 CANdb++ 软件中的格式一致 ，即信号的起始位是 数据最高位 ，在矩阵中的位置是 LSB 
+7、例如：同样占据矩阵中01234567这8个bit的信号。
+Intel 格式的数据最低位是0，起始位是0；
+Motorola_MSB 格式，数据最低位是7，起始位则是7;
+Motorola LSB 格式，数据最低位还是7，但是起始位和 Intel 格式一样是 0 ;</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="J1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000A000000}">
       <text>
         <r>
@@ -2585,12 +2728,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="232">
   <si>
     <t>测试协议</t>
   </si>
   <si>
     <t>DBC英文名</t>
+  </si>
+  <si>
+    <t>DBC描述</t>
   </si>
   <si>
     <t>DBC页面名称</t>
@@ -2755,12 +2901,6 @@
     <t>Event</t>
   </si>
   <si>
-    <t>报文的注释可以写到这里</t>
-  </si>
-  <si>
-    <t>报文的注释也也也也可以写到这里</t>
-  </si>
-  <si>
     <t>可以在这里填写报文的备注</t>
   </si>
   <si>
@@ -2837,9 +2977,6 @@
   </si>
   <si>
     <t>Cycle</t>
-  </si>
-  <si>
-    <t>上装发给中控屏1(发给网关，网关转给中控屏)</t>
   </si>
   <si>
     <t>CabinToCCS1_FactoryID</t>
@@ -2918,9 +3055,6 @@
     <t>0x1898ffff</t>
   </si>
   <si>
-    <t>摩托罗拉格式请参照这一帧报文来编写</t>
-  </si>
-  <si>
     <t xml:space="preserve">          </t>
   </si>
   <si>
@@ -3228,9 +3362,6 @@
     <t>sig1_2</t>
   </si>
   <si>
-    <t>CCSToCabin2</t>
-  </si>
-  <si>
     <t>0x180201AB</t>
   </si>
   <si>
@@ -3279,19 +3410,59 @@
     <phoneticPr fontId="44" type="noConversion"/>
   </si>
   <si>
-    <t>SignalSendType
-信号发送类型（必填）9</t>
+    <t>Signed</t>
+  </si>
+  <si>
+    <t>CCSToCabin2</t>
     <phoneticPr fontId="44" type="noConversion"/>
   </si>
   <si>
-    <t>DataType
-数据类型(必填)13</t>
+    <t>自定义属性名称</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>GwUsedMsg</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>GwUsedMsg
+网关需求报文(非必填)</t>
     <phoneticPr fontId="44" type="noConversion"/>
   </si>
   <si>
-    <t>InitialValuePhys
-物理初始值（必填）18</t>
-    <phoneticPr fontId="44" type="noConversion"/>
+    <t>自定义属性描述</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>网关需求报文</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enumeration</t>
+  </si>
+  <si>
+    <t>自定义属性作用域</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义属性值类型</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义属性最小值</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义属性最大值</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义属性默认值</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义属性枚举表</t>
+    <phoneticPr fontId="48" type="noConversion"/>
   </si>
   <si>
     <t>SignalMinValueHex
@@ -3299,89 +3470,22 @@
     <phoneticPr fontId="44" type="noConversion"/>
   </si>
   <si>
+    <t>SignalMaxValueHex
+总线最大值（十六进制）（非必填）20</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>InitialValueHex
+总线初始值（十六进制）（必填）21</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
     <t>InvalidValueHex
 总线无效值（十六进制）（非必填）22</t>
     <phoneticPr fontId="44" type="noConversion"/>
   </si>
   <si>
-    <t>SignalName
-信号名称（必填）6
-绿色项的内容是必填项，其余项可以不填</t>
-    <phoneticPr fontId="44" type="noConversion"/>
-  </si>
-  <si>
-    <t>SignalDescription
-信号描述(SignalComment 信号注释)（非必填）7</t>
-    <phoneticPr fontId="44" type="noConversion"/>
-  </si>
-  <si>
-    <t>GroupType 
-分组类型</t>
-    <phoneticPr fontId="44" type="noConversion"/>
-  </si>
-  <si>
-    <t>IfActive</t>
-  </si>
-  <si>
-    <t>StartBit
-起始位(必填)11</t>
-    <phoneticPr fontId="44" type="noConversion"/>
-  </si>
-  <si>
-    <t>BitLength(Bit)
-信号长度(必填)12</t>
-    <phoneticPr fontId="44" type="noConversion"/>
-  </si>
-  <si>
-    <t>Resolution 分辨率; 
-精度(必填)Factor14</t>
-    <phoneticPr fontId="44" type="noConversion"/>
-  </si>
-  <si>
-    <t>Offset
-偏移量(必填)15</t>
-    <phoneticPr fontId="44" type="noConversion"/>
-  </si>
-  <si>
-    <t>SignalMinValuePhys
-物理最小值(必填)16</t>
-    <phoneticPr fontId="44" type="noConversion"/>
-  </si>
-  <si>
-    <t>SignalMaxValuePhys
-物理最大值(非必填)17</t>
-    <phoneticPr fontId="44" type="noConversion"/>
-  </si>
-  <si>
-    <t>DBC描述</t>
-    <phoneticPr fontId="44" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点列表</t>
-    <phoneticPr fontId="44" type="noConversion"/>
-  </si>
-  <si>
-    <t>CCS</t>
-    <phoneticPr fontId="44" type="noConversion"/>
-  </si>
-  <si>
-    <t>CCS, GW</t>
-    <phoneticPr fontId="44" type="noConversion"/>
-  </si>
-  <si>
-    <t>波特率（单位：Kbps）</t>
-    <phoneticPr fontId="44" type="noConversion"/>
-  </si>
-  <si>
-    <t>DBC版本</t>
-    <phoneticPr fontId="44" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.0.0</t>
-    <phoneticPr fontId="44" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.0.1</t>
+    <t>counter自动累加,从0加到255,然后循环，初始值为0，每次报文发送成功(收到ACK)以后，Counter加1；在Busoff出现恢复后，按照off前的值加1继续发送; ECU Reset 以后，Counter值清零。</t>
     <phoneticPr fontId="44" type="noConversion"/>
   </si>
 </sst>
@@ -3392,7 +3496,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$¥-804]#,##0.0000000000000;[$¥-804]\-#,##0.0000000000000"/>
   </numFmts>
-  <fonts count="49" x14ac:knownFonts="1">
+  <fonts count="53" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3693,10 +3797,25 @@
     <font>
       <b/>
       <sz val="14"/>
-      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -3707,8 +3826,23 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="12"/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="2"/>
@@ -4063,7 +4197,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4186,31 +4320,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="5" borderId="1" xfId="29" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="52" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="38">
@@ -4538,15 +4663,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="51" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B1" s="51" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="51" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
@@ -4559,75 +4684,125 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A3D3AA-9247-454A-9796-2078BC41A26D}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
+    <col min="2" max="2" width="14.75" customWidth="1"/>
+    <col min="3" max="3" width="23.25" customWidth="1"/>
+    <col min="4" max="4" width="19.375" customWidth="1"/>
+    <col min="5" max="5" width="16.375" customWidth="1"/>
+    <col min="6" max="6" width="17.875" customWidth="1"/>
+    <col min="7" max="7" width="17.125" customWidth="1"/>
+    <col min="8" max="8" width="16.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="55" t="s">
+        <v>215</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>222</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>223</v>
+      </c>
+      <c r="F1" s="55" t="s">
+        <v>224</v>
+      </c>
+      <c r="G1" s="55" t="s">
+        <v>225</v>
+      </c>
+      <c r="H1" s="55" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="55" t="s">
+        <v>216</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56" t="s">
+        <v>220</v>
+      </c>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="56"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="48" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{50F88472-F2AC-41AE-A38C-683DE1D8CB7E}">
+      <formula1>"Integer, Float, String, Enumeration, Hex "</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="13.25" customWidth="1"/>
-    <col min="3" max="3" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="12.625" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="25.625" style="57" customWidth="1"/>
+    <col min="1" max="1" width="13.25" customWidth="1"/>
+    <col min="2" max="2" width="14.875" customWidth="1"/>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="58" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="59" t="s">
-        <v>237</v>
-      </c>
-      <c r="C1" s="59" t="s">
-        <v>232</v>
-      </c>
-      <c r="D1" s="58" t="s">
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="59" t="s">
-        <v>233</v>
-      </c>
-      <c r="F1" s="60" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="58" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="59" t="s">
-        <v>238</v>
-      </c>
-      <c r="C2" s="58" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="59" t="s">
-        <v>235</v>
-      </c>
-      <c r="F2" s="61">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="58" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="59" t="s">
-        <v>239</v>
-      </c>
-      <c r="C3" s="58" t="s">
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="58" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="59" t="s">
-        <v>235</v>
-      </c>
-      <c r="F3" s="61">
-        <v>500</v>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4636,7 +4811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AH95"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.149999999999999" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
@@ -4673,120 +4848,120 @@
   <sheetData>
     <row r="1" spans="1:34" s="23" customFormat="1" ht="143.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="28" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="53" t="s">
-        <v>222</v>
-      </c>
-      <c r="H1" s="52" t="s">
-        <v>223</v>
+        <v>13</v>
+      </c>
+      <c r="G1" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>15</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="52" t="s">
-        <v>217</v>
+        <v>16</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>17</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L1" s="28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M1" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="N1" s="52" t="s">
-        <v>218</v>
+        <v>20</v>
+      </c>
+      <c r="N1" s="30" t="s">
+        <v>21</v>
       </c>
       <c r="O1" s="28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P1" s="28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q1" s="30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R1" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="52" t="s">
-        <v>219</v>
-      </c>
-      <c r="T1" s="52" t="s">
-        <v>220</v>
+        <v>25</v>
+      </c>
+      <c r="S1" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="T1" s="30" t="s">
+        <v>27</v>
       </c>
       <c r="U1" s="30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V1" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W1" s="30" t="s">
-        <v>221</v>
+        <v>30</v>
       </c>
       <c r="X1" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y1" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Z1" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA1" s="30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AB1" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC1" s="52" t="s">
-        <v>224</v>
+        <v>35</v>
+      </c>
+      <c r="AC1" s="30" t="s">
+        <v>36</v>
       </c>
       <c r="AD1" s="49" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE1" s="49" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AF1" s="49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AG1" s="34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AH1" s="34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="23" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" s="31">
         <v>100</v>
@@ -4794,12 +4969,8 @@
       <c r="F2" s="31">
         <v>8</v>
       </c>
-      <c r="G2" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="H2" s="31" t="s">
-        <v>46</v>
-      </c>
+      <c r="G2" s="32"/>
+      <c r="H2" s="31"/>
       <c r="I2" s="31"/>
       <c r="J2" s="31"/>
       <c r="K2" s="31"/>
@@ -4818,21 +4989,21 @@
       <c r="X2" s="31"/>
       <c r="Y2" s="31"/>
       <c r="Z2" s="31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA2" s="31"/>
       <c r="AB2" s="31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AC2" s="31"/>
       <c r="AD2" s="34"/>
       <c r="AE2" s="34"/>
       <c r="AF2" s="34"/>
       <c r="AG2" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH2" s="34" t="s">
         <v>49</v>
-      </c>
-      <c r="AH2" s="34" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:34" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -4843,28 +5014,28 @@
       <c r="E3" s="34"/>
       <c r="F3" s="33"/>
       <c r="G3" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="I3" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="I3" s="44" t="s">
+      <c r="J3" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="44" t="s">
+      <c r="K3" s="45">
+        <v>0</v>
+      </c>
+      <c r="L3" s="45">
+        <v>0</v>
+      </c>
+      <c r="M3" s="45">
+        <v>8</v>
+      </c>
+      <c r="N3" s="46" t="s">
         <v>54</v>
-      </c>
-      <c r="K3" s="45">
-        <v>0</v>
-      </c>
-      <c r="L3" s="45">
-        <v>0</v>
-      </c>
-      <c r="M3" s="45">
-        <v>8</v>
-      </c>
-      <c r="N3" s="46" t="s">
-        <v>55</v>
       </c>
       <c r="O3" s="45">
         <v>1</v>
@@ -4893,14 +5064,14 @@
       <c r="W3" s="34"/>
       <c r="X3" s="34"/>
       <c r="Y3" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z3" s="33" t="s">
         <v>56</v>
-      </c>
-      <c r="Z3" s="33" t="s">
-        <v>57</v>
       </c>
       <c r="AA3" s="34"/>
       <c r="AB3" s="33"/>
-      <c r="AC3" s="44"/>
+      <c r="AC3" s="52"/>
       <c r="AD3" s="33"/>
       <c r="AE3" s="33"/>
       <c r="AF3" s="33"/>
@@ -4915,16 +5086,16 @@
       <c r="E4" s="34"/>
       <c r="F4" s="33"/>
       <c r="G4" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="36" t="s">
-        <v>59</v>
-      </c>
       <c r="I4" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" s="44" t="s">
         <v>53</v>
-      </c>
-      <c r="J4" s="44" t="s">
-        <v>54</v>
       </c>
       <c r="K4" s="34">
         <v>1</v>
@@ -4936,7 +5107,7 @@
         <v>2</v>
       </c>
       <c r="N4" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O4" s="45">
         <v>1</v>
@@ -4967,14 +5138,14 @@
       </c>
       <c r="X4" s="34"/>
       <c r="Y4" s="36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Z4" s="33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AA4" s="34"/>
       <c r="AB4" s="33"/>
-      <c r="AC4" s="44"/>
+      <c r="AC4" s="52"/>
       <c r="AD4" s="33"/>
       <c r="AE4" s="33"/>
       <c r="AF4" s="33"/>
@@ -4989,16 +5160,16 @@
       <c r="E5" s="34"/>
       <c r="F5" s="33"/>
       <c r="G5" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="33" t="s">
-        <v>62</v>
-      </c>
       <c r="I5" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="44" t="s">
         <v>53</v>
-      </c>
-      <c r="J5" s="44" t="s">
-        <v>54</v>
       </c>
       <c r="K5" s="34">
         <v>2</v>
@@ -5010,7 +5181,7 @@
         <v>4</v>
       </c>
       <c r="N5" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O5" s="45">
         <v>1</v>
@@ -5041,14 +5212,14 @@
       </c>
       <c r="X5" s="34"/>
       <c r="Y5" s="36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Z5" s="33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AA5" s="34"/>
       <c r="AB5" s="33"/>
-      <c r="AC5" s="44"/>
+      <c r="AC5" s="52"/>
       <c r="AD5" s="33"/>
       <c r="AE5" s="33"/>
       <c r="AF5" s="33"/>
@@ -5063,16 +5234,16 @@
       <c r="E6" s="34"/>
       <c r="F6" s="33"/>
       <c r="G6" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="H6" s="36" t="s">
-        <v>65</v>
-      </c>
       <c r="I6" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="44" t="s">
         <v>53</v>
-      </c>
-      <c r="J6" s="44" t="s">
-        <v>54</v>
       </c>
       <c r="K6" s="34">
         <v>2</v>
@@ -5084,7 +5255,7 @@
         <v>4</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O6" s="45">
         <v>1</v>
@@ -5115,14 +5286,14 @@
       </c>
       <c r="X6" s="34"/>
       <c r="Y6" s="36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AA6" s="34"/>
       <c r="AB6" s="33"/>
-      <c r="AC6" s="44"/>
+      <c r="AC6" s="52"/>
       <c r="AD6" s="33"/>
       <c r="AE6" s="33"/>
       <c r="AF6" s="33"/>
@@ -5137,16 +5308,16 @@
       <c r="E7" s="34"/>
       <c r="F7" s="33"/>
       <c r="G7" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="36" t="s">
-        <v>68</v>
-      </c>
       <c r="I7" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="44" t="s">
         <v>53</v>
-      </c>
-      <c r="J7" s="44" t="s">
-        <v>54</v>
       </c>
       <c r="K7" s="34"/>
       <c r="L7" s="34">
@@ -5156,7 +5327,7 @@
         <v>8</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O7" s="45">
         <v>1</v>
@@ -5185,16 +5356,16 @@
     </row>
     <row r="8" spans="1:34" s="24" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="C8" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="D8" s="37" t="s">
         <v>71</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>72</v>
       </c>
       <c r="E8" s="37">
         <v>100</v>
@@ -5202,12 +5373,8 @@
       <c r="F8" s="37">
         <v>8</v>
       </c>
-      <c r="G8" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>73</v>
-      </c>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
       <c r="I8" s="37"/>
       <c r="J8" s="47"/>
       <c r="K8" s="37"/>
@@ -5228,17 +5395,17 @@
       <c r="Z8" s="37"/>
       <c r="AA8" s="37"/>
       <c r="AB8" s="37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AC8" s="47"/>
       <c r="AD8" s="34"/>
       <c r="AE8" s="34"/>
       <c r="AF8" s="50"/>
       <c r="AG8" s="50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AH8" s="50" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -5249,16 +5416,16 @@
       <c r="E9" s="34"/>
       <c r="F9" s="33"/>
       <c r="G9" s="33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H9" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="44" t="s">
-        <v>53</v>
-      </c>
       <c r="J9" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K9" s="45">
         <v>0</v>
@@ -5270,7 +5437,7 @@
         <v>8</v>
       </c>
       <c r="N9" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O9" s="45">
         <v>1</v>
@@ -5299,12 +5466,12 @@
       <c r="W9" s="34"/>
       <c r="X9" s="34"/>
       <c r="Y9" s="33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z9" s="33"/>
       <c r="AA9" s="34"/>
       <c r="AB9" s="33"/>
-      <c r="AC9" s="44"/>
+      <c r="AC9" s="52"/>
       <c r="AD9" s="33"/>
       <c r="AE9" s="33"/>
       <c r="AF9" s="33"/>
@@ -5319,16 +5486,16 @@
       <c r="E10" s="34"/>
       <c r="F10" s="33"/>
       <c r="G10" s="33" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H10" s="36" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J10" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K10" s="34">
         <v>1</v>
@@ -5341,7 +5508,7 @@
         <v>8</v>
       </c>
       <c r="N10" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O10" s="45">
         <v>1</v>
@@ -5388,16 +5555,16 @@
       <c r="E11" s="34"/>
       <c r="F11" s="33"/>
       <c r="G11" s="33" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H11" s="36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K11" s="34">
         <v>2</v>
@@ -5410,7 +5577,7 @@
         <v>4</v>
       </c>
       <c r="N11" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O11" s="45">
         <v>1</v>
@@ -5439,7 +5606,7 @@
       <c r="W11" s="34"/>
       <c r="X11" s="34"/>
       <c r="Y11" s="36" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Z11" s="36"/>
       <c r="AA11" s="34"/>
@@ -5459,16 +5626,16 @@
       <c r="E12" s="34"/>
       <c r="F12" s="33"/>
       <c r="G12" s="33" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K12" s="34">
         <v>2</v>
@@ -5480,7 +5647,7 @@
         <v>4</v>
       </c>
       <c r="N12" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O12" s="45">
         <v>1</v>
@@ -5508,10 +5675,10 @@
       </c>
       <c r="W12" s="34"/>
       <c r="X12" s="34" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="Y12" s="36" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Z12" s="36"/>
       <c r="AA12" s="34"/>
@@ -5531,16 +5698,16 @@
       <c r="E13" s="34"/>
       <c r="F13" s="33"/>
       <c r="G13" s="33" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H13" s="36" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K13" s="34">
         <v>3</v>
@@ -5552,7 +5719,7 @@
         <v>2</v>
       </c>
       <c r="N13" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O13" s="45">
         <v>1</v>
@@ -5581,7 +5748,7 @@
       <c r="W13" s="34"/>
       <c r="X13" s="34"/>
       <c r="Y13" s="36" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Z13" s="36"/>
       <c r="AA13" s="34"/>
@@ -5601,16 +5768,16 @@
       <c r="E14" s="34"/>
       <c r="F14" s="33"/>
       <c r="G14" s="33" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H14" s="36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K14" s="34">
         <v>3</v>
@@ -5622,7 +5789,7 @@
         <v>2</v>
       </c>
       <c r="N14" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O14" s="45">
         <v>1</v>
@@ -5651,7 +5818,7 @@
       <c r="W14" s="34"/>
       <c r="X14" s="34"/>
       <c r="Y14" s="36" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="Z14" s="36"/>
       <c r="AA14" s="34"/>
@@ -5671,16 +5838,16 @@
       <c r="E15" s="34"/>
       <c r="F15" s="33"/>
       <c r="G15" s="33" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K15" s="34">
         <v>3</v>
@@ -5692,7 +5859,7 @@
         <v>2</v>
       </c>
       <c r="N15" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O15" s="45">
         <v>1</v>
@@ -5715,7 +5882,7 @@
       <c r="W15" s="34"/>
       <c r="X15" s="34"/>
       <c r="Y15" s="36" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="Z15" s="36"/>
       <c r="AA15" s="34"/>
@@ -5735,16 +5902,16 @@
       <c r="E16" s="34"/>
       <c r="F16" s="33"/>
       <c r="G16" s="33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K16" s="34">
         <v>7</v>
@@ -5756,7 +5923,7 @@
         <v>8</v>
       </c>
       <c r="N16" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O16" s="45">
         <v>1</v>
@@ -5785,7 +5952,7 @@
       <c r="W16" s="34"/>
       <c r="X16" s="34"/>
       <c r="Y16" s="36" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Z16" s="36"/>
       <c r="AA16" s="34"/>
@@ -5799,16 +5966,16 @@
     </row>
     <row r="17" spans="1:34" s="25" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="39" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E17" s="39">
         <v>50</v>
@@ -5817,9 +5984,7 @@
         <v>8</v>
       </c>
       <c r="G17" s="39"/>
-      <c r="H17" s="39" t="s">
-        <v>98</v>
-      </c>
+      <c r="H17" s="39"/>
       <c r="I17" s="39"/>
       <c r="J17" s="39"/>
       <c r="K17" s="39"/>
@@ -5840,7 +6005,7 @@
       <c r="Z17" s="39"/>
       <c r="AA17" s="39"/>
       <c r="AB17" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AC17" s="39"/>
       <c r="AD17" s="34"/>
@@ -5851,7 +6016,7 @@
     </row>
     <row r="18" spans="1:34" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A18" s="33" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
@@ -5859,16 +6024,16 @@
       <c r="E18" s="34"/>
       <c r="F18" s="33"/>
       <c r="G18" s="33" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H18" s="38" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I18" s="44" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J18" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K18" s="33"/>
       <c r="L18" s="34">
@@ -5878,7 +6043,7 @@
         <v>8</v>
       </c>
       <c r="N18" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O18" s="34">
         <v>1</v>
@@ -5907,7 +6072,7 @@
     </row>
     <row r="19" spans="1:34" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A19" s="33" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B19" s="33"/>
       <c r="C19" s="33"/>
@@ -5915,14 +6080,14 @@
       <c r="E19" s="34"/>
       <c r="F19" s="33"/>
       <c r="G19" s="33" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H19" s="33"/>
       <c r="I19" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J19" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K19" s="33"/>
       <c r="L19" s="34">
@@ -5932,7 +6097,7 @@
         <v>8</v>
       </c>
       <c r="N19" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O19" s="34">
         <v>1</v>
@@ -5961,7 +6126,7 @@
     </row>
     <row r="20" spans="1:34" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A20" s="33" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B20" s="33"/>
       <c r="C20" s="33"/>
@@ -5969,14 +6134,14 @@
       <c r="E20" s="34"/>
       <c r="F20" s="33"/>
       <c r="G20" s="33" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H20" s="33"/>
       <c r="I20" s="44" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J20" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K20" s="33"/>
       <c r="L20" s="34">
@@ -5986,7 +6151,7 @@
         <v>8</v>
       </c>
       <c r="N20" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O20" s="34">
         <v>1</v>
@@ -6017,30 +6182,30 @@
       <c r="A21" s="33"/>
       <c r="B21" s="33"/>
       <c r="C21" s="33" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D21" s="33"/>
       <c r="E21" s="34"/>
       <c r="F21" s="33"/>
       <c r="G21" s="33" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H21" s="33"/>
       <c r="I21" s="44" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J21" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K21" s="33"/>
       <c r="L21" s="48" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="M21" s="34">
         <v>4</v>
       </c>
       <c r="N21" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O21" s="34">
         <v>1</v>
@@ -6075,24 +6240,24 @@
       <c r="E22" s="34"/>
       <c r="F22" s="33"/>
       <c r="G22" s="33" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H22" s="33"/>
       <c r="I22" s="44" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K22" s="33"/>
       <c r="L22" s="48" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M22" s="48" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="N22" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O22" s="34">
         <v>1</v>
@@ -6127,16 +6292,16 @@
       <c r="E23" s="34"/>
       <c r="F23" s="33"/>
       <c r="G23" s="33" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H23" s="38" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I23" s="44" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J23" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K23" s="34"/>
       <c r="L23" s="48">
@@ -6146,7 +6311,7 @@
         <v>16</v>
       </c>
       <c r="N23" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O23" s="34">
         <v>1</v>
@@ -6175,16 +6340,16 @@
     </row>
     <row r="24" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="40" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D24" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E24" s="41">
         <v>200</v>
@@ -6221,14 +6386,14 @@
       <c r="E25" s="43"/>
       <c r="F25" s="42"/>
       <c r="G25" s="42" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H25" s="42"/>
       <c r="I25" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J25" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K25" s="43"/>
       <c r="L25" s="43">
@@ -6238,7 +6403,7 @@
         <v>8</v>
       </c>
       <c r="N25" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O25" s="43">
         <v>1</v>
@@ -6265,14 +6430,14 @@
       <c r="E26" s="43"/>
       <c r="F26" s="42"/>
       <c r="G26" s="42" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H26" s="42"/>
       <c r="I26" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J26" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K26" s="43"/>
       <c r="L26" s="43">
@@ -6282,7 +6447,7 @@
         <v>8</v>
       </c>
       <c r="N26" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O26" s="43">
         <v>1</v>
@@ -6309,14 +6474,14 @@
       <c r="E27" s="43"/>
       <c r="F27" s="42"/>
       <c r="G27" s="42" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H27" s="42"/>
       <c r="I27" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J27" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K27" s="43"/>
       <c r="L27" s="43">
@@ -6326,7 +6491,7 @@
         <v>8</v>
       </c>
       <c r="N27" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O27" s="43">
         <v>1</v>
@@ -6353,14 +6518,14 @@
       <c r="E28" s="43"/>
       <c r="F28" s="42"/>
       <c r="G28" s="42" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H28" s="42"/>
       <c r="I28" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J28" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K28" s="43"/>
       <c r="L28" s="43">
@@ -6370,7 +6535,7 @@
         <v>8</v>
       </c>
       <c r="N28" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O28" s="43">
         <v>1</v>
@@ -6397,14 +6562,14 @@
       <c r="E29" s="43"/>
       <c r="F29" s="42"/>
       <c r="G29" s="42" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H29" s="42"/>
       <c r="I29" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J29" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K29" s="43"/>
       <c r="L29" s="43">
@@ -6414,7 +6579,7 @@
         <v>8</v>
       </c>
       <c r="N29" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O29" s="43">
         <v>0.2</v>
@@ -6441,14 +6606,14 @@
       <c r="E30" s="43"/>
       <c r="F30" s="42"/>
       <c r="G30" s="42" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H30" s="42"/>
       <c r="I30" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J30" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K30" s="43"/>
       <c r="L30" s="43">
@@ -6458,7 +6623,7 @@
         <v>8</v>
       </c>
       <c r="N30" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O30" s="43">
         <v>0.5</v>
@@ -6485,14 +6650,14 @@
       <c r="E31" s="43"/>
       <c r="F31" s="42"/>
       <c r="G31" s="42" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H31" s="42"/>
       <c r="I31" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J31" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K31" s="43"/>
       <c r="L31" s="43">
@@ -6502,7 +6667,7 @@
         <v>8</v>
       </c>
       <c r="N31" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O31" s="43">
         <v>0.1</v>
@@ -6529,14 +6694,14 @@
       <c r="E32" s="43"/>
       <c r="F32" s="42"/>
       <c r="G32" s="42" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H32" s="42"/>
       <c r="I32" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J32" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K32" s="43"/>
       <c r="L32" s="43">
@@ -6546,7 +6711,7 @@
         <v>8</v>
       </c>
       <c r="N32" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O32" s="43">
         <v>0.1</v>
@@ -6567,16 +6732,16 @@
     </row>
     <row r="33" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="40" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D33" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E33" s="41">
         <v>200</v>
@@ -6613,14 +6778,14 @@
       <c r="E34" s="43"/>
       <c r="F34" s="42"/>
       <c r="G34" s="42" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H34" s="42"/>
       <c r="I34" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J34" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K34" s="43"/>
       <c r="L34" s="43">
@@ -6630,7 +6795,7 @@
         <v>8</v>
       </c>
       <c r="N34" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O34" s="43">
         <v>1</v>
@@ -6657,14 +6822,14 @@
       <c r="E35" s="43"/>
       <c r="F35" s="42"/>
       <c r="G35" s="42" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H35" s="42"/>
       <c r="I35" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J35" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K35" s="43"/>
       <c r="L35" s="43">
@@ -6674,7 +6839,7 @@
         <v>8</v>
       </c>
       <c r="N35" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O35" s="43">
         <v>1</v>
@@ -6701,14 +6866,14 @@
       <c r="E36" s="43"/>
       <c r="F36" s="42"/>
       <c r="G36" s="42" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H36" s="42"/>
       <c r="I36" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J36" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K36" s="43"/>
       <c r="L36" s="43">
@@ -6718,7 +6883,7 @@
         <v>8</v>
       </c>
       <c r="N36" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O36" s="43">
         <v>1</v>
@@ -6745,14 +6910,14 @@
       <c r="E37" s="43"/>
       <c r="F37" s="42"/>
       <c r="G37" s="42" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H37" s="42"/>
       <c r="I37" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J37" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K37" s="43"/>
       <c r="L37" s="43">
@@ -6762,7 +6927,7 @@
         <v>8</v>
       </c>
       <c r="N37" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O37" s="43">
         <v>1</v>
@@ -6789,14 +6954,14 @@
       <c r="E38" s="43"/>
       <c r="F38" s="42"/>
       <c r="G38" s="42" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H38" s="42"/>
       <c r="I38" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J38" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K38" s="43"/>
       <c r="L38" s="43">
@@ -6806,7 +6971,7 @@
         <v>8</v>
       </c>
       <c r="N38" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O38" s="43">
         <v>1</v>
@@ -6833,14 +6998,14 @@
       <c r="E39" s="43"/>
       <c r="F39" s="42"/>
       <c r="G39" s="42" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H39" s="42"/>
       <c r="I39" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J39" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K39" s="43"/>
       <c r="L39" s="43">
@@ -6850,7 +7015,7 @@
         <v>8</v>
       </c>
       <c r="N39" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O39" s="43">
         <v>1</v>
@@ -6877,14 +7042,14 @@
       <c r="E40" s="43"/>
       <c r="F40" s="42"/>
       <c r="G40" s="42" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H40" s="42"/>
       <c r="I40" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J40" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K40" s="43"/>
       <c r="L40" s="43">
@@ -6894,7 +7059,7 @@
         <v>8</v>
       </c>
       <c r="N40" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O40" s="43">
         <v>1</v>
@@ -6921,14 +7086,14 @@
       <c r="E41" s="43"/>
       <c r="F41" s="42"/>
       <c r="G41" s="42" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H41" s="42"/>
       <c r="I41" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J41" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K41" s="43"/>
       <c r="L41" s="43">
@@ -6938,7 +7103,7 @@
         <v>8</v>
       </c>
       <c r="N41" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O41" s="43">
         <v>1</v>
@@ -6959,16 +7124,16 @@
     </row>
     <row r="42" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="40" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C42" s="40" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D42" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E42" s="41">
         <v>200</v>
@@ -7005,14 +7170,14 @@
       <c r="E43" s="43"/>
       <c r="F43" s="42"/>
       <c r="G43" s="42" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H43" s="42"/>
       <c r="I43" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J43" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K43" s="43"/>
       <c r="L43" s="43">
@@ -7022,7 +7187,7 @@
         <v>8</v>
       </c>
       <c r="N43" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O43" s="43">
         <v>1</v>
@@ -7049,14 +7214,14 @@
       <c r="E44" s="43"/>
       <c r="F44" s="42"/>
       <c r="G44" s="42" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H44" s="42"/>
       <c r="I44" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J44" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K44" s="43"/>
       <c r="L44" s="43">
@@ -7066,7 +7231,7 @@
         <v>8</v>
       </c>
       <c r="N44" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O44" s="43">
         <v>1</v>
@@ -7093,14 +7258,14 @@
       <c r="E45" s="43"/>
       <c r="F45" s="42"/>
       <c r="G45" s="42" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H45" s="42"/>
       <c r="I45" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J45" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K45" s="43"/>
       <c r="L45" s="43">
@@ -7110,7 +7275,7 @@
         <v>8</v>
       </c>
       <c r="N45" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O45" s="43">
         <v>1</v>
@@ -7137,14 +7302,14 @@
       <c r="E46" s="43"/>
       <c r="F46" s="42"/>
       <c r="G46" s="42" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H46" s="42"/>
       <c r="I46" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J46" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K46" s="43"/>
       <c r="L46" s="43">
@@ -7154,7 +7319,7 @@
         <v>8</v>
       </c>
       <c r="N46" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O46" s="43">
         <v>1</v>
@@ -7181,14 +7346,14 @@
       <c r="E47" s="43"/>
       <c r="F47" s="42"/>
       <c r="G47" s="42" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H47" s="42"/>
       <c r="I47" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J47" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K47" s="43"/>
       <c r="L47" s="43">
@@ -7198,7 +7363,7 @@
         <v>8</v>
       </c>
       <c r="N47" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O47" s="43">
         <v>0.2</v>
@@ -7225,14 +7390,14 @@
       <c r="E48" s="43"/>
       <c r="F48" s="42"/>
       <c r="G48" s="42" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H48" s="42"/>
       <c r="I48" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J48" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K48" s="43"/>
       <c r="L48" s="43">
@@ -7242,7 +7407,7 @@
         <v>8</v>
       </c>
       <c r="N48" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O48" s="43">
         <v>0.5</v>
@@ -7269,14 +7434,14 @@
       <c r="E49" s="43"/>
       <c r="F49" s="42"/>
       <c r="G49" s="42" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H49" s="42"/>
       <c r="I49" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J49" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K49" s="43"/>
       <c r="L49" s="43">
@@ -7286,7 +7451,7 @@
         <v>8</v>
       </c>
       <c r="N49" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O49" s="43">
         <v>0.1</v>
@@ -7313,14 +7478,14 @@
       <c r="E50" s="43"/>
       <c r="F50" s="42"/>
       <c r="G50" s="42" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H50" s="42"/>
       <c r="I50" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J50" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K50" s="43"/>
       <c r="L50" s="43">
@@ -7330,7 +7495,7 @@
         <v>8</v>
       </c>
       <c r="N50" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O50" s="43">
         <v>0.1</v>
@@ -7351,16 +7516,16 @@
     </row>
     <row r="51" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="40" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C51" s="40" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E51" s="41">
         <v>200</v>
@@ -7397,14 +7562,14 @@
       <c r="E52" s="43"/>
       <c r="F52" s="42"/>
       <c r="G52" s="42" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H52" s="42"/>
       <c r="I52" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J52" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K52" s="43"/>
       <c r="L52" s="43">
@@ -7414,7 +7579,7 @@
         <v>8</v>
       </c>
       <c r="N52" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O52" s="43">
         <v>1</v>
@@ -7441,14 +7606,14 @@
       <c r="E53" s="43"/>
       <c r="F53" s="42"/>
       <c r="G53" s="42" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H53" s="42"/>
       <c r="I53" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J53" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K53" s="43"/>
       <c r="L53" s="43">
@@ -7458,7 +7623,7 @@
         <v>8</v>
       </c>
       <c r="N53" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O53" s="43">
         <v>1</v>
@@ -7485,14 +7650,14 @@
       <c r="E54" s="43"/>
       <c r="F54" s="42"/>
       <c r="G54" s="42" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H54" s="42"/>
       <c r="I54" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J54" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K54" s="43"/>
       <c r="L54" s="43">
@@ -7502,7 +7667,7 @@
         <v>8</v>
       </c>
       <c r="N54" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O54" s="43">
         <v>1</v>
@@ -7529,14 +7694,14 @@
       <c r="E55" s="43"/>
       <c r="F55" s="42"/>
       <c r="G55" s="42" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H55" s="42"/>
       <c r="I55" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J55" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K55" s="43"/>
       <c r="L55" s="43">
@@ -7546,7 +7711,7 @@
         <v>8</v>
       </c>
       <c r="N55" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O55" s="43">
         <v>1</v>
@@ -7573,14 +7738,14 @@
       <c r="E56" s="43"/>
       <c r="F56" s="42"/>
       <c r="G56" s="42" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H56" s="42"/>
       <c r="I56" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J56" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K56" s="43"/>
       <c r="L56" s="43">
@@ -7590,7 +7755,7 @@
         <v>8</v>
       </c>
       <c r="N56" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O56" s="43">
         <v>1</v>
@@ -7617,14 +7782,14 @@
       <c r="E57" s="43"/>
       <c r="F57" s="42"/>
       <c r="G57" s="42" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H57" s="42"/>
       <c r="I57" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J57" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K57" s="43"/>
       <c r="L57" s="43">
@@ -7634,7 +7799,7 @@
         <v>8</v>
       </c>
       <c r="N57" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O57" s="43">
         <v>1</v>
@@ -7661,14 +7826,14 @@
       <c r="E58" s="43"/>
       <c r="F58" s="42"/>
       <c r="G58" s="42" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H58" s="42"/>
       <c r="I58" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J58" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K58" s="43"/>
       <c r="L58" s="43">
@@ -7678,7 +7843,7 @@
         <v>8</v>
       </c>
       <c r="N58" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O58" s="43">
         <v>1</v>
@@ -7705,14 +7870,14 @@
       <c r="E59" s="43"/>
       <c r="F59" s="42"/>
       <c r="G59" s="42" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H59" s="42"/>
       <c r="I59" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J59" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K59" s="43"/>
       <c r="L59" s="43">
@@ -7722,7 +7887,7 @@
         <v>8</v>
       </c>
       <c r="N59" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O59" s="43">
         <v>1</v>
@@ -7743,16 +7908,16 @@
     </row>
     <row r="60" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="40" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B60" s="39" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C60" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D60" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E60" s="41">
         <v>200</v>
@@ -7789,14 +7954,14 @@
       <c r="E61" s="43"/>
       <c r="F61" s="42"/>
       <c r="G61" s="42" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H61" s="42"/>
       <c r="I61" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J61" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K61" s="43"/>
       <c r="L61" s="43">
@@ -7806,7 +7971,7 @@
         <v>8</v>
       </c>
       <c r="N61" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O61" s="43">
         <v>1</v>
@@ -7833,14 +7998,14 @@
       <c r="E62" s="43"/>
       <c r="F62" s="42"/>
       <c r="G62" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H62" s="42"/>
       <c r="I62" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J62" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K62" s="43"/>
       <c r="L62" s="43">
@@ -7850,7 +8015,7 @@
         <v>8</v>
       </c>
       <c r="N62" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O62" s="43">
         <v>1</v>
@@ -7877,14 +8042,14 @@
       <c r="E63" s="43"/>
       <c r="F63" s="42"/>
       <c r="G63" s="42" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H63" s="42"/>
       <c r="I63" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J63" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K63" s="43"/>
       <c r="L63" s="43">
@@ -7894,7 +8059,7 @@
         <v>8</v>
       </c>
       <c r="N63" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O63" s="43">
         <v>1</v>
@@ -7921,14 +8086,14 @@
       <c r="E64" s="43"/>
       <c r="F64" s="42"/>
       <c r="G64" s="42" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H64" s="42"/>
       <c r="I64" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J64" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K64" s="43"/>
       <c r="L64" s="43">
@@ -7938,7 +8103,7 @@
         <v>8</v>
       </c>
       <c r="N64" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O64" s="43">
         <v>1</v>
@@ -7965,14 +8130,14 @@
       <c r="E65" s="43"/>
       <c r="F65" s="42"/>
       <c r="G65" s="42" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H65" s="42"/>
       <c r="I65" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J65" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K65" s="43"/>
       <c r="L65" s="43">
@@ -7982,7 +8147,7 @@
         <v>8</v>
       </c>
       <c r="N65" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O65" s="43">
         <v>0.1</v>
@@ -8009,14 +8174,14 @@
       <c r="E66" s="43"/>
       <c r="F66" s="42"/>
       <c r="G66" s="42" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H66" s="42"/>
       <c r="I66" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J66" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K66" s="43"/>
       <c r="L66" s="43">
@@ -8026,7 +8191,7 @@
         <v>8</v>
       </c>
       <c r="N66" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O66" s="43">
         <v>0.5</v>
@@ -8053,14 +8218,14 @@
       <c r="E67" s="43"/>
       <c r="F67" s="42"/>
       <c r="G67" s="42" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H67" s="42"/>
       <c r="I67" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J67" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K67" s="43"/>
       <c r="L67" s="43">
@@ -8070,7 +8235,7 @@
         <v>8</v>
       </c>
       <c r="N67" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O67" s="43">
         <v>0.1</v>
@@ -8097,14 +8262,14 @@
       <c r="E68" s="43"/>
       <c r="F68" s="42"/>
       <c r="G68" s="42" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H68" s="42"/>
       <c r="I68" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J68" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K68" s="43"/>
       <c r="L68" s="43">
@@ -8114,7 +8279,7 @@
         <v>8</v>
       </c>
       <c r="N68" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O68" s="43">
         <v>0.1</v>
@@ -8135,16 +8300,16 @@
     </row>
     <row r="69" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B69" s="39" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C69" s="40" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D69" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E69" s="41">
         <v>200</v>
@@ -8181,14 +8346,14 @@
       <c r="E70" s="43"/>
       <c r="F70" s="42"/>
       <c r="G70" s="42" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H70" s="42"/>
       <c r="I70" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J70" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K70" s="43"/>
       <c r="L70" s="43">
@@ -8198,7 +8363,7 @@
         <v>8</v>
       </c>
       <c r="N70" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O70" s="43">
         <v>1</v>
@@ -8225,14 +8390,14 @@
       <c r="E71" s="43"/>
       <c r="F71" s="42"/>
       <c r="G71" s="42" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H71" s="42"/>
       <c r="I71" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J71" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K71" s="43"/>
       <c r="L71" s="43">
@@ -8242,7 +8407,7 @@
         <v>8</v>
       </c>
       <c r="N71" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O71" s="43">
         <v>1</v>
@@ -8269,14 +8434,14 @@
       <c r="E72" s="43"/>
       <c r="F72" s="42"/>
       <c r="G72" s="42" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H72" s="42"/>
       <c r="I72" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J72" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K72" s="43"/>
       <c r="L72" s="43">
@@ -8286,7 +8451,7 @@
         <v>8</v>
       </c>
       <c r="N72" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O72" s="43">
         <v>1</v>
@@ -8313,14 +8478,14 @@
       <c r="E73" s="43"/>
       <c r="F73" s="42"/>
       <c r="G73" s="42" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H73" s="42"/>
       <c r="I73" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J73" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K73" s="43"/>
       <c r="L73" s="43">
@@ -8330,7 +8495,7 @@
         <v>8</v>
       </c>
       <c r="N73" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O73" s="43">
         <v>1</v>
@@ -8357,14 +8522,14 @@
       <c r="E74" s="43"/>
       <c r="F74" s="42"/>
       <c r="G74" s="42" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H74" s="42"/>
       <c r="I74" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J74" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K74" s="43"/>
       <c r="L74" s="43">
@@ -8374,7 +8539,7 @@
         <v>8</v>
       </c>
       <c r="N74" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O74" s="43">
         <v>1</v>
@@ -8401,14 +8566,14 @@
       <c r="E75" s="43"/>
       <c r="F75" s="42"/>
       <c r="G75" s="42" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H75" s="42"/>
       <c r="I75" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J75" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K75" s="43"/>
       <c r="L75" s="43">
@@ -8418,7 +8583,7 @@
         <v>8</v>
       </c>
       <c r="N75" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O75" s="43">
         <v>1</v>
@@ -8445,14 +8610,14 @@
       <c r="E76" s="43"/>
       <c r="F76" s="42"/>
       <c r="G76" s="42" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H76" s="42"/>
       <c r="I76" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J76" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K76" s="43"/>
       <c r="L76" s="43">
@@ -8462,7 +8627,7 @@
         <v>8</v>
       </c>
       <c r="N76" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O76" s="43">
         <v>1</v>
@@ -8489,14 +8654,14 @@
       <c r="E77" s="43"/>
       <c r="F77" s="42"/>
       <c r="G77" s="42" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H77" s="42"/>
       <c r="I77" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J77" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K77" s="43"/>
       <c r="L77" s="43">
@@ -8506,7 +8671,7 @@
         <v>8</v>
       </c>
       <c r="N77" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O77" s="43">
         <v>1</v>
@@ -8527,16 +8692,16 @@
     </row>
     <row r="78" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="40" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B78" s="39" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C78" s="40" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D78" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E78" s="41">
         <v>200</v>
@@ -8573,14 +8738,14 @@
       <c r="E79" s="43"/>
       <c r="F79" s="42"/>
       <c r="G79" s="42" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H79" s="42"/>
       <c r="I79" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J79" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K79" s="43"/>
       <c r="L79" s="43">
@@ -8590,7 +8755,7 @@
         <v>8</v>
       </c>
       <c r="N79" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O79" s="43">
         <v>1</v>
@@ -8617,14 +8782,14 @@
       <c r="E80" s="43"/>
       <c r="F80" s="42"/>
       <c r="G80" s="42" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H80" s="42"/>
       <c r="I80" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J80" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K80" s="43"/>
       <c r="L80" s="43">
@@ -8634,7 +8799,7 @@
         <v>8</v>
       </c>
       <c r="N80" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O80" s="43">
         <v>1</v>
@@ -8661,14 +8826,14 @@
       <c r="E81" s="43"/>
       <c r="F81" s="42"/>
       <c r="G81" s="42" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H81" s="42"/>
       <c r="I81" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J81" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K81" s="43"/>
       <c r="L81" s="43">
@@ -8678,7 +8843,7 @@
         <v>8</v>
       </c>
       <c r="N81" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O81" s="43">
         <v>1</v>
@@ -8705,14 +8870,14 @@
       <c r="E82" s="43"/>
       <c r="F82" s="42"/>
       <c r="G82" s="42" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H82" s="42"/>
       <c r="I82" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J82" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K82" s="43"/>
       <c r="L82" s="43">
@@ -8722,7 +8887,7 @@
         <v>8</v>
       </c>
       <c r="N82" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O82" s="43">
         <v>1</v>
@@ -8749,14 +8914,14 @@
       <c r="E83" s="43"/>
       <c r="F83" s="42"/>
       <c r="G83" s="42" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H83" s="42"/>
       <c r="I83" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J83" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K83" s="43"/>
       <c r="L83" s="43">
@@ -8766,7 +8931,7 @@
         <v>8</v>
       </c>
       <c r="N83" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O83" s="43">
         <v>0.2</v>
@@ -8793,14 +8958,14 @@
       <c r="E84" s="43"/>
       <c r="F84" s="42"/>
       <c r="G84" s="42" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H84" s="42"/>
       <c r="I84" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J84" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K84" s="43"/>
       <c r="L84" s="43">
@@ -8810,7 +8975,7 @@
         <v>8</v>
       </c>
       <c r="N84" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O84" s="43">
         <v>0.5</v>
@@ -8837,14 +9002,14 @@
       <c r="E85" s="43"/>
       <c r="F85" s="42"/>
       <c r="G85" s="42" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H85" s="42"/>
       <c r="I85" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J85" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K85" s="43"/>
       <c r="L85" s="43">
@@ -8854,7 +9019,7 @@
         <v>8</v>
       </c>
       <c r="N85" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O85" s="43">
         <v>0.1</v>
@@ -8881,14 +9046,14 @@
       <c r="E86" s="43"/>
       <c r="F86" s="42"/>
       <c r="G86" s="42" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H86" s="42"/>
       <c r="I86" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J86" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K86" s="43"/>
       <c r="L86" s="43">
@@ -8898,7 +9063,7 @@
         <v>8</v>
       </c>
       <c r="N86" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O86" s="43">
         <v>0.1</v>
@@ -8919,16 +9084,16 @@
     </row>
     <row r="87" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="40" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B87" s="39" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C87" s="40" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D87" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E87" s="41">
         <v>200</v>
@@ -8965,14 +9130,14 @@
       <c r="E88" s="43"/>
       <c r="F88" s="42"/>
       <c r="G88" s="42" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H88" s="42"/>
       <c r="I88" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J88" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K88" s="43"/>
       <c r="L88" s="43">
@@ -8982,7 +9147,7 @@
         <v>8</v>
       </c>
       <c r="N88" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O88" s="43">
         <v>1</v>
@@ -9009,14 +9174,14 @@
       <c r="E89" s="43"/>
       <c r="F89" s="42"/>
       <c r="G89" s="42" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H89" s="42"/>
       <c r="I89" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J89" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K89" s="43"/>
       <c r="L89" s="43">
@@ -9026,7 +9191,7 @@
         <v>8</v>
       </c>
       <c r="N89" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O89" s="43">
         <v>1</v>
@@ -9053,14 +9218,14 @@
       <c r="E90" s="43"/>
       <c r="F90" s="42"/>
       <c r="G90" s="42" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H90" s="42"/>
       <c r="I90" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J90" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K90" s="43"/>
       <c r="L90" s="43">
@@ -9070,7 +9235,7 @@
         <v>8</v>
       </c>
       <c r="N90" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O90" s="43">
         <v>1</v>
@@ -9097,14 +9262,14 @@
       <c r="E91" s="43"/>
       <c r="F91" s="42"/>
       <c r="G91" s="42" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H91" s="42"/>
       <c r="I91" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J91" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K91" s="43"/>
       <c r="L91" s="43">
@@ -9114,7 +9279,7 @@
         <v>8</v>
       </c>
       <c r="N91" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O91" s="43">
         <v>1</v>
@@ -9141,14 +9306,14 @@
       <c r="E92" s="43"/>
       <c r="F92" s="42"/>
       <c r="G92" s="42" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H92" s="42"/>
       <c r="I92" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J92" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K92" s="43"/>
       <c r="L92" s="43">
@@ -9158,7 +9323,7 @@
         <v>8</v>
       </c>
       <c r="N92" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O92" s="43">
         <v>1</v>
@@ -9185,14 +9350,14 @@
       <c r="E93" s="43"/>
       <c r="F93" s="42"/>
       <c r="G93" s="42" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H93" s="42"/>
       <c r="I93" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J93" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K93" s="43"/>
       <c r="L93" s="43">
@@ -9202,7 +9367,7 @@
         <v>8</v>
       </c>
       <c r="N93" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O93" s="43">
         <v>1</v>
@@ -9229,14 +9394,14 @@
       <c r="E94" s="43"/>
       <c r="F94" s="42"/>
       <c r="G94" s="42" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H94" s="42"/>
       <c r="I94" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J94" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K94" s="43"/>
       <c r="L94" s="43">
@@ -9246,7 +9411,7 @@
         <v>8</v>
       </c>
       <c r="N94" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O94" s="43">
         <v>1</v>
@@ -9273,14 +9438,14 @@
       <c r="E95" s="43"/>
       <c r="F95" s="42"/>
       <c r="G95" s="42" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H95" s="42"/>
       <c r="I95" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J95" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K95" s="43"/>
       <c r="L95" s="43">
@@ -9290,7 +9455,7 @@
         <v>8</v>
       </c>
       <c r="N95" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O95" s="43">
         <v>1</v>
@@ -9347,21 +9512,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AH41"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.149999999999999" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="9.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="15.75" style="3" customWidth="1"/>
+    <col min="2" max="2" width="10.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.5" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9" style="3" customWidth="1"/>
     <col min="5" max="5" width="10.5" style="4" customWidth="1"/>
-    <col min="6" max="6" width="8.875" style="3"/>
-    <col min="7" max="7" width="35.75" style="3" customWidth="1"/>
-    <col min="8" max="8" width="33" style="3" customWidth="1"/>
-    <col min="9" max="9" width="8.5" style="3" customWidth="1"/>
-    <col min="10" max="10" width="9.25" style="3" customWidth="1"/>
+    <col min="6" max="6" width="2.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="19.625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="24.625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="39.25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.875" style="3" customWidth="1"/>
     <col min="11" max="11" width="3.75" style="4" customWidth="1"/>
     <col min="12" max="13" width="8.875" style="4"/>
     <col min="14" max="14" width="11.875" style="3" customWidth="1"/>
@@ -9373,133 +9538,132 @@
     <col min="21" max="21" width="11.125" style="4" customWidth="1" outlineLevel="1"/>
     <col min="22" max="24" width="8.875" style="4" customWidth="1" outlineLevel="1"/>
     <col min="25" max="25" width="44.25" style="3" customWidth="1"/>
-    <col min="26" max="26" width="8.25" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="27" max="27" width="8.875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="28" max="28" width="11" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="29" max="29" width="13.75" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="30" max="30" width="11.375" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="31" max="31" width="9.75" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="32" max="32" width="8.875" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="33" max="33" width="8.875" style="3" collapsed="1"/>
-    <col min="34" max="16384" width="8.875" style="3"/>
+    <col min="26" max="26" width="36.625" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="27" max="27" width="8.875" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="28" max="28" width="11" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="29" max="29" width="13.75" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="30" max="30" width="11.375" style="5" customWidth="1" outlineLevel="1"/>
+    <col min="31" max="31" width="9.75" style="5" customWidth="1" outlineLevel="1"/>
+    <col min="32" max="32" width="8.875" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="33" max="16384" width="8.875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1" ht="88.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="T1" s="54" t="s">
+        <v>227</v>
+      </c>
+      <c r="U1" s="54" t="s">
+        <v>228</v>
+      </c>
+      <c r="V1" s="54" t="s">
+        <v>229</v>
+      </c>
+      <c r="W1" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB1" s="54" t="s">
         <v>217</v>
       </c>
-      <c r="K1" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="55" t="s">
-        <v>226</v>
-      </c>
-      <c r="M1" s="55" t="s">
-        <v>227</v>
-      </c>
-      <c r="N1" s="54" t="s">
-        <v>218</v>
-      </c>
-      <c r="O1" s="55" t="s">
-        <v>228</v>
-      </c>
-      <c r="P1" s="55" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q1" s="54" t="s">
-        <v>230</v>
-      </c>
-      <c r="R1" s="54" t="s">
-        <v>231</v>
-      </c>
-      <c r="S1" s="54" t="s">
-        <v>219</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="W1" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="X1" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y1" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA1" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB1" s="8" t="s">
-        <v>34</v>
-      </c>
       <c r="AC1" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AD1" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE1" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AF1" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG1" s="56" t="s">
-        <v>234</v>
+        <v>39</v>
+      </c>
+      <c r="AG1" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="AH1" s="21" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="2" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2" s="11">
         <v>100</v>
@@ -9534,10 +9698,10 @@
       <c r="AE2" s="10"/>
       <c r="AF2" s="10"/>
       <c r="AG2" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH2" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="AH2" s="10" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -9548,12 +9712,10 @@
       <c r="E3" s="13"/>
       <c r="F3" s="12"/>
       <c r="G3" s="12" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H3" s="12"/>
-      <c r="I3" s="12" t="s">
-        <v>53</v>
-      </c>
+      <c r="I3" s="12"/>
       <c r="J3" s="12"/>
       <c r="K3" s="13"/>
       <c r="L3" s="13">
@@ -9596,12 +9758,10 @@
       <c r="E4" s="13"/>
       <c r="F4" s="12"/>
       <c r="G4" s="12" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H4" s="12"/>
-      <c r="I4" s="12" t="s">
-        <v>53</v>
-      </c>
+      <c r="I4" s="12"/>
       <c r="J4" s="12"/>
       <c r="K4" s="13"/>
       <c r="L4" s="13">
@@ -9612,10 +9772,10 @@
       </c>
       <c r="N4" s="12"/>
       <c r="O4" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P4" s="13">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="Q4" s="13"/>
       <c r="R4" s="13"/>
@@ -9637,17 +9797,17 @@
       <c r="AH4" s="12"/>
     </row>
     <row r="5" spans="1:34" s="2" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>201</v>
+      <c r="A5" s="53" t="s">
+        <v>214</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c r="E5" s="11">
         <v>100</v>
@@ -9692,7 +9852,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
@@ -9706,10 +9866,10 @@
       </c>
       <c r="N6" s="12"/>
       <c r="O6" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P6" s="13">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="Q6" s="13"/>
       <c r="R6" s="13"/>
@@ -9738,7 +9898,7 @@
       <c r="E7" s="13"/>
       <c r="F7" s="12"/>
       <c r="G7" s="12" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
@@ -9752,10 +9912,10 @@
       </c>
       <c r="N7" s="12"/>
       <c r="O7" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P7" s="13">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="Q7" s="13"/>
       <c r="R7" s="13"/>
@@ -9778,16 +9938,16 @@
     </row>
     <row r="8" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c r="E8" s="16">
         <v>500</v>
@@ -9822,10 +9982,10 @@
       <c r="AE8" s="15"/>
       <c r="AF8" s="15"/>
       <c r="AG8" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AH8" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -9836,7 +9996,7 @@
       <c r="E9" s="13"/>
       <c r="F9" s="12"/>
       <c r="G9" s="12" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -9850,10 +10010,10 @@
       </c>
       <c r="N9" s="12"/>
       <c r="O9" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P9" s="13">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="Q9" s="13"/>
       <c r="R9" s="13"/>
@@ -9882,7 +10042,7 @@
       <c r="E10" s="13"/>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
@@ -9896,10 +10056,10 @@
       </c>
       <c r="N10" s="12"/>
       <c r="O10" s="13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P10" s="13">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="Q10" s="13"/>
       <c r="R10" s="13"/>
@@ -9922,16 +10082,16 @@
     </row>
     <row r="11" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" s="31">
         <v>100</v>
@@ -9939,12 +10099,8 @@
       <c r="F11" s="31">
         <v>8</v>
       </c>
-      <c r="G11" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="31" t="s">
-        <v>46</v>
-      </c>
+      <c r="G11" s="57"/>
+      <c r="H11" s="31"/>
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
       <c r="K11" s="31"/>
@@ -9963,21 +10119,7 @@
       <c r="X11" s="31"/>
       <c r="Y11" s="31"/>
       <c r="Z11" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA11" s="31"/>
-      <c r="AB11" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC11" s="31"/>
-      <c r="AD11" s="34"/>
-      <c r="AE11" s="34"/>
-      <c r="AF11" s="34"/>
-      <c r="AG11" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="AH11" s="34" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
@@ -9988,28 +10130,26 @@
       <c r="E12" s="34"/>
       <c r="F12" s="33"/>
       <c r="G12" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="H12" s="33" t="s">
+      <c r="I12" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="I12" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="J12" s="44" t="s">
+      <c r="J12" s="44"/>
+      <c r="K12" s="45">
+        <v>0</v>
+      </c>
+      <c r="L12" s="45">
+        <v>0</v>
+      </c>
+      <c r="M12" s="45">
+        <v>8</v>
+      </c>
+      <c r="N12" s="46" t="s">
         <v>54</v>
-      </c>
-      <c r="K12" s="45">
-        <v>0</v>
-      </c>
-      <c r="L12" s="45">
-        <v>0</v>
-      </c>
-      <c r="M12" s="45">
-        <v>8</v>
-      </c>
-      <c r="N12" s="46" t="s">
-        <v>55</v>
       </c>
       <c r="O12" s="45">
         <v>1</v>
@@ -10037,20 +10177,10 @@
       </c>
       <c r="W12" s="34"/>
       <c r="X12" s="34"/>
-      <c r="Y12" s="33" t="s">
+      <c r="Y12" s="33"/>
+      <c r="Z12" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="Z12" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA12" s="34"/>
-      <c r="AB12" s="33"/>
-      <c r="AC12" s="44"/>
-      <c r="AD12" s="33"/>
-      <c r="AE12" s="33"/>
-      <c r="AF12" s="33"/>
-      <c r="AG12" s="33"/>
-      <c r="AH12" s="33"/>
     </row>
     <row r="13" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="33"/>
@@ -10060,17 +10190,15 @@
       <c r="E13" s="34"/>
       <c r="F13" s="33"/>
       <c r="G13" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="H13" s="36" t="s">
-        <v>59</v>
-      </c>
       <c r="I13" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="J13" s="44" t="s">
-        <v>54</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="J13" s="44"/>
       <c r="K13" s="34">
         <v>1</v>
       </c>
@@ -10081,7 +10209,7 @@
         <v>2</v>
       </c>
       <c r="N13" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O13" s="45">
         <v>1</v>
@@ -10107,24 +10235,14 @@
       <c r="V13" s="34">
         <v>0</v>
       </c>
-      <c r="W13" s="34">
-        <v>3</v>
-      </c>
+      <c r="W13" s="34"/>
       <c r="X13" s="34"/>
       <c r="Y13" s="36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Z13" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA13" s="34"/>
-      <c r="AB13" s="33"/>
-      <c r="AC13" s="44"/>
-      <c r="AD13" s="33"/>
-      <c r="AE13" s="33"/>
-      <c r="AF13" s="33"/>
-      <c r="AG13" s="33"/>
-      <c r="AH13" s="33"/>
+        <v>56</v>
+      </c>
     </row>
     <row r="14" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="33"/>
@@ -10134,17 +10252,15 @@
       <c r="E14" s="34"/>
       <c r="F14" s="33"/>
       <c r="G14" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="H14" s="33" t="s">
-        <v>62</v>
-      </c>
       <c r="I14" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="J14" s="44" t="s">
-        <v>54</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="J14" s="44"/>
       <c r="K14" s="34">
         <v>2</v>
       </c>
@@ -10155,7 +10271,7 @@
         <v>4</v>
       </c>
       <c r="N14" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O14" s="45">
         <v>1</v>
@@ -10181,24 +10297,14 @@
       <c r="V14" s="34">
         <v>0</v>
       </c>
-      <c r="W14" s="34">
-        <v>15</v>
-      </c>
+      <c r="W14" s="34"/>
       <c r="X14" s="34"/>
       <c r="Y14" s="36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Z14" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA14" s="34"/>
-      <c r="AB14" s="33"/>
-      <c r="AC14" s="44"/>
-      <c r="AD14" s="33"/>
-      <c r="AE14" s="33"/>
-      <c r="AF14" s="33"/>
-      <c r="AG14" s="33"/>
-      <c r="AH14" s="33"/>
+        <v>56</v>
+      </c>
     </row>
     <row r="15" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="33"/>
@@ -10208,17 +10314,15 @@
       <c r="E15" s="34"/>
       <c r="F15" s="33"/>
       <c r="G15" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="H15" s="36" t="s">
-        <v>65</v>
-      </c>
       <c r="I15" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="J15" s="44" t="s">
-        <v>54</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="J15" s="44"/>
       <c r="K15" s="34">
         <v>2</v>
       </c>
@@ -10229,7 +10333,7 @@
         <v>4</v>
       </c>
       <c r="N15" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O15" s="45">
         <v>1</v>
@@ -10255,24 +10359,14 @@
       <c r="V15" s="34">
         <v>0</v>
       </c>
-      <c r="W15" s="34">
-        <v>15</v>
-      </c>
+      <c r="W15" s="34"/>
       <c r="X15" s="34"/>
       <c r="Y15" s="36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z15" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA15" s="34"/>
-      <c r="AB15" s="33"/>
-      <c r="AC15" s="44"/>
-      <c r="AD15" s="33"/>
-      <c r="AE15" s="33"/>
-      <c r="AF15" s="33"/>
-      <c r="AG15" s="33"/>
-      <c r="AH15" s="33"/>
+        <v>56</v>
+      </c>
     </row>
     <row r="16" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="33"/>
@@ -10282,17 +10376,15 @@
       <c r="E16" s="34"/>
       <c r="F16" s="33"/>
       <c r="G16" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="H16" s="36" t="s">
-        <v>68</v>
-      </c>
       <c r="I16" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="J16" s="44" t="s">
-        <v>54</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="J16" s="44"/>
       <c r="K16" s="34"/>
       <c r="L16" s="34">
         <v>56</v>
@@ -10301,7 +10393,7 @@
         <v>8</v>
       </c>
       <c r="N16" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O16" s="45">
         <v>1</v>
@@ -10319,27 +10411,19 @@
       <c r="X16" s="34"/>
       <c r="Y16" s="36"/>
       <c r="Z16" s="33"/>
-      <c r="AA16" s="34"/>
-      <c r="AB16" s="33"/>
-      <c r="AC16" s="44"/>
-      <c r="AD16" s="33"/>
-      <c r="AE16" s="33"/>
-      <c r="AF16" s="33"/>
-      <c r="AG16" s="33"/>
-      <c r="AH16" s="33"/>
-    </row>
-    <row r="17" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="C17" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="D17" s="37" t="s">
         <v>71</v>
-      </c>
-      <c r="D17" s="37" t="s">
-        <v>72</v>
       </c>
       <c r="E17" s="37">
         <v>100</v>
@@ -10347,12 +10431,8 @@
       <c r="F17" s="37">
         <v>8</v>
       </c>
-      <c r="G17" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17" s="37" t="s">
-        <v>73</v>
-      </c>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
       <c r="I17" s="37"/>
       <c r="J17" s="47"/>
       <c r="K17" s="37"/>
@@ -10371,22 +10451,8 @@
       <c r="X17" s="37"/>
       <c r="Y17" s="37"/>
       <c r="Z17" s="37"/>
-      <c r="AA17" s="37"/>
-      <c r="AB17" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC17" s="47"/>
-      <c r="AD17" s="34"/>
-      <c r="AE17" s="34"/>
-      <c r="AF17" s="50"/>
-      <c r="AG17" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH17" s="50" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="33"/>
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
@@ -10394,16 +10460,16 @@
       <c r="E18" s="34"/>
       <c r="F18" s="33"/>
       <c r="G18" s="33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H18" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="I18" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="44" t="s">
-        <v>53</v>
-      </c>
       <c r="J18" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K18" s="45">
         <v>0</v>
@@ -10415,7 +10481,7 @@
         <v>8</v>
       </c>
       <c r="N18" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O18" s="45">
         <v>1</v>
@@ -10443,20 +10509,10 @@
       </c>
       <c r="W18" s="34"/>
       <c r="X18" s="34"/>
-      <c r="Y18" s="33" t="s">
-        <v>56</v>
-      </c>
+      <c r="Y18" s="33"/>
       <c r="Z18" s="33"/>
-      <c r="AA18" s="34"/>
-      <c r="AB18" s="33"/>
-      <c r="AC18" s="44"/>
-      <c r="AD18" s="33"/>
-      <c r="AE18" s="33"/>
-      <c r="AF18" s="33"/>
-      <c r="AG18" s="33"/>
-      <c r="AH18" s="33"/>
-    </row>
-    <row r="19" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="33"/>
       <c r="B19" s="33"/>
       <c r="C19" s="33"/>
@@ -10464,29 +10520,28 @@
       <c r="E19" s="34"/>
       <c r="F19" s="33"/>
       <c r="G19" s="33" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H19" s="36" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I19" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J19" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K19" s="34">
         <v>1</v>
       </c>
       <c r="L19" s="34">
-        <f>M18+L18</f>
         <v>8</v>
       </c>
       <c r="M19" s="34">
         <v>8</v>
       </c>
       <c r="N19" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O19" s="45">
         <v>1</v>
@@ -10516,16 +10571,8 @@
       <c r="X19" s="34"/>
       <c r="Y19" s="36"/>
       <c r="Z19" s="36"/>
-      <c r="AA19" s="34"/>
-      <c r="AB19" s="33"/>
-      <c r="AC19" s="44"/>
-      <c r="AD19" s="33"/>
-      <c r="AE19" s="33"/>
-      <c r="AF19" s="33"/>
-      <c r="AG19" s="33"/>
-      <c r="AH19" s="33"/>
-    </row>
-    <row r="20" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="33"/>
       <c r="B20" s="33"/>
       <c r="C20" s="33"/>
@@ -10533,29 +10580,28 @@
       <c r="E20" s="34"/>
       <c r="F20" s="33"/>
       <c r="G20" s="33" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H20" s="36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I20" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J20" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K20" s="34">
         <v>2</v>
       </c>
       <c r="L20" s="34">
-        <f>M19+L19</f>
         <v>16</v>
       </c>
       <c r="M20" s="34">
         <v>4</v>
       </c>
       <c r="N20" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O20" s="45">
         <v>1</v>
@@ -10584,19 +10630,11 @@
       <c r="W20" s="34"/>
       <c r="X20" s="34"/>
       <c r="Y20" s="36" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Z20" s="36"/>
-      <c r="AA20" s="34"/>
-      <c r="AB20" s="33"/>
-      <c r="AC20" s="44"/>
-      <c r="AD20" s="33"/>
-      <c r="AE20" s="33"/>
-      <c r="AF20" s="33"/>
-      <c r="AG20" s="33"/>
-      <c r="AH20" s="33"/>
-    </row>
-    <row r="21" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="33"/>
       <c r="B21" s="33"/>
       <c r="C21" s="33"/>
@@ -10604,16 +10642,16 @@
       <c r="E21" s="34"/>
       <c r="F21" s="33"/>
       <c r="G21" s="33" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H21" s="36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I21" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J21" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K21" s="34">
         <v>2</v>
@@ -10625,7 +10663,7 @@
         <v>4</v>
       </c>
       <c r="N21" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O21" s="45">
         <v>1</v>
@@ -10653,22 +10691,14 @@
       </c>
       <c r="W21" s="34"/>
       <c r="X21" s="34" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="Y21" s="36" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Z21" s="36"/>
-      <c r="AA21" s="34"/>
-      <c r="AB21" s="33"/>
-      <c r="AC21" s="44"/>
-      <c r="AD21" s="33"/>
-      <c r="AE21" s="33"/>
-      <c r="AF21" s="33"/>
-      <c r="AG21" s="33"/>
-      <c r="AH21" s="33"/>
-    </row>
-    <row r="22" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="33"/>
       <c r="B22" s="33"/>
       <c r="C22" s="33"/>
@@ -10676,16 +10706,16 @@
       <c r="E22" s="34"/>
       <c r="F22" s="33"/>
       <c r="G22" s="33" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H22" s="36" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I22" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K22" s="34">
         <v>3</v>
@@ -10697,7 +10727,7 @@
         <v>2</v>
       </c>
       <c r="N22" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O22" s="45">
         <v>1</v>
@@ -10726,19 +10756,11 @@
       <c r="W22" s="34"/>
       <c r="X22" s="34"/>
       <c r="Y22" s="36" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Z22" s="36"/>
-      <c r="AA22" s="34"/>
-      <c r="AB22" s="33"/>
-      <c r="AC22" s="44"/>
-      <c r="AD22" s="33"/>
-      <c r="AE22" s="33"/>
-      <c r="AF22" s="33"/>
-      <c r="AG22" s="33"/>
-      <c r="AH22" s="33"/>
-    </row>
-    <row r="23" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="33"/>
       <c r="B23" s="33"/>
       <c r="C23" s="33"/>
@@ -10746,16 +10768,16 @@
       <c r="E23" s="34"/>
       <c r="F23" s="33"/>
       <c r="G23" s="33" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H23" s="36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I23" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J23" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K23" s="34">
         <v>3</v>
@@ -10767,7 +10789,7 @@
         <v>2</v>
       </c>
       <c r="N23" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O23" s="45">
         <v>1</v>
@@ -10796,19 +10818,11 @@
       <c r="W23" s="34"/>
       <c r="X23" s="34"/>
       <c r="Y23" s="36" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="Z23" s="36"/>
-      <c r="AA23" s="34"/>
-      <c r="AB23" s="33"/>
-      <c r="AC23" s="44"/>
-      <c r="AD23" s="33"/>
-      <c r="AE23" s="33"/>
-      <c r="AF23" s="33"/>
-      <c r="AG23" s="33"/>
-      <c r="AH23" s="33"/>
-    </row>
-    <row r="24" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="33"/>
       <c r="B24" s="33"/>
       <c r="C24" s="33"/>
@@ -10816,16 +10830,16 @@
       <c r="E24" s="34"/>
       <c r="F24" s="33"/>
       <c r="G24" s="33" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I24" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J24" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K24" s="34">
         <v>3</v>
@@ -10837,7 +10851,7 @@
         <v>2</v>
       </c>
       <c r="N24" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O24" s="45">
         <v>1</v>
@@ -10860,19 +10874,11 @@
       <c r="W24" s="34"/>
       <c r="X24" s="34"/>
       <c r="Y24" s="36" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="Z24" s="36"/>
-      <c r="AA24" s="34"/>
-      <c r="AB24" s="33"/>
-      <c r="AC24" s="44"/>
-      <c r="AD24" s="33"/>
-      <c r="AE24" s="33"/>
-      <c r="AF24" s="33"/>
-      <c r="AG24" s="33"/>
-      <c r="AH24" s="33"/>
-    </row>
-    <row r="25" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="33"/>
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
@@ -10880,16 +10886,16 @@
       <c r="E25" s="34"/>
       <c r="F25" s="33"/>
       <c r="G25" s="33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H25" s="38" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I25" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J25" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K25" s="34">
         <v>7</v>
@@ -10901,7 +10907,7 @@
         <v>8</v>
       </c>
       <c r="N25" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O25" s="45">
         <v>1</v>
@@ -10929,31 +10935,23 @@
       </c>
       <c r="W25" s="34"/>
       <c r="X25" s="34"/>
-      <c r="Y25" s="36" t="s">
+      <c r="Y25" s="58"/>
+      <c r="Z25" s="58" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="Z25" s="36"/>
-      <c r="AA25" s="34"/>
-      <c r="AB25" s="33"/>
-      <c r="AC25" s="44"/>
-      <c r="AD25" s="33"/>
-      <c r="AE25" s="33"/>
-      <c r="AF25" s="33"/>
-      <c r="AG25" s="33"/>
-      <c r="AH25" s="33"/>
-    </row>
-    <row r="26" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>97</v>
-      </c>
       <c r="D26" s="39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E26" s="39">
         <v>50</v>
@@ -10962,9 +10960,7 @@
         <v>8</v>
       </c>
       <c r="G26" s="39"/>
-      <c r="H26" s="39" t="s">
-        <v>98</v>
-      </c>
+      <c r="H26" s="39"/>
       <c r="I26" s="39"/>
       <c r="J26" s="39"/>
       <c r="K26" s="39"/>
@@ -10983,20 +10979,10 @@
       <c r="X26" s="39"/>
       <c r="Y26" s="39"/>
       <c r="Z26" s="39"/>
-      <c r="AA26" s="39"/>
-      <c r="AB26" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC26" s="39"/>
-      <c r="AD26" s="34"/>
-      <c r="AE26" s="34"/>
-      <c r="AF26" s="34"/>
-      <c r="AG26" s="34"/>
-      <c r="AH26" s="34"/>
-    </row>
-    <row r="27" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="33" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B27" s="33"/>
       <c r="C27" s="33"/>
@@ -11004,16 +10990,16 @@
       <c r="E27" s="34"/>
       <c r="F27" s="33"/>
       <c r="G27" s="33" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H27" s="38" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I27" s="44" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J27" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K27" s="33"/>
       <c r="L27" s="34">
@@ -11023,7 +11009,7 @@
         <v>8</v>
       </c>
       <c r="N27" s="46" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="O27" s="34">
         <v>1</v>
@@ -11041,18 +11027,10 @@
       <c r="X27" s="33"/>
       <c r="Y27" s="33"/>
       <c r="Z27" s="33"/>
-      <c r="AA27" s="33"/>
-      <c r="AB27" s="33"/>
-      <c r="AC27" s="44"/>
-      <c r="AD27" s="33"/>
-      <c r="AE27" s="33"/>
-      <c r="AF27" s="33"/>
-      <c r="AG27" s="33"/>
-      <c r="AH27" s="33"/>
-    </row>
-    <row r="28" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="33" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B28" s="33"/>
       <c r="C28" s="33"/>
@@ -11060,14 +11038,14 @@
       <c r="E28" s="34"/>
       <c r="F28" s="33"/>
       <c r="G28" s="33" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H28" s="33"/>
       <c r="I28" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J28" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K28" s="33"/>
       <c r="L28" s="34">
@@ -11077,7 +11055,7 @@
         <v>8</v>
       </c>
       <c r="N28" s="46" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="O28" s="34">
         <v>1</v>
@@ -11095,18 +11073,10 @@
       <c r="X28" s="33"/>
       <c r="Y28" s="33"/>
       <c r="Z28" s="33"/>
-      <c r="AA28" s="33"/>
-      <c r="AB28" s="33"/>
-      <c r="AC28" s="44"/>
-      <c r="AD28" s="33"/>
-      <c r="AE28" s="33"/>
-      <c r="AF28" s="33"/>
-      <c r="AG28" s="33"/>
-      <c r="AH28" s="33"/>
-    </row>
-    <row r="29" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="33" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B29" s="33"/>
       <c r="C29" s="33"/>
@@ -11114,14 +11084,14 @@
       <c r="E29" s="34"/>
       <c r="F29" s="33"/>
       <c r="G29" s="33" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H29" s="33"/>
       <c r="I29" s="44" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J29" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K29" s="33"/>
       <c r="L29" s="34">
@@ -11131,7 +11101,7 @@
         <v>8</v>
       </c>
       <c r="N29" s="46" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="O29" s="34">
         <v>1</v>
@@ -11149,43 +11119,35 @@
       <c r="X29" s="33"/>
       <c r="Y29" s="33"/>
       <c r="Z29" s="33"/>
-      <c r="AA29" s="33"/>
-      <c r="AB29" s="33"/>
-      <c r="AC29" s="44"/>
-      <c r="AD29" s="33"/>
-      <c r="AE29" s="33"/>
-      <c r="AF29" s="33"/>
-      <c r="AG29" s="33"/>
-      <c r="AH29" s="33"/>
-    </row>
-    <row r="30" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="30" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="33"/>
       <c r="B30" s="33"/>
       <c r="C30" s="33" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D30" s="33"/>
       <c r="E30" s="34"/>
       <c r="F30" s="33"/>
       <c r="G30" s="33" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H30" s="33"/>
       <c r="I30" s="44" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J30" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K30" s="33"/>
       <c r="L30" s="48" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="M30" s="34">
         <v>4</v>
       </c>
       <c r="N30" s="46" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="O30" s="34">
         <v>1</v>
@@ -11203,16 +11165,8 @@
       <c r="X30" s="33"/>
       <c r="Y30" s="33"/>
       <c r="Z30" s="33"/>
-      <c r="AA30" s="33"/>
-      <c r="AB30" s="33"/>
-      <c r="AC30" s="44"/>
-      <c r="AD30" s="33"/>
-      <c r="AE30" s="33"/>
-      <c r="AF30" s="33"/>
-      <c r="AG30" s="33"/>
-      <c r="AH30" s="33"/>
-    </row>
-    <row r="31" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="33"/>
       <c r="B31" s="33"/>
       <c r="C31" s="33"/>
@@ -11220,24 +11174,24 @@
       <c r="E31" s="34"/>
       <c r="F31" s="33"/>
       <c r="G31" s="33" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H31" s="33"/>
       <c r="I31" s="44" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J31" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K31" s="33"/>
       <c r="L31" s="48" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M31" s="48" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="N31" s="46" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="O31" s="34">
         <v>1</v>
@@ -11255,16 +11209,8 @@
       <c r="X31" s="33"/>
       <c r="Y31" s="33"/>
       <c r="Z31" s="33"/>
-      <c r="AA31" s="33"/>
-      <c r="AB31" s="33"/>
-      <c r="AC31" s="44"/>
-      <c r="AD31" s="33"/>
-      <c r="AE31" s="33"/>
-      <c r="AF31" s="33"/>
-      <c r="AG31" s="33"/>
-      <c r="AH31" s="33"/>
-    </row>
-    <row r="32" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="33"/>
       <c r="B32" s="33"/>
       <c r="C32" s="33"/>
@@ -11272,16 +11218,16 @@
       <c r="E32" s="34"/>
       <c r="F32" s="33"/>
       <c r="G32" s="33" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H32" s="38" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I32" s="44" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J32" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K32" s="34"/>
       <c r="L32" s="48">
@@ -11291,7 +11237,7 @@
         <v>16</v>
       </c>
       <c r="N32" s="46" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="O32" s="34">
         <v>1</v>
@@ -11309,27 +11255,19 @@
       <c r="X32" s="34"/>
       <c r="Y32" s="33"/>
       <c r="Z32" s="33"/>
-      <c r="AA32" s="34"/>
-      <c r="AB32" s="33"/>
-      <c r="AC32" s="44"/>
-      <c r="AD32" s="33"/>
-      <c r="AE32" s="33"/>
-      <c r="AF32" s="33"/>
-      <c r="AG32" s="33"/>
-      <c r="AH32" s="33"/>
-    </row>
-    <row r="33" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="40" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D33" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E33" s="41">
         <v>200</v>
@@ -11357,16 +11295,8 @@
       <c r="X33" s="41"/>
       <c r="Y33" s="40"/>
       <c r="Z33" s="40"/>
-      <c r="AA33" s="23"/>
-      <c r="AB33" s="27"/>
-      <c r="AC33" s="27"/>
-      <c r="AD33" s="26"/>
-      <c r="AE33" s="26"/>
-      <c r="AF33" s="27"/>
-      <c r="AG33" s="27"/>
-      <c r="AH33" s="27"/>
-    </row>
-    <row r="34" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="42"/>
       <c r="B34" s="42"/>
       <c r="C34" s="42"/>
@@ -11374,15 +11304,13 @@
       <c r="E34" s="43"/>
       <c r="F34" s="42"/>
       <c r="G34" s="42" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H34" s="42"/>
       <c r="I34" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="J34" s="42" t="s">
-        <v>72</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="J34" s="42"/>
       <c r="K34" s="43"/>
       <c r="L34" s="43">
         <v>0</v>
@@ -11391,7 +11319,7 @@
         <v>8</v>
       </c>
       <c r="N34" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O34" s="43">
         <v>1</v>
@@ -11409,16 +11337,8 @@
       <c r="X34" s="43"/>
       <c r="Y34" s="42"/>
       <c r="Z34" s="42"/>
-      <c r="AA34" s="23"/>
-      <c r="AB34" s="27"/>
-      <c r="AC34" s="27"/>
-      <c r="AD34" s="26"/>
-      <c r="AE34" s="26"/>
-      <c r="AF34" s="27"/>
-      <c r="AG34" s="27"/>
-      <c r="AH34" s="27"/>
-    </row>
-    <row r="35" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="42"/>
       <c r="B35" s="42"/>
       <c r="C35" s="42"/>
@@ -11426,15 +11346,13 @@
       <c r="E35" s="43"/>
       <c r="F35" s="42"/>
       <c r="G35" s="42" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H35" s="42"/>
       <c r="I35" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="J35" s="42" t="s">
-        <v>72</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="J35" s="42"/>
       <c r="K35" s="43"/>
       <c r="L35" s="43">
         <v>8</v>
@@ -11443,7 +11361,7 @@
         <v>8</v>
       </c>
       <c r="N35" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O35" s="43">
         <v>1</v>
@@ -11461,16 +11379,8 @@
       <c r="X35" s="43"/>
       <c r="Y35" s="42"/>
       <c r="Z35" s="42"/>
-      <c r="AA35" s="23"/>
-      <c r="AB35" s="27"/>
-      <c r="AC35" s="27"/>
-      <c r="AD35" s="26"/>
-      <c r="AE35" s="26"/>
-      <c r="AF35" s="27"/>
-      <c r="AG35" s="27"/>
-      <c r="AH35" s="27"/>
-    </row>
-    <row r="36" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="42"/>
       <c r="B36" s="42"/>
       <c r="C36" s="42"/>
@@ -11478,15 +11388,13 @@
       <c r="E36" s="43"/>
       <c r="F36" s="42"/>
       <c r="G36" s="42" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H36" s="42"/>
       <c r="I36" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="J36" s="42" t="s">
-        <v>72</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="J36" s="42"/>
       <c r="K36" s="43"/>
       <c r="L36" s="43">
         <v>16</v>
@@ -11495,7 +11403,7 @@
         <v>8</v>
       </c>
       <c r="N36" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O36" s="43">
         <v>1</v>
@@ -11513,16 +11421,8 @@
       <c r="X36" s="43"/>
       <c r="Y36" s="42"/>
       <c r="Z36" s="42"/>
-      <c r="AA36" s="23"/>
-      <c r="AB36" s="27"/>
-      <c r="AC36" s="27"/>
-      <c r="AD36" s="26"/>
-      <c r="AE36" s="26"/>
-      <c r="AF36" s="27"/>
-      <c r="AG36" s="27"/>
-      <c r="AH36" s="27"/>
-    </row>
-    <row r="37" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="42"/>
       <c r="B37" s="42"/>
       <c r="C37" s="42"/>
@@ -11530,15 +11430,13 @@
       <c r="E37" s="43"/>
       <c r="F37" s="42"/>
       <c r="G37" s="42" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H37" s="42"/>
       <c r="I37" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="J37" s="42" t="s">
-        <v>72</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="J37" s="42"/>
       <c r="K37" s="43"/>
       <c r="L37" s="43">
         <v>24</v>
@@ -11547,7 +11445,7 @@
         <v>8</v>
       </c>
       <c r="N37" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O37" s="43">
         <v>1</v>
@@ -11565,16 +11463,8 @@
       <c r="X37" s="43"/>
       <c r="Y37" s="42"/>
       <c r="Z37" s="42"/>
-      <c r="AA37" s="23"/>
-      <c r="AB37" s="27"/>
-      <c r="AC37" s="27"/>
-      <c r="AD37" s="26"/>
-      <c r="AE37" s="26"/>
-      <c r="AF37" s="27"/>
-      <c r="AG37" s="27"/>
-      <c r="AH37" s="27"/>
-    </row>
-    <row r="38" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="42"/>
       <c r="B38" s="42"/>
       <c r="C38" s="42"/>
@@ -11582,15 +11472,13 @@
       <c r="E38" s="43"/>
       <c r="F38" s="42"/>
       <c r="G38" s="42" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H38" s="42"/>
       <c r="I38" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="J38" s="42" t="s">
-        <v>72</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="J38" s="42"/>
       <c r="K38" s="43"/>
       <c r="L38" s="43">
         <v>32</v>
@@ -11599,7 +11487,7 @@
         <v>8</v>
       </c>
       <c r="N38" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O38" s="43">
         <v>0.2</v>
@@ -11617,16 +11505,8 @@
       <c r="X38" s="43"/>
       <c r="Y38" s="42"/>
       <c r="Z38" s="42"/>
-      <c r="AA38" s="23"/>
-      <c r="AB38" s="27"/>
-      <c r="AC38" s="27"/>
-      <c r="AD38" s="26"/>
-      <c r="AE38" s="26"/>
-      <c r="AF38" s="27"/>
-      <c r="AG38" s="27"/>
-      <c r="AH38" s="27"/>
-    </row>
-    <row r="39" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="42"/>
       <c r="B39" s="42"/>
       <c r="C39" s="42"/>
@@ -11634,15 +11514,13 @@
       <c r="E39" s="43"/>
       <c r="F39" s="42"/>
       <c r="G39" s="42" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H39" s="42"/>
       <c r="I39" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="J39" s="42" t="s">
-        <v>72</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="J39" s="42"/>
       <c r="K39" s="43"/>
       <c r="L39" s="43">
         <v>40</v>
@@ -11651,7 +11529,7 @@
         <v>8</v>
       </c>
       <c r="N39" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O39" s="43">
         <v>0.5</v>
@@ -11669,16 +11547,8 @@
       <c r="X39" s="43"/>
       <c r="Y39" s="42"/>
       <c r="Z39" s="42"/>
-      <c r="AA39" s="23"/>
-      <c r="AB39" s="27"/>
-      <c r="AC39" s="27"/>
-      <c r="AD39" s="26"/>
-      <c r="AE39" s="26"/>
-      <c r="AF39" s="27"/>
-      <c r="AG39" s="27"/>
-      <c r="AH39" s="27"/>
-    </row>
-    <row r="40" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="42"/>
       <c r="B40" s="42"/>
       <c r="C40" s="42"/>
@@ -11686,15 +11556,13 @@
       <c r="E40" s="43"/>
       <c r="F40" s="42"/>
       <c r="G40" s="42" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H40" s="42"/>
       <c r="I40" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="J40" s="42" t="s">
-        <v>72</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="J40" s="42"/>
       <c r="K40" s="43"/>
       <c r="L40" s="43">
         <v>48</v>
@@ -11703,7 +11571,7 @@
         <v>8</v>
       </c>
       <c r="N40" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O40" s="43">
         <v>0.1</v>
@@ -11721,16 +11589,8 @@
       <c r="X40" s="43"/>
       <c r="Y40" s="42"/>
       <c r="Z40" s="42"/>
-      <c r="AA40" s="23"/>
-      <c r="AB40" s="27"/>
-      <c r="AC40" s="27"/>
-      <c r="AD40" s="26"/>
-      <c r="AE40" s="26"/>
-      <c r="AF40" s="27"/>
-      <c r="AG40" s="27"/>
-      <c r="AH40" s="27"/>
-    </row>
-    <row r="41" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="42"/>
       <c r="B41" s="42"/>
       <c r="C41" s="42"/>
@@ -11738,15 +11598,13 @@
       <c r="E41" s="43"/>
       <c r="F41" s="42"/>
       <c r="G41" s="42" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H41" s="42"/>
       <c r="I41" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="J41" s="42" t="s">
-        <v>72</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="J41" s="42"/>
       <c r="K41" s="43"/>
       <c r="L41" s="43">
         <v>56</v>
@@ -11755,7 +11613,7 @@
         <v>8</v>
       </c>
       <c r="N41" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O41" s="43">
         <v>0.1</v>
@@ -11773,14 +11631,6 @@
       <c r="X41" s="43"/>
       <c r="Y41" s="42"/>
       <c r="Z41" s="42"/>
-      <c r="AA41" s="23"/>
-      <c r="AB41" s="27"/>
-      <c r="AC41" s="27"/>
-      <c r="AD41" s="26"/>
-      <c r="AE41" s="26"/>
-      <c r="AF41" s="27"/>
-      <c r="AG41" s="27"/>
-      <c r="AH41" s="27"/>
     </row>
   </sheetData>
   <phoneticPr fontId="44" type="noConversion"/>
@@ -11820,7 +11670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AH10"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.149999999999999" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
@@ -11859,120 +11709,120 @@
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1" ht="88.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AC1" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AD1" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE1" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AF1" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AG1" s="21" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AH1" s="21" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="2" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2" s="11">
         <v>100</v>
@@ -12007,10 +11857,10 @@
       <c r="AE2" s="10"/>
       <c r="AF2" s="10"/>
       <c r="AG2" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH2" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="AH2" s="10" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -12021,7 +11871,7 @@
       <c r="E3" s="13"/>
       <c r="F3" s="12"/>
       <c r="G3" s="12" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
@@ -12067,7 +11917,7 @@
       <c r="E4" s="13"/>
       <c r="F4" s="12"/>
       <c r="G4" s="12" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
@@ -12081,10 +11931,10 @@
       </c>
       <c r="N4" s="12"/>
       <c r="O4" s="13">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="P4" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q4" s="13"/>
       <c r="R4" s="13"/>
@@ -12107,16 +11957,16 @@
     </row>
     <row r="5" spans="1:34" s="2" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="E5" s="11">
         <v>100</v>
@@ -12151,10 +12001,10 @@
       <c r="AE5" s="10"/>
       <c r="AF5" s="10"/>
       <c r="AG5" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH5" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="AH5" s="10" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -12165,7 +12015,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
@@ -12179,10 +12029,10 @@
       </c>
       <c r="N6" s="12"/>
       <c r="O6" s="13">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="P6" s="13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q6" s="13"/>
       <c r="R6" s="13"/>
@@ -12211,7 +12061,7 @@
       <c r="E7" s="13"/>
       <c r="F7" s="12"/>
       <c r="G7" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
@@ -12225,10 +12075,10 @@
       </c>
       <c r="N7" s="12"/>
       <c r="O7" s="13">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="P7" s="13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q7" s="13"/>
       <c r="R7" s="13"/>
@@ -12251,16 +12101,16 @@
     </row>
     <row r="8" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="E8" s="16">
         <v>500</v>
@@ -12295,10 +12145,10 @@
       <c r="AE8" s="15"/>
       <c r="AF8" s="19"/>
       <c r="AG8" s="22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AH8" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -12309,7 +12159,7 @@
       <c r="E9" s="13"/>
       <c r="F9" s="12"/>
       <c r="G9" s="12" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -12323,10 +12173,10 @@
       </c>
       <c r="N9" s="12"/>
       <c r="O9" s="13">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="P9" s="13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q9" s="13"/>
       <c r="R9" s="13"/>
@@ -12355,7 +12205,7 @@
       <c r="E10" s="13"/>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
@@ -12369,10 +12219,10 @@
       </c>
       <c r="N10" s="12"/>
       <c r="O10" s="13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P10" s="13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q10" s="13"/>
       <c r="R10" s="13"/>

--- a/src/test/resources/Excel/DBC模版.xlsx
+++ b/src/test/resources/Excel/DBC模版.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_USER\SLC\Code\IDEA_Project\smart-dbc\src\test\resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D7A55C-A02A-4934-AD4D-C4C639DCCB9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C33761-CCC0-4EE1-A73A-173476E51006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="476" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2728,7 +2728,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="236">
   <si>
     <t>测试协议</t>
   </si>
@@ -3486,6 +3486,20 @@
   </si>
   <si>
     <t>counter自动累加,从0加到255,然后循环，初始值为0，每次报文发送成功(收到ACK)以后，Counter加1；在Busoff出现恢复后，按照off前的值加1继续发送; ECU Reset 以后，Counter值清零。</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>0 = 预留; 1 = 关闭; 2 = 开启; 3 = 无效值未使用;</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnChange</t>
+  </si>
+  <si>
+    <t>IfActive</t>
+  </si>
+  <si>
+    <t>OnWrite</t>
     <phoneticPr fontId="44" type="noConversion"/>
   </si>
 </sst>
@@ -10138,7 +10152,9 @@
       <c r="I12" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J12" s="44"/>
+      <c r="J12" s="52" t="s">
+        <v>235</v>
+      </c>
       <c r="K12" s="45">
         <v>0</v>
       </c>
@@ -10198,7 +10214,9 @@
       <c r="I13" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J13" s="44"/>
+      <c r="J13" s="44" t="s">
+        <v>233</v>
+      </c>
       <c r="K13" s="34">
         <v>1</v>
       </c>
@@ -10237,8 +10255,8 @@
       </c>
       <c r="W13" s="34"/>
       <c r="X13" s="34"/>
-      <c r="Y13" s="36" t="s">
-        <v>59</v>
+      <c r="Y13" s="58" t="s">
+        <v>232</v>
       </c>
       <c r="Z13" s="33" t="s">
         <v>56</v>
@@ -10260,7 +10278,9 @@
       <c r="I14" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J14" s="44"/>
+      <c r="J14" s="44" t="s">
+        <v>234</v>
+      </c>
       <c r="K14" s="34">
         <v>2</v>
       </c>
